--- a/fermentation_model/data/mem2026/LAB019-021/Mediciones-Offline-LAB019-021.xlsx
+++ b/fermentation_model/data/mem2026/LAB019-021/Mediciones-Offline-LAB019-021.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\claud\Desktop\Universidad\Memoria\Model\pyomo-doe\fermentation_model\data\mem2026\LAB019-021\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E946FA-65AD-43BE-A8F4-D40F8374705F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6752819D-75B5-4853-A457-35646CC55701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="46">
   <si>
     <t>CodigoLab</t>
   </si>
@@ -158,6 +158,9 @@
   </si>
   <si>
     <t>Disparo por densidad: muestra 7 (23-09 15:00) = 1039.0 g/L</t>
+  </si>
+  <si>
+    <t>Etanol</t>
   </si>
 </sst>
 </file>
@@ -441,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L500"/>
+  <dimension ref="A1:M500"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -450,11 +453,11 @@
     <col min="4" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
     <col min="7" max="8" width="15" customWidth="1"/>
-    <col min="9" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="30" customWidth="1"/>
+    <col min="9" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -486,13 +489,16 @@
         <v>23</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="2">
         <v>46286</v>
       </c>
@@ -519,10 +525,11 @@
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="6"/>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="K2" s="8"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="6"/>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="2">
         <v>46286</v>
       </c>
@@ -549,10 +556,11 @@
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="6"/>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="K3" s="8"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="6"/>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="2">
         <v>46286</v>
       </c>
@@ -578,10 +586,11 @@
         <v>15.7</v>
       </c>
       <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="6"/>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="K4" s="8"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="6"/>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="2">
         <v>46286</v>
       </c>
@@ -610,12 +619,15 @@
         <v>85</v>
       </c>
       <c r="J5" s="5"/>
-      <c r="K5" s="5">
+      <c r="K5" s="8">
+        <v>1.53</v>
+      </c>
+      <c r="L5" s="5">
         <v>50</v>
       </c>
-      <c r="L5" s="6"/>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="M5" s="6"/>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="2">
         <v>46286</v>
       </c>
@@ -644,12 +656,15 @@
         <v>90</v>
       </c>
       <c r="J6" s="5"/>
-      <c r="K6" s="5">
+      <c r="K6" s="8">
+        <v>1.51</v>
+      </c>
+      <c r="L6" s="5">
         <v>50</v>
       </c>
-      <c r="L6" s="6"/>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="M6" s="6"/>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="2">
         <v>46286</v>
       </c>
@@ -678,12 +693,15 @@
         <v>85</v>
       </c>
       <c r="J7" s="5"/>
-      <c r="K7" s="5">
+      <c r="K7" s="8">
+        <v>1.49</v>
+      </c>
+      <c r="L7" s="5">
         <v>50</v>
       </c>
-      <c r="L7" s="6"/>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="M7" s="6"/>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="2">
         <v>46287</v>
       </c>
@@ -712,10 +730,11 @@
         <v>71</v>
       </c>
       <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="6"/>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="K8" s="8"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="6"/>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="2">
         <v>46287</v>
       </c>
@@ -744,10 +763,11 @@
         <v>79</v>
       </c>
       <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="6"/>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="K9" s="8"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="6"/>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="2">
         <v>46287</v>
       </c>
@@ -776,10 +796,11 @@
         <v>60</v>
       </c>
       <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="6"/>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="K10" s="8"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="6"/>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="2">
         <v>46287</v>
       </c>
@@ -808,10 +829,11 @@
         <v>64</v>
       </c>
       <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="6"/>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="K11" s="8"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="6"/>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="2">
         <v>46287</v>
       </c>
@@ -840,10 +862,11 @@
         <v>79</v>
       </c>
       <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="6"/>
-    </row>
-    <row r="13" spans="1:12">
+      <c r="K12" s="8"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="6"/>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="2">
         <v>46287</v>
       </c>
@@ -872,10 +895,11 @@
         <v>66</v>
       </c>
       <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="6"/>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="K13" s="8"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="6"/>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="2">
         <v>46287</v>
       </c>
@@ -904,12 +928,15 @@
         <v>54</v>
       </c>
       <c r="J14" s="5"/>
-      <c r="K14" s="5">
+      <c r="K14" s="8">
+        <v>1.74</v>
+      </c>
+      <c r="L14" s="5">
         <v>50</v>
       </c>
-      <c r="L14" s="6"/>
-    </row>
-    <row r="15" spans="1:12">
+      <c r="M14" s="6"/>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="2">
         <v>46287</v>
       </c>
@@ -938,12 +965,15 @@
         <v>63</v>
       </c>
       <c r="J15" s="5"/>
-      <c r="K15" s="5">
+      <c r="K15" s="8">
+        <v>1.21</v>
+      </c>
+      <c r="L15" s="5">
         <v>50</v>
       </c>
-      <c r="L15" s="6"/>
-    </row>
-    <row r="16" spans="1:12">
+      <c r="M15" s="6"/>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="2">
         <v>46287</v>
       </c>
@@ -972,12 +1002,15 @@
         <v>59.5</v>
       </c>
       <c r="J16" s="5"/>
-      <c r="K16" s="5">
+      <c r="K16" s="8">
+        <v>1.93</v>
+      </c>
+      <c r="L16" s="5">
         <v>50</v>
       </c>
-      <c r="L16" s="6"/>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="M16" s="6"/>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="2">
         <v>46288</v>
       </c>
@@ -1006,10 +1039,11 @@
         <v>59</v>
       </c>
       <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="6"/>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="K17" s="8"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="6"/>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="2">
         <v>46288</v>
       </c>
@@ -1038,10 +1072,11 @@
         <v>61</v>
       </c>
       <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="6"/>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="K18" s="8"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="6"/>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="2">
         <v>46288</v>
       </c>
@@ -1070,10 +1105,11 @@
         <v>77</v>
       </c>
       <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="6"/>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="K19" s="8"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="6"/>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="2">
         <v>46288</v>
       </c>
@@ -1102,10 +1138,11 @@
         <v>80</v>
       </c>
       <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="6"/>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="K20" s="8"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="6"/>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="2">
         <v>46288</v>
       </c>
@@ -1134,10 +1171,11 @@
         <v>67</v>
       </c>
       <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="6"/>
-    </row>
-    <row r="22" spans="1:12">
+      <c r="K21" s="8"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="6"/>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="2">
         <v>46288</v>
       </c>
@@ -1166,10 +1204,11 @@
         <v>64</v>
       </c>
       <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="6"/>
-    </row>
-    <row r="23" spans="1:12">
+      <c r="K22" s="8"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="6"/>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" s="2">
         <v>46288</v>
       </c>
@@ -1196,12 +1235,15 @@
       </c>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
-      <c r="K23" s="5">
+      <c r="K23" s="8">
+        <v>2.31</v>
+      </c>
+      <c r="L23" s="5">
         <v>50</v>
       </c>
-      <c r="L23" s="6"/>
-    </row>
-    <row r="24" spans="1:12">
+      <c r="M23" s="6"/>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" s="2">
         <v>46288</v>
       </c>
@@ -1228,12 +1270,15 @@
       </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
-      <c r="K24" s="5">
+      <c r="K24" s="8">
+        <v>2.35</v>
+      </c>
+      <c r="L24" s="5">
         <v>50</v>
       </c>
-      <c r="L24" s="6"/>
-    </row>
-    <row r="25" spans="1:12">
+      <c r="M24" s="6"/>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" s="2">
         <v>46288</v>
       </c>
@@ -1260,12 +1305,15 @@
       </c>
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
-      <c r="K25" s="5">
+      <c r="K25" s="8">
+        <v>4.26</v>
+      </c>
+      <c r="L25" s="5">
         <v>50</v>
       </c>
-      <c r="L25" s="6"/>
-    </row>
-    <row r="26" spans="1:12">
+      <c r="M25" s="6"/>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" s="2">
         <v>46289</v>
       </c>
@@ -1292,10 +1340,11 @@
       </c>
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="6"/>
-    </row>
-    <row r="27" spans="1:12">
+      <c r="K26" s="8"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="6"/>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" s="2">
         <v>46289</v>
       </c>
@@ -1322,10 +1371,11 @@
       </c>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="6"/>
-    </row>
-    <row r="28" spans="1:12">
+      <c r="K27" s="8"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="6"/>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="2">
         <v>46289</v>
       </c>
@@ -1352,10 +1402,11 @@
       </c>
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="6"/>
-    </row>
-    <row r="29" spans="1:12">
+      <c r="K28" s="8"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="6"/>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="2">
         <v>46289</v>
       </c>
@@ -1382,10 +1433,11 @@
       </c>
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="6"/>
-    </row>
-    <row r="30" spans="1:12">
+      <c r="K29" s="8"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="6"/>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" s="2">
         <v>46289</v>
       </c>
@@ -1412,10 +1464,11 @@
       </c>
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="6"/>
-    </row>
-    <row r="31" spans="1:12">
+      <c r="K30" s="8"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="6"/>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="2">
         <v>46289</v>
       </c>
@@ -1442,10 +1495,11 @@
       </c>
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="6"/>
-    </row>
-    <row r="32" spans="1:12">
+      <c r="K31" s="8"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="6"/>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" s="2">
         <v>46289</v>
       </c>
@@ -1472,12 +1526,15 @@
       </c>
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
-      <c r="K32" s="5">
+      <c r="K32" s="8">
+        <v>4.1900000000000004</v>
+      </c>
+      <c r="L32" s="5">
         <v>50</v>
       </c>
-      <c r="L32" s="6"/>
-    </row>
-    <row r="33" spans="1:12">
+      <c r="M32" s="6"/>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" s="2">
         <v>46289</v>
       </c>
@@ -1504,12 +1561,15 @@
       </c>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
-      <c r="K33" s="5">
+      <c r="K33" s="8">
+        <v>3.75</v>
+      </c>
+      <c r="L33" s="5">
         <v>50</v>
       </c>
-      <c r="L33" s="6"/>
-    </row>
-    <row r="34" spans="1:12">
+      <c r="M33" s="6"/>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" s="2">
         <v>46289</v>
       </c>
@@ -1536,12 +1596,15 @@
       </c>
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
-      <c r="K34" s="5">
+      <c r="K34" s="8">
+        <v>7.27</v>
+      </c>
+      <c r="L34" s="5">
         <v>50</v>
       </c>
-      <c r="L34" s="6"/>
-    </row>
-    <row r="35" spans="1:12">
+      <c r="M34" s="6"/>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" s="2">
         <v>46290</v>
       </c>
@@ -1568,12 +1631,15 @@
       </c>
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
-      <c r="K35" s="5">
+      <c r="K35" s="8">
+        <v>6.13</v>
+      </c>
+      <c r="L35" s="5">
         <v>50</v>
       </c>
-      <c r="L35" s="6"/>
-    </row>
-    <row r="36" spans="1:12">
+      <c r="M35" s="6"/>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" s="2">
         <v>46290</v>
       </c>
@@ -1600,12 +1666,15 @@
       </c>
       <c r="I36" s="5"/>
       <c r="J36" s="5"/>
-      <c r="K36" s="5">
+      <c r="K36" s="8">
+        <v>5.09</v>
+      </c>
+      <c r="L36" s="5">
         <v>50</v>
       </c>
-      <c r="L36" s="6"/>
-    </row>
-    <row r="37" spans="1:12">
+      <c r="M36" s="6"/>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" s="2">
         <v>46290</v>
       </c>
@@ -1632,12 +1701,15 @@
       </c>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
-      <c r="K37" s="5">
+      <c r="K37" s="8">
+        <v>8.83</v>
+      </c>
+      <c r="L37" s="5">
         <v>50</v>
       </c>
-      <c r="L37" s="6"/>
-    </row>
-    <row r="38" spans="1:12">
+      <c r="M37" s="6"/>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" s="2">
         <v>46293</v>
       </c>
@@ -1664,12 +1736,15 @@
       </c>
       <c r="I38" s="5"/>
       <c r="J38" s="5"/>
-      <c r="K38" s="5">
+      <c r="K38" s="8">
+        <v>9.91</v>
+      </c>
+      <c r="L38" s="5">
         <v>50</v>
       </c>
-      <c r="L38" s="6"/>
-    </row>
-    <row r="39" spans="1:12">
+      <c r="M38" s="6"/>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" s="2">
         <v>46293</v>
       </c>
@@ -1696,12 +1771,15 @@
       </c>
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
-      <c r="K39" s="5">
+      <c r="K39" s="8">
+        <v>7.33</v>
+      </c>
+      <c r="L39" s="5">
         <v>50</v>
       </c>
-      <c r="L39" s="6"/>
-    </row>
-    <row r="40" spans="1:12">
+      <c r="M39" s="6"/>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" s="2">
         <v>46293</v>
       </c>
@@ -1728,12 +1806,15 @@
       </c>
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
-      <c r="K40" s="5">
+      <c r="K40" s="8">
+        <v>8.66</v>
+      </c>
+      <c r="L40" s="5">
         <v>50</v>
       </c>
-      <c r="L40" s="6"/>
-    </row>
-    <row r="41" spans="1:12">
+      <c r="M40" s="6"/>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" s="2"/>
       <c r="B41" s="3"/>
       <c r="F41" s="4"/>
@@ -1742,9 +1823,10 @@
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
-      <c r="L41" s="6"/>
-    </row>
-    <row r="42" spans="1:12">
+      <c r="L41" s="5"/>
+      <c r="M41" s="6"/>
+    </row>
+    <row r="42" spans="1:13">
       <c r="A42" s="2"/>
       <c r="B42" s="3"/>
       <c r="F42" s="4"/>
@@ -1753,9 +1835,10 @@
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
-      <c r="L42" s="6"/>
-    </row>
-    <row r="43" spans="1:12">
+      <c r="L42" s="5"/>
+      <c r="M42" s="6"/>
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43" s="2"/>
       <c r="B43" s="3"/>
       <c r="F43" s="4"/>
@@ -1764,9 +1847,10 @@
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
-      <c r="L43" s="6"/>
-    </row>
-    <row r="44" spans="1:12">
+      <c r="L43" s="5"/>
+      <c r="M43" s="6"/>
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44" s="2"/>
       <c r="B44" s="3"/>
       <c r="F44" s="4"/>
@@ -1775,9 +1859,10 @@
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
-      <c r="L44" s="6"/>
-    </row>
-    <row r="45" spans="1:12">
+      <c r="L44" s="5"/>
+      <c r="M44" s="6"/>
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45" s="2"/>
       <c r="B45" s="3"/>
       <c r="F45" s="4"/>
@@ -1786,9 +1871,10 @@
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
-      <c r="L45" s="6"/>
-    </row>
-    <row r="46" spans="1:12">
+      <c r="L45" s="5"/>
+      <c r="M45" s="6"/>
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46" s="2"/>
       <c r="B46" s="3"/>
       <c r="F46" s="4"/>
@@ -1797,9 +1883,10 @@
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
-      <c r="L46" s="6"/>
-    </row>
-    <row r="47" spans="1:12">
+      <c r="L46" s="5"/>
+      <c r="M46" s="6"/>
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47" s="2"/>
       <c r="B47" s="3"/>
       <c r="F47" s="4"/>
@@ -1808,9 +1895,10 @@
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
-      <c r="L47" s="6"/>
-    </row>
-    <row r="48" spans="1:12">
+      <c r="L47" s="5"/>
+      <c r="M47" s="6"/>
+    </row>
+    <row r="48" spans="1:13">
       <c r="A48" s="2"/>
       <c r="B48" s="3"/>
       <c r="F48" s="4"/>
@@ -1819,9 +1907,10 @@
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
       <c r="K48" s="5"/>
-      <c r="L48" s="6"/>
-    </row>
-    <row r="49" spans="1:12">
+      <c r="L48" s="5"/>
+      <c r="M48" s="6"/>
+    </row>
+    <row r="49" spans="1:13">
       <c r="A49" s="2"/>
       <c r="B49" s="3"/>
       <c r="F49" s="4"/>
@@ -1830,9 +1919,10 @@
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
       <c r="K49" s="5"/>
-      <c r="L49" s="6"/>
-    </row>
-    <row r="50" spans="1:12">
+      <c r="L49" s="5"/>
+      <c r="M49" s="6"/>
+    </row>
+    <row r="50" spans="1:13">
       <c r="A50" s="2"/>
       <c r="B50" s="3"/>
       <c r="F50" s="4"/>
@@ -1841,9 +1931,10 @@
       <c r="I50" s="5"/>
       <c r="J50" s="5"/>
       <c r="K50" s="5"/>
-      <c r="L50" s="6"/>
-    </row>
-    <row r="51" spans="1:12">
+      <c r="L50" s="5"/>
+      <c r="M50" s="6"/>
+    </row>
+    <row r="51" spans="1:13">
       <c r="A51" s="2"/>
       <c r="B51" s="3"/>
       <c r="F51" s="4"/>
@@ -1852,9 +1943,10 @@
       <c r="I51" s="5"/>
       <c r="J51" s="5"/>
       <c r="K51" s="5"/>
-      <c r="L51" s="6"/>
-    </row>
-    <row r="52" spans="1:12">
+      <c r="L51" s="5"/>
+      <c r="M51" s="6"/>
+    </row>
+    <row r="52" spans="1:13">
       <c r="A52" s="2"/>
       <c r="B52" s="3"/>
       <c r="F52" s="4"/>
@@ -1863,9 +1955,10 @@
       <c r="I52" s="5"/>
       <c r="J52" s="5"/>
       <c r="K52" s="5"/>
-      <c r="L52" s="6"/>
-    </row>
-    <row r="53" spans="1:12">
+      <c r="L52" s="5"/>
+      <c r="M52" s="6"/>
+    </row>
+    <row r="53" spans="1:13">
       <c r="A53" s="2"/>
       <c r="B53" s="3"/>
       <c r="F53" s="4"/>
@@ -1874,9 +1967,10 @@
       <c r="I53" s="5"/>
       <c r="J53" s="5"/>
       <c r="K53" s="5"/>
-      <c r="L53" s="6"/>
-    </row>
-    <row r="54" spans="1:12">
+      <c r="L53" s="5"/>
+      <c r="M53" s="6"/>
+    </row>
+    <row r="54" spans="1:13">
       <c r="A54" s="2"/>
       <c r="B54" s="3"/>
       <c r="F54" s="4"/>
@@ -1885,9 +1979,10 @@
       <c r="I54" s="5"/>
       <c r="J54" s="5"/>
       <c r="K54" s="5"/>
-      <c r="L54" s="6"/>
-    </row>
-    <row r="55" spans="1:12">
+      <c r="L54" s="5"/>
+      <c r="M54" s="6"/>
+    </row>
+    <row r="55" spans="1:13">
       <c r="A55" s="2"/>
       <c r="B55" s="3"/>
       <c r="F55" s="4"/>
@@ -1896,9 +1991,10 @@
       <c r="I55" s="5"/>
       <c r="J55" s="5"/>
       <c r="K55" s="5"/>
-      <c r="L55" s="6"/>
-    </row>
-    <row r="56" spans="1:12">
+      <c r="L55" s="5"/>
+      <c r="M55" s="6"/>
+    </row>
+    <row r="56" spans="1:13">
       <c r="A56" s="2"/>
       <c r="B56" s="3"/>
       <c r="F56" s="4"/>
@@ -1907,9 +2003,10 @@
       <c r="I56" s="5"/>
       <c r="J56" s="5"/>
       <c r="K56" s="5"/>
-      <c r="L56" s="6"/>
-    </row>
-    <row r="57" spans="1:12">
+      <c r="L56" s="5"/>
+      <c r="M56" s="6"/>
+    </row>
+    <row r="57" spans="1:13">
       <c r="A57" s="2"/>
       <c r="B57" s="3"/>
       <c r="F57" s="4"/>
@@ -1918,9 +2015,10 @@
       <c r="I57" s="5"/>
       <c r="J57" s="5"/>
       <c r="K57" s="5"/>
-      <c r="L57" s="6"/>
-    </row>
-    <row r="58" spans="1:12">
+      <c r="L57" s="5"/>
+      <c r="M57" s="6"/>
+    </row>
+    <row r="58" spans="1:13">
       <c r="A58" s="2"/>
       <c r="B58" s="3"/>
       <c r="F58" s="4"/>
@@ -1929,9 +2027,10 @@
       <c r="I58" s="5"/>
       <c r="J58" s="5"/>
       <c r="K58" s="5"/>
-      <c r="L58" s="6"/>
-    </row>
-    <row r="59" spans="1:12">
+      <c r="L58" s="5"/>
+      <c r="M58" s="6"/>
+    </row>
+    <row r="59" spans="1:13">
       <c r="A59" s="2"/>
       <c r="B59" s="3"/>
       <c r="F59" s="4"/>
@@ -1940,9 +2039,10 @@
       <c r="I59" s="5"/>
       <c r="J59" s="5"/>
       <c r="K59" s="5"/>
-      <c r="L59" s="6"/>
-    </row>
-    <row r="60" spans="1:12">
+      <c r="L59" s="5"/>
+      <c r="M59" s="6"/>
+    </row>
+    <row r="60" spans="1:13">
       <c r="A60" s="2"/>
       <c r="B60" s="3"/>
       <c r="F60" s="4"/>
@@ -1951,9 +2051,10 @@
       <c r="I60" s="5"/>
       <c r="J60" s="5"/>
       <c r="K60" s="5"/>
-      <c r="L60" s="6"/>
-    </row>
-    <row r="61" spans="1:12">
+      <c r="L60" s="5"/>
+      <c r="M60" s="6"/>
+    </row>
+    <row r="61" spans="1:13">
       <c r="A61" s="2"/>
       <c r="B61" s="3"/>
       <c r="F61" s="4"/>
@@ -1962,9 +2063,10 @@
       <c r="I61" s="5"/>
       <c r="J61" s="5"/>
       <c r="K61" s="5"/>
-      <c r="L61" s="6"/>
-    </row>
-    <row r="62" spans="1:12">
+      <c r="L61" s="5"/>
+      <c r="M61" s="6"/>
+    </row>
+    <row r="62" spans="1:13">
       <c r="A62" s="2"/>
       <c r="B62" s="3"/>
       <c r="F62" s="4"/>
@@ -1973,9 +2075,10 @@
       <c r="I62" s="5"/>
       <c r="J62" s="5"/>
       <c r="K62" s="5"/>
-      <c r="L62" s="6"/>
-    </row>
-    <row r="63" spans="1:12">
+      <c r="L62" s="5"/>
+      <c r="M62" s="6"/>
+    </row>
+    <row r="63" spans="1:13">
       <c r="A63" s="2"/>
       <c r="B63" s="3"/>
       <c r="F63" s="4"/>
@@ -1984,9 +2087,10 @@
       <c r="I63" s="5"/>
       <c r="J63" s="5"/>
       <c r="K63" s="5"/>
-      <c r="L63" s="6"/>
-    </row>
-    <row r="64" spans="1:12">
+      <c r="L63" s="5"/>
+      <c r="M63" s="6"/>
+    </row>
+    <row r="64" spans="1:13">
       <c r="A64" s="2"/>
       <c r="B64" s="3"/>
       <c r="F64" s="4"/>
@@ -1995,9 +2099,10 @@
       <c r="I64" s="5"/>
       <c r="J64" s="5"/>
       <c r="K64" s="5"/>
-      <c r="L64" s="6"/>
-    </row>
-    <row r="65" spans="1:12">
+      <c r="L64" s="5"/>
+      <c r="M64" s="6"/>
+    </row>
+    <row r="65" spans="1:13">
       <c r="A65" s="2"/>
       <c r="B65" s="3"/>
       <c r="F65" s="4"/>
@@ -2006,9 +2111,10 @@
       <c r="I65" s="5"/>
       <c r="J65" s="5"/>
       <c r="K65" s="5"/>
-      <c r="L65" s="6"/>
-    </row>
-    <row r="66" spans="1:12">
+      <c r="L65" s="5"/>
+      <c r="M65" s="6"/>
+    </row>
+    <row r="66" spans="1:13">
       <c r="A66" s="2"/>
       <c r="B66" s="3"/>
       <c r="F66" s="4"/>
@@ -2017,9 +2123,10 @@
       <c r="I66" s="5"/>
       <c r="J66" s="5"/>
       <c r="K66" s="5"/>
-      <c r="L66" s="6"/>
-    </row>
-    <row r="67" spans="1:12">
+      <c r="L66" s="5"/>
+      <c r="M66" s="6"/>
+    </row>
+    <row r="67" spans="1:13">
       <c r="A67" s="2"/>
       <c r="B67" s="3"/>
       <c r="F67" s="4"/>
@@ -2028,9 +2135,10 @@
       <c r="I67" s="5"/>
       <c r="J67" s="5"/>
       <c r="K67" s="5"/>
-      <c r="L67" s="6"/>
-    </row>
-    <row r="68" spans="1:12">
+      <c r="L67" s="5"/>
+      <c r="M67" s="6"/>
+    </row>
+    <row r="68" spans="1:13">
       <c r="A68" s="2"/>
       <c r="B68" s="3"/>
       <c r="F68" s="4"/>
@@ -2039,9 +2147,10 @@
       <c r="I68" s="5"/>
       <c r="J68" s="5"/>
       <c r="K68" s="5"/>
-      <c r="L68" s="6"/>
-    </row>
-    <row r="69" spans="1:12">
+      <c r="L68" s="5"/>
+      <c r="M68" s="6"/>
+    </row>
+    <row r="69" spans="1:13">
       <c r="A69" s="2"/>
       <c r="B69" s="3"/>
       <c r="F69" s="4"/>
@@ -2050,9 +2159,10 @@
       <c r="I69" s="5"/>
       <c r="J69" s="5"/>
       <c r="K69" s="5"/>
-      <c r="L69" s="6"/>
-    </row>
-    <row r="70" spans="1:12">
+      <c r="L69" s="5"/>
+      <c r="M69" s="6"/>
+    </row>
+    <row r="70" spans="1:13">
       <c r="A70" s="2"/>
       <c r="B70" s="3"/>
       <c r="F70" s="4"/>
@@ -2061,9 +2171,10 @@
       <c r="I70" s="5"/>
       <c r="J70" s="5"/>
       <c r="K70" s="5"/>
-      <c r="L70" s="6"/>
-    </row>
-    <row r="71" spans="1:12">
+      <c r="L70" s="5"/>
+      <c r="M70" s="6"/>
+    </row>
+    <row r="71" spans="1:13">
       <c r="A71" s="2"/>
       <c r="B71" s="3"/>
       <c r="F71" s="4"/>
@@ -2072,9 +2183,10 @@
       <c r="I71" s="5"/>
       <c r="J71" s="5"/>
       <c r="K71" s="5"/>
-      <c r="L71" s="6"/>
-    </row>
-    <row r="72" spans="1:12">
+      <c r="L71" s="5"/>
+      <c r="M71" s="6"/>
+    </row>
+    <row r="72" spans="1:13">
       <c r="A72" s="2"/>
       <c r="B72" s="3"/>
       <c r="F72" s="4"/>
@@ -2083,9 +2195,10 @@
       <c r="I72" s="5"/>
       <c r="J72" s="5"/>
       <c r="K72" s="5"/>
-      <c r="L72" s="6"/>
-    </row>
-    <row r="73" spans="1:12">
+      <c r="L72" s="5"/>
+      <c r="M72" s="6"/>
+    </row>
+    <row r="73" spans="1:13">
       <c r="A73" s="2"/>
       <c r="B73" s="3"/>
       <c r="F73" s="4"/>
@@ -2094,9 +2207,10 @@
       <c r="I73" s="5"/>
       <c r="J73" s="5"/>
       <c r="K73" s="5"/>
-      <c r="L73" s="6"/>
-    </row>
-    <row r="74" spans="1:12">
+      <c r="L73" s="5"/>
+      <c r="M73" s="6"/>
+    </row>
+    <row r="74" spans="1:13">
       <c r="A74" s="2"/>
       <c r="B74" s="3"/>
       <c r="F74" s="4"/>
@@ -2105,9 +2219,10 @@
       <c r="I74" s="5"/>
       <c r="J74" s="5"/>
       <c r="K74" s="5"/>
-      <c r="L74" s="6"/>
-    </row>
-    <row r="75" spans="1:12">
+      <c r="L74" s="5"/>
+      <c r="M74" s="6"/>
+    </row>
+    <row r="75" spans="1:13">
       <c r="A75" s="2"/>
       <c r="B75" s="3"/>
       <c r="F75" s="4"/>
@@ -2116,9 +2231,10 @@
       <c r="I75" s="5"/>
       <c r="J75" s="5"/>
       <c r="K75" s="5"/>
-      <c r="L75" s="6"/>
-    </row>
-    <row r="76" spans="1:12">
+      <c r="L75" s="5"/>
+      <c r="M75" s="6"/>
+    </row>
+    <row r="76" spans="1:13">
       <c r="A76" s="2"/>
       <c r="B76" s="3"/>
       <c r="F76" s="4"/>
@@ -2127,9 +2243,10 @@
       <c r="I76" s="5"/>
       <c r="J76" s="5"/>
       <c r="K76" s="5"/>
-      <c r="L76" s="6"/>
-    </row>
-    <row r="77" spans="1:12">
+      <c r="L76" s="5"/>
+      <c r="M76" s="6"/>
+    </row>
+    <row r="77" spans="1:13">
       <c r="A77" s="2"/>
       <c r="B77" s="3"/>
       <c r="F77" s="4"/>
@@ -2138,9 +2255,10 @@
       <c r="I77" s="5"/>
       <c r="J77" s="5"/>
       <c r="K77" s="5"/>
-      <c r="L77" s="6"/>
-    </row>
-    <row r="78" spans="1:12">
+      <c r="L77" s="5"/>
+      <c r="M77" s="6"/>
+    </row>
+    <row r="78" spans="1:13">
       <c r="A78" s="2"/>
       <c r="B78" s="3"/>
       <c r="F78" s="4"/>
@@ -2149,9 +2267,10 @@
       <c r="I78" s="5"/>
       <c r="J78" s="5"/>
       <c r="K78" s="5"/>
-      <c r="L78" s="6"/>
-    </row>
-    <row r="79" spans="1:12">
+      <c r="L78" s="5"/>
+      <c r="M78" s="6"/>
+    </row>
+    <row r="79" spans="1:13">
       <c r="A79" s="2"/>
       <c r="B79" s="3"/>
       <c r="F79" s="4"/>
@@ -2160,9 +2279,10 @@
       <c r="I79" s="5"/>
       <c r="J79" s="5"/>
       <c r="K79" s="5"/>
-      <c r="L79" s="6"/>
-    </row>
-    <row r="80" spans="1:12">
+      <c r="L79" s="5"/>
+      <c r="M79" s="6"/>
+    </row>
+    <row r="80" spans="1:13">
       <c r="A80" s="2"/>
       <c r="B80" s="3"/>
       <c r="F80" s="4"/>
@@ -2171,9 +2291,10 @@
       <c r="I80" s="5"/>
       <c r="J80" s="5"/>
       <c r="K80" s="5"/>
-      <c r="L80" s="6"/>
-    </row>
-    <row r="81" spans="1:12">
+      <c r="L80" s="5"/>
+      <c r="M80" s="6"/>
+    </row>
+    <row r="81" spans="1:13">
       <c r="A81" s="2"/>
       <c r="B81" s="3"/>
       <c r="F81" s="4"/>
@@ -2182,9 +2303,10 @@
       <c r="I81" s="5"/>
       <c r="J81" s="5"/>
       <c r="K81" s="5"/>
-      <c r="L81" s="6"/>
-    </row>
-    <row r="82" spans="1:12">
+      <c r="L81" s="5"/>
+      <c r="M81" s="6"/>
+    </row>
+    <row r="82" spans="1:13">
       <c r="A82" s="2"/>
       <c r="B82" s="3"/>
       <c r="F82" s="4"/>
@@ -2193,9 +2315,10 @@
       <c r="I82" s="5"/>
       <c r="J82" s="5"/>
       <c r="K82" s="5"/>
-      <c r="L82" s="6"/>
-    </row>
-    <row r="83" spans="1:12">
+      <c r="L82" s="5"/>
+      <c r="M82" s="6"/>
+    </row>
+    <row r="83" spans="1:13">
       <c r="A83" s="2"/>
       <c r="B83" s="3"/>
       <c r="F83" s="4"/>
@@ -2204,9 +2327,10 @@
       <c r="I83" s="5"/>
       <c r="J83" s="5"/>
       <c r="K83" s="5"/>
-      <c r="L83" s="6"/>
-    </row>
-    <row r="84" spans="1:12">
+      <c r="L83" s="5"/>
+      <c r="M83" s="6"/>
+    </row>
+    <row r="84" spans="1:13">
       <c r="A84" s="2"/>
       <c r="B84" s="3"/>
       <c r="F84" s="4"/>
@@ -2215,9 +2339,10 @@
       <c r="I84" s="5"/>
       <c r="J84" s="5"/>
       <c r="K84" s="5"/>
-      <c r="L84" s="6"/>
-    </row>
-    <row r="85" spans="1:12">
+      <c r="L84" s="5"/>
+      <c r="M84" s="6"/>
+    </row>
+    <row r="85" spans="1:13">
       <c r="A85" s="2"/>
       <c r="B85" s="3"/>
       <c r="F85" s="4"/>
@@ -2226,9 +2351,10 @@
       <c r="I85" s="5"/>
       <c r="J85" s="5"/>
       <c r="K85" s="5"/>
-      <c r="L85" s="6"/>
-    </row>
-    <row r="86" spans="1:12">
+      <c r="L85" s="5"/>
+      <c r="M85" s="6"/>
+    </row>
+    <row r="86" spans="1:13">
       <c r="A86" s="2"/>
       <c r="B86" s="3"/>
       <c r="F86" s="4"/>
@@ -2237,9 +2363,10 @@
       <c r="I86" s="5"/>
       <c r="J86" s="5"/>
       <c r="K86" s="5"/>
-      <c r="L86" s="6"/>
-    </row>
-    <row r="87" spans="1:12">
+      <c r="L86" s="5"/>
+      <c r="M86" s="6"/>
+    </row>
+    <row r="87" spans="1:13">
       <c r="A87" s="2"/>
       <c r="B87" s="3"/>
       <c r="F87" s="4"/>
@@ -2248,9 +2375,10 @@
       <c r="I87" s="5"/>
       <c r="J87" s="5"/>
       <c r="K87" s="5"/>
-      <c r="L87" s="6"/>
-    </row>
-    <row r="88" spans="1:12">
+      <c r="L87" s="5"/>
+      <c r="M87" s="6"/>
+    </row>
+    <row r="88" spans="1:13">
       <c r="A88" s="2"/>
       <c r="B88" s="3"/>
       <c r="F88" s="4"/>
@@ -2259,9 +2387,10 @@
       <c r="I88" s="5"/>
       <c r="J88" s="5"/>
       <c r="K88" s="5"/>
-      <c r="L88" s="6"/>
-    </row>
-    <row r="89" spans="1:12">
+      <c r="L88" s="5"/>
+      <c r="M88" s="6"/>
+    </row>
+    <row r="89" spans="1:13">
       <c r="A89" s="2"/>
       <c r="B89" s="3"/>
       <c r="F89" s="4"/>
@@ -2270,9 +2399,10 @@
       <c r="I89" s="5"/>
       <c r="J89" s="5"/>
       <c r="K89" s="5"/>
-      <c r="L89" s="6"/>
-    </row>
-    <row r="90" spans="1:12">
+      <c r="L89" s="5"/>
+      <c r="M89" s="6"/>
+    </row>
+    <row r="90" spans="1:13">
       <c r="A90" s="2"/>
       <c r="B90" s="3"/>
       <c r="F90" s="4"/>
@@ -2281,9 +2411,10 @@
       <c r="I90" s="5"/>
       <c r="J90" s="5"/>
       <c r="K90" s="5"/>
-      <c r="L90" s="6"/>
-    </row>
-    <row r="91" spans="1:12">
+      <c r="L90" s="5"/>
+      <c r="M90" s="6"/>
+    </row>
+    <row r="91" spans="1:13">
       <c r="A91" s="2"/>
       <c r="B91" s="3"/>
       <c r="F91" s="4"/>
@@ -2292,9 +2423,10 @@
       <c r="I91" s="5"/>
       <c r="J91" s="5"/>
       <c r="K91" s="5"/>
-      <c r="L91" s="6"/>
-    </row>
-    <row r="92" spans="1:12">
+      <c r="L91" s="5"/>
+      <c r="M91" s="6"/>
+    </row>
+    <row r="92" spans="1:13">
       <c r="A92" s="2"/>
       <c r="B92" s="3"/>
       <c r="F92" s="4"/>
@@ -2303,9 +2435,10 @@
       <c r="I92" s="5"/>
       <c r="J92" s="5"/>
       <c r="K92" s="5"/>
-      <c r="L92" s="6"/>
-    </row>
-    <row r="93" spans="1:12">
+      <c r="L92" s="5"/>
+      <c r="M92" s="6"/>
+    </row>
+    <row r="93" spans="1:13">
       <c r="A93" s="2"/>
       <c r="B93" s="3"/>
       <c r="F93" s="4"/>
@@ -2314,9 +2447,10 @@
       <c r="I93" s="5"/>
       <c r="J93" s="5"/>
       <c r="K93" s="5"/>
-      <c r="L93" s="6"/>
-    </row>
-    <row r="94" spans="1:12">
+      <c r="L93" s="5"/>
+      <c r="M93" s="6"/>
+    </row>
+    <row r="94" spans="1:13">
       <c r="A94" s="2"/>
       <c r="B94" s="3"/>
       <c r="F94" s="4"/>
@@ -2325,9 +2459,10 @@
       <c r="I94" s="5"/>
       <c r="J94" s="5"/>
       <c r="K94" s="5"/>
-      <c r="L94" s="6"/>
-    </row>
-    <row r="95" spans="1:12">
+      <c r="L94" s="5"/>
+      <c r="M94" s="6"/>
+    </row>
+    <row r="95" spans="1:13">
       <c r="A95" s="2"/>
       <c r="B95" s="3"/>
       <c r="F95" s="4"/>
@@ -2336,9 +2471,10 @@
       <c r="I95" s="5"/>
       <c r="J95" s="5"/>
       <c r="K95" s="5"/>
-      <c r="L95" s="6"/>
-    </row>
-    <row r="96" spans="1:12">
+      <c r="L95" s="5"/>
+      <c r="M95" s="6"/>
+    </row>
+    <row r="96" spans="1:13">
       <c r="A96" s="2"/>
       <c r="B96" s="3"/>
       <c r="F96" s="4"/>
@@ -2347,9 +2483,10 @@
       <c r="I96" s="5"/>
       <c r="J96" s="5"/>
       <c r="K96" s="5"/>
-      <c r="L96" s="6"/>
-    </row>
-    <row r="97" spans="1:12">
+      <c r="L96" s="5"/>
+      <c r="M96" s="6"/>
+    </row>
+    <row r="97" spans="1:13">
       <c r="A97" s="2"/>
       <c r="B97" s="3"/>
       <c r="F97" s="4"/>
@@ -2358,9 +2495,10 @@
       <c r="I97" s="5"/>
       <c r="J97" s="5"/>
       <c r="K97" s="5"/>
-      <c r="L97" s="6"/>
-    </row>
-    <row r="98" spans="1:12">
+      <c r="L97" s="5"/>
+      <c r="M97" s="6"/>
+    </row>
+    <row r="98" spans="1:13">
       <c r="A98" s="2"/>
       <c r="B98" s="3"/>
       <c r="F98" s="4"/>
@@ -2369,9 +2507,10 @@
       <c r="I98" s="5"/>
       <c r="J98" s="5"/>
       <c r="K98" s="5"/>
-      <c r="L98" s="6"/>
-    </row>
-    <row r="99" spans="1:12">
+      <c r="L98" s="5"/>
+      <c r="M98" s="6"/>
+    </row>
+    <row r="99" spans="1:13">
       <c r="A99" s="2"/>
       <c r="B99" s="3"/>
       <c r="F99" s="4"/>
@@ -2380,9 +2519,10 @@
       <c r="I99" s="5"/>
       <c r="J99" s="5"/>
       <c r="K99" s="5"/>
-      <c r="L99" s="6"/>
-    </row>
-    <row r="100" spans="1:12">
+      <c r="L99" s="5"/>
+      <c r="M99" s="6"/>
+    </row>
+    <row r="100" spans="1:13">
       <c r="A100" s="2"/>
       <c r="B100" s="3"/>
       <c r="F100" s="4"/>
@@ -2391,9 +2531,10 @@
       <c r="I100" s="5"/>
       <c r="J100" s="5"/>
       <c r="K100" s="5"/>
-      <c r="L100" s="6"/>
-    </row>
-    <row r="101" spans="1:12">
+      <c r="L100" s="5"/>
+      <c r="M100" s="6"/>
+    </row>
+    <row r="101" spans="1:13">
       <c r="A101" s="2"/>
       <c r="B101" s="3"/>
       <c r="F101" s="4"/>
@@ -2402,9 +2543,10 @@
       <c r="I101" s="5"/>
       <c r="J101" s="5"/>
       <c r="K101" s="5"/>
-      <c r="L101" s="6"/>
-    </row>
-    <row r="102" spans="1:12">
+      <c r="L101" s="5"/>
+      <c r="M101" s="6"/>
+    </row>
+    <row r="102" spans="1:13">
       <c r="A102" s="2"/>
       <c r="B102" s="3"/>
       <c r="F102" s="4"/>
@@ -2413,9 +2555,10 @@
       <c r="I102" s="5"/>
       <c r="J102" s="5"/>
       <c r="K102" s="5"/>
-      <c r="L102" s="6"/>
-    </row>
-    <row r="103" spans="1:12">
+      <c r="L102" s="5"/>
+      <c r="M102" s="6"/>
+    </row>
+    <row r="103" spans="1:13">
       <c r="A103" s="2"/>
       <c r="B103" s="3"/>
       <c r="F103" s="4"/>
@@ -2424,9 +2567,10 @@
       <c r="I103" s="5"/>
       <c r="J103" s="5"/>
       <c r="K103" s="5"/>
-      <c r="L103" s="6"/>
-    </row>
-    <row r="104" spans="1:12">
+      <c r="L103" s="5"/>
+      <c r="M103" s="6"/>
+    </row>
+    <row r="104" spans="1:13">
       <c r="A104" s="2"/>
       <c r="B104" s="3"/>
       <c r="F104" s="4"/>
@@ -2435,9 +2579,10 @@
       <c r="I104" s="5"/>
       <c r="J104" s="5"/>
       <c r="K104" s="5"/>
-      <c r="L104" s="6"/>
-    </row>
-    <row r="105" spans="1:12">
+      <c r="L104" s="5"/>
+      <c r="M104" s="6"/>
+    </row>
+    <row r="105" spans="1:13">
       <c r="A105" s="2"/>
       <c r="B105" s="3"/>
       <c r="F105" s="4"/>
@@ -2446,9 +2591,10 @@
       <c r="I105" s="5"/>
       <c r="J105" s="5"/>
       <c r="K105" s="5"/>
-      <c r="L105" s="6"/>
-    </row>
-    <row r="106" spans="1:12">
+      <c r="L105" s="5"/>
+      <c r="M105" s="6"/>
+    </row>
+    <row r="106" spans="1:13">
       <c r="A106" s="2"/>
       <c r="B106" s="3"/>
       <c r="F106" s="4"/>
@@ -2457,9 +2603,10 @@
       <c r="I106" s="5"/>
       <c r="J106" s="5"/>
       <c r="K106" s="5"/>
-      <c r="L106" s="6"/>
-    </row>
-    <row r="107" spans="1:12">
+      <c r="L106" s="5"/>
+      <c r="M106" s="6"/>
+    </row>
+    <row r="107" spans="1:13">
       <c r="A107" s="2"/>
       <c r="B107" s="3"/>
       <c r="F107" s="4"/>
@@ -2468,9 +2615,10 @@
       <c r="I107" s="5"/>
       <c r="J107" s="5"/>
       <c r="K107" s="5"/>
-      <c r="L107" s="6"/>
-    </row>
-    <row r="108" spans="1:12">
+      <c r="L107" s="5"/>
+      <c r="M107" s="6"/>
+    </row>
+    <row r="108" spans="1:13">
       <c r="A108" s="2"/>
       <c r="B108" s="3"/>
       <c r="F108" s="4"/>
@@ -2479,9 +2627,10 @@
       <c r="I108" s="5"/>
       <c r="J108" s="5"/>
       <c r="K108" s="5"/>
-      <c r="L108" s="6"/>
-    </row>
-    <row r="109" spans="1:12">
+      <c r="L108" s="5"/>
+      <c r="M108" s="6"/>
+    </row>
+    <row r="109" spans="1:13">
       <c r="A109" s="2"/>
       <c r="B109" s="3"/>
       <c r="F109" s="4"/>
@@ -2490,9 +2639,10 @@
       <c r="I109" s="5"/>
       <c r="J109" s="5"/>
       <c r="K109" s="5"/>
-      <c r="L109" s="6"/>
-    </row>
-    <row r="110" spans="1:12">
+      <c r="L109" s="5"/>
+      <c r="M109" s="6"/>
+    </row>
+    <row r="110" spans="1:13">
       <c r="A110" s="2"/>
       <c r="B110" s="3"/>
       <c r="F110" s="4"/>
@@ -2501,9 +2651,10 @@
       <c r="I110" s="5"/>
       <c r="J110" s="5"/>
       <c r="K110" s="5"/>
-      <c r="L110" s="6"/>
-    </row>
-    <row r="111" spans="1:12">
+      <c r="L110" s="5"/>
+      <c r="M110" s="6"/>
+    </row>
+    <row r="111" spans="1:13">
       <c r="A111" s="2"/>
       <c r="B111" s="3"/>
       <c r="F111" s="4"/>
@@ -2512,9 +2663,10 @@
       <c r="I111" s="5"/>
       <c r="J111" s="5"/>
       <c r="K111" s="5"/>
-      <c r="L111" s="6"/>
-    </row>
-    <row r="112" spans="1:12">
+      <c r="L111" s="5"/>
+      <c r="M111" s="6"/>
+    </row>
+    <row r="112" spans="1:13">
       <c r="A112" s="2"/>
       <c r="B112" s="3"/>
       <c r="F112" s="4"/>
@@ -2523,9 +2675,10 @@
       <c r="I112" s="5"/>
       <c r="J112" s="5"/>
       <c r="K112" s="5"/>
-      <c r="L112" s="6"/>
-    </row>
-    <row r="113" spans="1:12">
+      <c r="L112" s="5"/>
+      <c r="M112" s="6"/>
+    </row>
+    <row r="113" spans="1:13">
       <c r="A113" s="2"/>
       <c r="B113" s="3"/>
       <c r="F113" s="4"/>
@@ -2534,9 +2687,10 @@
       <c r="I113" s="5"/>
       <c r="J113" s="5"/>
       <c r="K113" s="5"/>
-      <c r="L113" s="6"/>
-    </row>
-    <row r="114" spans="1:12">
+      <c r="L113" s="5"/>
+      <c r="M113" s="6"/>
+    </row>
+    <row r="114" spans="1:13">
       <c r="A114" s="2"/>
       <c r="B114" s="3"/>
       <c r="F114" s="4"/>
@@ -2545,9 +2699,10 @@
       <c r="I114" s="5"/>
       <c r="J114" s="5"/>
       <c r="K114" s="5"/>
-      <c r="L114" s="6"/>
-    </row>
-    <row r="115" spans="1:12">
+      <c r="L114" s="5"/>
+      <c r="M114" s="6"/>
+    </row>
+    <row r="115" spans="1:13">
       <c r="A115" s="2"/>
       <c r="B115" s="3"/>
       <c r="F115" s="4"/>
@@ -2556,9 +2711,10 @@
       <c r="I115" s="5"/>
       <c r="J115" s="5"/>
       <c r="K115" s="5"/>
-      <c r="L115" s="6"/>
-    </row>
-    <row r="116" spans="1:12">
+      <c r="L115" s="5"/>
+      <c r="M115" s="6"/>
+    </row>
+    <row r="116" spans="1:13">
       <c r="A116" s="2"/>
       <c r="B116" s="3"/>
       <c r="F116" s="4"/>
@@ -2567,9 +2723,10 @@
       <c r="I116" s="5"/>
       <c r="J116" s="5"/>
       <c r="K116" s="5"/>
-      <c r="L116" s="6"/>
-    </row>
-    <row r="117" spans="1:12">
+      <c r="L116" s="5"/>
+      <c r="M116" s="6"/>
+    </row>
+    <row r="117" spans="1:13">
       <c r="A117" s="2"/>
       <c r="B117" s="3"/>
       <c r="F117" s="4"/>
@@ -2578,9 +2735,10 @@
       <c r="I117" s="5"/>
       <c r="J117" s="5"/>
       <c r="K117" s="5"/>
-      <c r="L117" s="6"/>
-    </row>
-    <row r="118" spans="1:12">
+      <c r="L117" s="5"/>
+      <c r="M117" s="6"/>
+    </row>
+    <row r="118" spans="1:13">
       <c r="A118" s="2"/>
       <c r="B118" s="3"/>
       <c r="F118" s="4"/>
@@ -2589,9 +2747,10 @@
       <c r="I118" s="5"/>
       <c r="J118" s="5"/>
       <c r="K118" s="5"/>
-      <c r="L118" s="6"/>
-    </row>
-    <row r="119" spans="1:12">
+      <c r="L118" s="5"/>
+      <c r="M118" s="6"/>
+    </row>
+    <row r="119" spans="1:13">
       <c r="A119" s="2"/>
       <c r="B119" s="3"/>
       <c r="F119" s="4"/>
@@ -2600,9 +2759,10 @@
       <c r="I119" s="5"/>
       <c r="J119" s="5"/>
       <c r="K119" s="5"/>
-      <c r="L119" s="6"/>
-    </row>
-    <row r="120" spans="1:12">
+      <c r="L119" s="5"/>
+      <c r="M119" s="6"/>
+    </row>
+    <row r="120" spans="1:13">
       <c r="A120" s="2"/>
       <c r="B120" s="3"/>
       <c r="F120" s="4"/>
@@ -2611,9 +2771,10 @@
       <c r="I120" s="5"/>
       <c r="J120" s="5"/>
       <c r="K120" s="5"/>
-      <c r="L120" s="6"/>
-    </row>
-    <row r="121" spans="1:12">
+      <c r="L120" s="5"/>
+      <c r="M120" s="6"/>
+    </row>
+    <row r="121" spans="1:13">
       <c r="A121" s="2"/>
       <c r="B121" s="3"/>
       <c r="F121" s="4"/>
@@ -2622,9 +2783,10 @@
       <c r="I121" s="5"/>
       <c r="J121" s="5"/>
       <c r="K121" s="5"/>
-      <c r="L121" s="6"/>
-    </row>
-    <row r="122" spans="1:12">
+      <c r="L121" s="5"/>
+      <c r="M121" s="6"/>
+    </row>
+    <row r="122" spans="1:13">
       <c r="A122" s="2"/>
       <c r="B122" s="3"/>
       <c r="F122" s="4"/>
@@ -2633,9 +2795,10 @@
       <c r="I122" s="5"/>
       <c r="J122" s="5"/>
       <c r="K122" s="5"/>
-      <c r="L122" s="6"/>
-    </row>
-    <row r="123" spans="1:12">
+      <c r="L122" s="5"/>
+      <c r="M122" s="6"/>
+    </row>
+    <row r="123" spans="1:13">
       <c r="A123" s="2"/>
       <c r="B123" s="3"/>
       <c r="F123" s="4"/>
@@ -2644,9 +2807,10 @@
       <c r="I123" s="5"/>
       <c r="J123" s="5"/>
       <c r="K123" s="5"/>
-      <c r="L123" s="6"/>
-    </row>
-    <row r="124" spans="1:12">
+      <c r="L123" s="5"/>
+      <c r="M123" s="6"/>
+    </row>
+    <row r="124" spans="1:13">
       <c r="A124" s="2"/>
       <c r="B124" s="3"/>
       <c r="F124" s="4"/>
@@ -2655,9 +2819,10 @@
       <c r="I124" s="5"/>
       <c r="J124" s="5"/>
       <c r="K124" s="5"/>
-      <c r="L124" s="6"/>
-    </row>
-    <row r="125" spans="1:12">
+      <c r="L124" s="5"/>
+      <c r="M124" s="6"/>
+    </row>
+    <row r="125" spans="1:13">
       <c r="A125" s="2"/>
       <c r="B125" s="3"/>
       <c r="F125" s="4"/>
@@ -2666,9 +2831,10 @@
       <c r="I125" s="5"/>
       <c r="J125" s="5"/>
       <c r="K125" s="5"/>
-      <c r="L125" s="6"/>
-    </row>
-    <row r="126" spans="1:12">
+      <c r="L125" s="5"/>
+      <c r="M125" s="6"/>
+    </row>
+    <row r="126" spans="1:13">
       <c r="A126" s="2"/>
       <c r="B126" s="3"/>
       <c r="F126" s="4"/>
@@ -2677,9 +2843,10 @@
       <c r="I126" s="5"/>
       <c r="J126" s="5"/>
       <c r="K126" s="5"/>
-      <c r="L126" s="6"/>
-    </row>
-    <row r="127" spans="1:12">
+      <c r="L126" s="5"/>
+      <c r="M126" s="6"/>
+    </row>
+    <row r="127" spans="1:13">
       <c r="A127" s="2"/>
       <c r="B127" s="3"/>
       <c r="F127" s="4"/>
@@ -2688,9 +2855,10 @@
       <c r="I127" s="5"/>
       <c r="J127" s="5"/>
       <c r="K127" s="5"/>
-      <c r="L127" s="6"/>
-    </row>
-    <row r="128" spans="1:12">
+      <c r="L127" s="5"/>
+      <c r="M127" s="6"/>
+    </row>
+    <row r="128" spans="1:13">
       <c r="A128" s="2"/>
       <c r="B128" s="3"/>
       <c r="F128" s="4"/>
@@ -2699,9 +2867,10 @@
       <c r="I128" s="5"/>
       <c r="J128" s="5"/>
       <c r="K128" s="5"/>
-      <c r="L128" s="6"/>
-    </row>
-    <row r="129" spans="1:12">
+      <c r="L128" s="5"/>
+      <c r="M128" s="6"/>
+    </row>
+    <row r="129" spans="1:13">
       <c r="A129" s="2"/>
       <c r="B129" s="3"/>
       <c r="F129" s="4"/>
@@ -2710,9 +2879,10 @@
       <c r="I129" s="5"/>
       <c r="J129" s="5"/>
       <c r="K129" s="5"/>
-      <c r="L129" s="6"/>
-    </row>
-    <row r="130" spans="1:12">
+      <c r="L129" s="5"/>
+      <c r="M129" s="6"/>
+    </row>
+    <row r="130" spans="1:13">
       <c r="A130" s="2"/>
       <c r="B130" s="3"/>
       <c r="F130" s="4"/>
@@ -2721,9 +2891,10 @@
       <c r="I130" s="5"/>
       <c r="J130" s="5"/>
       <c r="K130" s="5"/>
-      <c r="L130" s="6"/>
-    </row>
-    <row r="131" spans="1:12">
+      <c r="L130" s="5"/>
+      <c r="M130" s="6"/>
+    </row>
+    <row r="131" spans="1:13">
       <c r="A131" s="2"/>
       <c r="B131" s="3"/>
       <c r="F131" s="4"/>
@@ -2732,9 +2903,10 @@
       <c r="I131" s="5"/>
       <c r="J131" s="5"/>
       <c r="K131" s="5"/>
-      <c r="L131" s="6"/>
-    </row>
-    <row r="132" spans="1:12">
+      <c r="L131" s="5"/>
+      <c r="M131" s="6"/>
+    </row>
+    <row r="132" spans="1:13">
       <c r="A132" s="2"/>
       <c r="B132" s="3"/>
       <c r="F132" s="4"/>
@@ -2743,9 +2915,10 @@
       <c r="I132" s="5"/>
       <c r="J132" s="5"/>
       <c r="K132" s="5"/>
-      <c r="L132" s="6"/>
-    </row>
-    <row r="133" spans="1:12">
+      <c r="L132" s="5"/>
+      <c r="M132" s="6"/>
+    </row>
+    <row r="133" spans="1:13">
       <c r="A133" s="2"/>
       <c r="B133" s="3"/>
       <c r="F133" s="4"/>
@@ -2754,9 +2927,10 @@
       <c r="I133" s="5"/>
       <c r="J133" s="5"/>
       <c r="K133" s="5"/>
-      <c r="L133" s="6"/>
-    </row>
-    <row r="134" spans="1:12">
+      <c r="L133" s="5"/>
+      <c r="M133" s="6"/>
+    </row>
+    <row r="134" spans="1:13">
       <c r="A134" s="2"/>
       <c r="B134" s="3"/>
       <c r="F134" s="4"/>
@@ -2765,9 +2939,10 @@
       <c r="I134" s="5"/>
       <c r="J134" s="5"/>
       <c r="K134" s="5"/>
-      <c r="L134" s="6"/>
-    </row>
-    <row r="135" spans="1:12">
+      <c r="L134" s="5"/>
+      <c r="M134" s="6"/>
+    </row>
+    <row r="135" spans="1:13">
       <c r="A135" s="2"/>
       <c r="B135" s="3"/>
       <c r="F135" s="4"/>
@@ -2776,9 +2951,10 @@
       <c r="I135" s="5"/>
       <c r="J135" s="5"/>
       <c r="K135" s="5"/>
-      <c r="L135" s="6"/>
-    </row>
-    <row r="136" spans="1:12">
+      <c r="L135" s="5"/>
+      <c r="M135" s="6"/>
+    </row>
+    <row r="136" spans="1:13">
       <c r="A136" s="2"/>
       <c r="B136" s="3"/>
       <c r="F136" s="4"/>
@@ -2787,9 +2963,10 @@
       <c r="I136" s="5"/>
       <c r="J136" s="5"/>
       <c r="K136" s="5"/>
-      <c r="L136" s="6"/>
-    </row>
-    <row r="137" spans="1:12">
+      <c r="L136" s="5"/>
+      <c r="M136" s="6"/>
+    </row>
+    <row r="137" spans="1:13">
       <c r="A137" s="2"/>
       <c r="B137" s="3"/>
       <c r="F137" s="4"/>
@@ -2798,9 +2975,10 @@
       <c r="I137" s="5"/>
       <c r="J137" s="5"/>
       <c r="K137" s="5"/>
-      <c r="L137" s="6"/>
-    </row>
-    <row r="138" spans="1:12">
+      <c r="L137" s="5"/>
+      <c r="M137" s="6"/>
+    </row>
+    <row r="138" spans="1:13">
       <c r="A138" s="2"/>
       <c r="B138" s="3"/>
       <c r="F138" s="4"/>
@@ -2809,9 +2987,10 @@
       <c r="I138" s="5"/>
       <c r="J138" s="5"/>
       <c r="K138" s="5"/>
-      <c r="L138" s="6"/>
-    </row>
-    <row r="139" spans="1:12">
+      <c r="L138" s="5"/>
+      <c r="M138" s="6"/>
+    </row>
+    <row r="139" spans="1:13">
       <c r="A139" s="2"/>
       <c r="B139" s="3"/>
       <c r="F139" s="4"/>
@@ -2820,9 +2999,10 @@
       <c r="I139" s="5"/>
       <c r="J139" s="5"/>
       <c r="K139" s="5"/>
-      <c r="L139" s="6"/>
-    </row>
-    <row r="140" spans="1:12">
+      <c r="L139" s="5"/>
+      <c r="M139" s="6"/>
+    </row>
+    <row r="140" spans="1:13">
       <c r="A140" s="2"/>
       <c r="B140" s="3"/>
       <c r="F140" s="4"/>
@@ -2831,9 +3011,10 @@
       <c r="I140" s="5"/>
       <c r="J140" s="5"/>
       <c r="K140" s="5"/>
-      <c r="L140" s="6"/>
-    </row>
-    <row r="141" spans="1:12">
+      <c r="L140" s="5"/>
+      <c r="M140" s="6"/>
+    </row>
+    <row r="141" spans="1:13">
       <c r="A141" s="2"/>
       <c r="B141" s="3"/>
       <c r="F141" s="4"/>
@@ -2842,9 +3023,10 @@
       <c r="I141" s="5"/>
       <c r="J141" s="5"/>
       <c r="K141" s="5"/>
-      <c r="L141" s="6"/>
-    </row>
-    <row r="142" spans="1:12">
+      <c r="L141" s="5"/>
+      <c r="M141" s="6"/>
+    </row>
+    <row r="142" spans="1:13">
       <c r="A142" s="2"/>
       <c r="B142" s="3"/>
       <c r="F142" s="4"/>
@@ -2853,9 +3035,10 @@
       <c r="I142" s="5"/>
       <c r="J142" s="5"/>
       <c r="K142" s="5"/>
-      <c r="L142" s="6"/>
-    </row>
-    <row r="143" spans="1:12">
+      <c r="L142" s="5"/>
+      <c r="M142" s="6"/>
+    </row>
+    <row r="143" spans="1:13">
       <c r="A143" s="2"/>
       <c r="B143" s="3"/>
       <c r="F143" s="4"/>
@@ -2864,9 +3047,10 @@
       <c r="I143" s="5"/>
       <c r="J143" s="5"/>
       <c r="K143" s="5"/>
-      <c r="L143" s="6"/>
-    </row>
-    <row r="144" spans="1:12">
+      <c r="L143" s="5"/>
+      <c r="M143" s="6"/>
+    </row>
+    <row r="144" spans="1:13">
       <c r="A144" s="2"/>
       <c r="B144" s="3"/>
       <c r="F144" s="4"/>
@@ -2875,9 +3059,10 @@
       <c r="I144" s="5"/>
       <c r="J144" s="5"/>
       <c r="K144" s="5"/>
-      <c r="L144" s="6"/>
-    </row>
-    <row r="145" spans="1:12">
+      <c r="L144" s="5"/>
+      <c r="M144" s="6"/>
+    </row>
+    <row r="145" spans="1:13">
       <c r="A145" s="2"/>
       <c r="B145" s="3"/>
       <c r="F145" s="4"/>
@@ -2886,9 +3071,10 @@
       <c r="I145" s="5"/>
       <c r="J145" s="5"/>
       <c r="K145" s="5"/>
-      <c r="L145" s="6"/>
-    </row>
-    <row r="146" spans="1:12">
+      <c r="L145" s="5"/>
+      <c r="M145" s="6"/>
+    </row>
+    <row r="146" spans="1:13">
       <c r="A146" s="2"/>
       <c r="B146" s="3"/>
       <c r="F146" s="4"/>
@@ -2897,9 +3083,10 @@
       <c r="I146" s="5"/>
       <c r="J146" s="5"/>
       <c r="K146" s="5"/>
-      <c r="L146" s="6"/>
-    </row>
-    <row r="147" spans="1:12">
+      <c r="L146" s="5"/>
+      <c r="M146" s="6"/>
+    </row>
+    <row r="147" spans="1:13">
       <c r="A147" s="2"/>
       <c r="B147" s="3"/>
       <c r="F147" s="4"/>
@@ -2908,9 +3095,10 @@
       <c r="I147" s="5"/>
       <c r="J147" s="5"/>
       <c r="K147" s="5"/>
-      <c r="L147" s="6"/>
-    </row>
-    <row r="148" spans="1:12">
+      <c r="L147" s="5"/>
+      <c r="M147" s="6"/>
+    </row>
+    <row r="148" spans="1:13">
       <c r="A148" s="2"/>
       <c r="B148" s="3"/>
       <c r="F148" s="4"/>
@@ -2919,9 +3107,10 @@
       <c r="I148" s="5"/>
       <c r="J148" s="5"/>
       <c r="K148" s="5"/>
-      <c r="L148" s="6"/>
-    </row>
-    <row r="149" spans="1:12">
+      <c r="L148" s="5"/>
+      <c r="M148" s="6"/>
+    </row>
+    <row r="149" spans="1:13">
       <c r="A149" s="2"/>
       <c r="B149" s="3"/>
       <c r="F149" s="4"/>
@@ -2930,9 +3119,10 @@
       <c r="I149" s="5"/>
       <c r="J149" s="5"/>
       <c r="K149" s="5"/>
-      <c r="L149" s="6"/>
-    </row>
-    <row r="150" spans="1:12">
+      <c r="L149" s="5"/>
+      <c r="M149" s="6"/>
+    </row>
+    <row r="150" spans="1:13">
       <c r="A150" s="2"/>
       <c r="B150" s="3"/>
       <c r="F150" s="4"/>
@@ -2941,9 +3131,10 @@
       <c r="I150" s="5"/>
       <c r="J150" s="5"/>
       <c r="K150" s="5"/>
-      <c r="L150" s="6"/>
-    </row>
-    <row r="151" spans="1:12">
+      <c r="L150" s="5"/>
+      <c r="M150" s="6"/>
+    </row>
+    <row r="151" spans="1:13">
       <c r="A151" s="2"/>
       <c r="B151" s="3"/>
       <c r="F151" s="4"/>
@@ -2952,9 +3143,10 @@
       <c r="I151" s="5"/>
       <c r="J151" s="5"/>
       <c r="K151" s="5"/>
-      <c r="L151" s="6"/>
-    </row>
-    <row r="152" spans="1:12">
+      <c r="L151" s="5"/>
+      <c r="M151" s="6"/>
+    </row>
+    <row r="152" spans="1:13">
       <c r="A152" s="2"/>
       <c r="B152" s="3"/>
       <c r="F152" s="4"/>
@@ -2963,9 +3155,10 @@
       <c r="I152" s="5"/>
       <c r="J152" s="5"/>
       <c r="K152" s="5"/>
-      <c r="L152" s="6"/>
-    </row>
-    <row r="153" spans="1:12">
+      <c r="L152" s="5"/>
+      <c r="M152" s="6"/>
+    </row>
+    <row r="153" spans="1:13">
       <c r="A153" s="2"/>
       <c r="B153" s="3"/>
       <c r="F153" s="4"/>
@@ -2974,9 +3167,10 @@
       <c r="I153" s="5"/>
       <c r="J153" s="5"/>
       <c r="K153" s="5"/>
-      <c r="L153" s="6"/>
-    </row>
-    <row r="154" spans="1:12">
+      <c r="L153" s="5"/>
+      <c r="M153" s="6"/>
+    </row>
+    <row r="154" spans="1:13">
       <c r="A154" s="2"/>
       <c r="B154" s="3"/>
       <c r="F154" s="4"/>
@@ -2985,9 +3179,10 @@
       <c r="I154" s="5"/>
       <c r="J154" s="5"/>
       <c r="K154" s="5"/>
-      <c r="L154" s="6"/>
-    </row>
-    <row r="155" spans="1:12">
+      <c r="L154" s="5"/>
+      <c r="M154" s="6"/>
+    </row>
+    <row r="155" spans="1:13">
       <c r="A155" s="2"/>
       <c r="B155" s="3"/>
       <c r="F155" s="4"/>
@@ -2996,9 +3191,10 @@
       <c r="I155" s="5"/>
       <c r="J155" s="5"/>
       <c r="K155" s="5"/>
-      <c r="L155" s="6"/>
-    </row>
-    <row r="156" spans="1:12">
+      <c r="L155" s="5"/>
+      <c r="M155" s="6"/>
+    </row>
+    <row r="156" spans="1:13">
       <c r="A156" s="2"/>
       <c r="B156" s="3"/>
       <c r="F156" s="4"/>
@@ -3007,9 +3203,10 @@
       <c r="I156" s="5"/>
       <c r="J156" s="5"/>
       <c r="K156" s="5"/>
-      <c r="L156" s="6"/>
-    </row>
-    <row r="157" spans="1:12">
+      <c r="L156" s="5"/>
+      <c r="M156" s="6"/>
+    </row>
+    <row r="157" spans="1:13">
       <c r="A157" s="2"/>
       <c r="B157" s="3"/>
       <c r="F157" s="4"/>
@@ -3018,9 +3215,10 @@
       <c r="I157" s="5"/>
       <c r="J157" s="5"/>
       <c r="K157" s="5"/>
-      <c r="L157" s="6"/>
-    </row>
-    <row r="158" spans="1:12">
+      <c r="L157" s="5"/>
+      <c r="M157" s="6"/>
+    </row>
+    <row r="158" spans="1:13">
       <c r="A158" s="2"/>
       <c r="B158" s="3"/>
       <c r="F158" s="4"/>
@@ -3029,9 +3227,10 @@
       <c r="I158" s="5"/>
       <c r="J158" s="5"/>
       <c r="K158" s="5"/>
-      <c r="L158" s="6"/>
-    </row>
-    <row r="159" spans="1:12">
+      <c r="L158" s="5"/>
+      <c r="M158" s="6"/>
+    </row>
+    <row r="159" spans="1:13">
       <c r="A159" s="2"/>
       <c r="B159" s="3"/>
       <c r="F159" s="4"/>
@@ -3040,9 +3239,10 @@
       <c r="I159" s="5"/>
       <c r="J159" s="5"/>
       <c r="K159" s="5"/>
-      <c r="L159" s="6"/>
-    </row>
-    <row r="160" spans="1:12">
+      <c r="L159" s="5"/>
+      <c r="M159" s="6"/>
+    </row>
+    <row r="160" spans="1:13">
       <c r="A160" s="2"/>
       <c r="B160" s="3"/>
       <c r="F160" s="4"/>
@@ -3051,9 +3251,10 @@
       <c r="I160" s="5"/>
       <c r="J160" s="5"/>
       <c r="K160" s="5"/>
-      <c r="L160" s="6"/>
-    </row>
-    <row r="161" spans="1:12">
+      <c r="L160" s="5"/>
+      <c r="M160" s="6"/>
+    </row>
+    <row r="161" spans="1:13">
       <c r="A161" s="2"/>
       <c r="B161" s="3"/>
       <c r="F161" s="4"/>
@@ -3062,9 +3263,10 @@
       <c r="I161" s="5"/>
       <c r="J161" s="5"/>
       <c r="K161" s="5"/>
-      <c r="L161" s="6"/>
-    </row>
-    <row r="162" spans="1:12">
+      <c r="L161" s="5"/>
+      <c r="M161" s="6"/>
+    </row>
+    <row r="162" spans="1:13">
       <c r="A162" s="2"/>
       <c r="B162" s="3"/>
       <c r="F162" s="4"/>
@@ -3073,9 +3275,10 @@
       <c r="I162" s="5"/>
       <c r="J162" s="5"/>
       <c r="K162" s="5"/>
-      <c r="L162" s="6"/>
-    </row>
-    <row r="163" spans="1:12">
+      <c r="L162" s="5"/>
+      <c r="M162" s="6"/>
+    </row>
+    <row r="163" spans="1:13">
       <c r="A163" s="2"/>
       <c r="B163" s="3"/>
       <c r="F163" s="4"/>
@@ -3084,9 +3287,10 @@
       <c r="I163" s="5"/>
       <c r="J163" s="5"/>
       <c r="K163" s="5"/>
-      <c r="L163" s="6"/>
-    </row>
-    <row r="164" spans="1:12">
+      <c r="L163" s="5"/>
+      <c r="M163" s="6"/>
+    </row>
+    <row r="164" spans="1:13">
       <c r="A164" s="2"/>
       <c r="B164" s="3"/>
       <c r="F164" s="4"/>
@@ -3095,9 +3299,10 @@
       <c r="I164" s="5"/>
       <c r="J164" s="5"/>
       <c r="K164" s="5"/>
-      <c r="L164" s="6"/>
-    </row>
-    <row r="165" spans="1:12">
+      <c r="L164" s="5"/>
+      <c r="M164" s="6"/>
+    </row>
+    <row r="165" spans="1:13">
       <c r="A165" s="2"/>
       <c r="B165" s="3"/>
       <c r="F165" s="4"/>
@@ -3106,9 +3311,10 @@
       <c r="I165" s="5"/>
       <c r="J165" s="5"/>
       <c r="K165" s="5"/>
-      <c r="L165" s="6"/>
-    </row>
-    <row r="166" spans="1:12">
+      <c r="L165" s="5"/>
+      <c r="M165" s="6"/>
+    </row>
+    <row r="166" spans="1:13">
       <c r="A166" s="2"/>
       <c r="B166" s="3"/>
       <c r="F166" s="4"/>
@@ -3117,9 +3323,10 @@
       <c r="I166" s="5"/>
       <c r="J166" s="5"/>
       <c r="K166" s="5"/>
-      <c r="L166" s="6"/>
-    </row>
-    <row r="167" spans="1:12">
+      <c r="L166" s="5"/>
+      <c r="M166" s="6"/>
+    </row>
+    <row r="167" spans="1:13">
       <c r="A167" s="2"/>
       <c r="B167" s="3"/>
       <c r="F167" s="4"/>
@@ -3128,9 +3335,10 @@
       <c r="I167" s="5"/>
       <c r="J167" s="5"/>
       <c r="K167" s="5"/>
-      <c r="L167" s="6"/>
-    </row>
-    <row r="168" spans="1:12">
+      <c r="L167" s="5"/>
+      <c r="M167" s="6"/>
+    </row>
+    <row r="168" spans="1:13">
       <c r="A168" s="2"/>
       <c r="B168" s="3"/>
       <c r="F168" s="4"/>
@@ -3139,9 +3347,10 @@
       <c r="I168" s="5"/>
       <c r="J168" s="5"/>
       <c r="K168" s="5"/>
-      <c r="L168" s="6"/>
-    </row>
-    <row r="169" spans="1:12">
+      <c r="L168" s="5"/>
+      <c r="M168" s="6"/>
+    </row>
+    <row r="169" spans="1:13">
       <c r="A169" s="2"/>
       <c r="B169" s="3"/>
       <c r="F169" s="4"/>
@@ -3150,9 +3359,10 @@
       <c r="I169" s="5"/>
       <c r="J169" s="5"/>
       <c r="K169" s="5"/>
-      <c r="L169" s="6"/>
-    </row>
-    <row r="170" spans="1:12">
+      <c r="L169" s="5"/>
+      <c r="M169" s="6"/>
+    </row>
+    <row r="170" spans="1:13">
       <c r="A170" s="2"/>
       <c r="B170" s="3"/>
       <c r="F170" s="4"/>
@@ -3161,9 +3371,10 @@
       <c r="I170" s="5"/>
       <c r="J170" s="5"/>
       <c r="K170" s="5"/>
-      <c r="L170" s="6"/>
-    </row>
-    <row r="171" spans="1:12">
+      <c r="L170" s="5"/>
+      <c r="M170" s="6"/>
+    </row>
+    <row r="171" spans="1:13">
       <c r="A171" s="2"/>
       <c r="B171" s="3"/>
       <c r="F171" s="4"/>
@@ -3172,9 +3383,10 @@
       <c r="I171" s="5"/>
       <c r="J171" s="5"/>
       <c r="K171" s="5"/>
-      <c r="L171" s="6"/>
-    </row>
-    <row r="172" spans="1:12">
+      <c r="L171" s="5"/>
+      <c r="M171" s="6"/>
+    </row>
+    <row r="172" spans="1:13">
       <c r="A172" s="2"/>
       <c r="B172" s="3"/>
       <c r="F172" s="4"/>
@@ -3183,9 +3395,10 @@
       <c r="I172" s="5"/>
       <c r="J172" s="5"/>
       <c r="K172" s="5"/>
-      <c r="L172" s="6"/>
-    </row>
-    <row r="173" spans="1:12">
+      <c r="L172" s="5"/>
+      <c r="M172" s="6"/>
+    </row>
+    <row r="173" spans="1:13">
       <c r="A173" s="2"/>
       <c r="B173" s="3"/>
       <c r="F173" s="4"/>
@@ -3194,9 +3407,10 @@
       <c r="I173" s="5"/>
       <c r="J173" s="5"/>
       <c r="K173" s="5"/>
-      <c r="L173" s="6"/>
-    </row>
-    <row r="174" spans="1:12">
+      <c r="L173" s="5"/>
+      <c r="M173" s="6"/>
+    </row>
+    <row r="174" spans="1:13">
       <c r="A174" s="2"/>
       <c r="B174" s="3"/>
       <c r="F174" s="4"/>
@@ -3205,9 +3419,10 @@
       <c r="I174" s="5"/>
       <c r="J174" s="5"/>
       <c r="K174" s="5"/>
-      <c r="L174" s="6"/>
-    </row>
-    <row r="175" spans="1:12">
+      <c r="L174" s="5"/>
+      <c r="M174" s="6"/>
+    </row>
+    <row r="175" spans="1:13">
       <c r="A175" s="2"/>
       <c r="B175" s="3"/>
       <c r="F175" s="4"/>
@@ -3216,9 +3431,10 @@
       <c r="I175" s="5"/>
       <c r="J175" s="5"/>
       <c r="K175" s="5"/>
-      <c r="L175" s="6"/>
-    </row>
-    <row r="176" spans="1:12">
+      <c r="L175" s="5"/>
+      <c r="M175" s="6"/>
+    </row>
+    <row r="176" spans="1:13">
       <c r="A176" s="2"/>
       <c r="B176" s="3"/>
       <c r="F176" s="4"/>
@@ -3227,9 +3443,10 @@
       <c r="I176" s="5"/>
       <c r="J176" s="5"/>
       <c r="K176" s="5"/>
-      <c r="L176" s="6"/>
-    </row>
-    <row r="177" spans="1:12">
+      <c r="L176" s="5"/>
+      <c r="M176" s="6"/>
+    </row>
+    <row r="177" spans="1:13">
       <c r="A177" s="2"/>
       <c r="B177" s="3"/>
       <c r="F177" s="4"/>
@@ -3238,9 +3455,10 @@
       <c r="I177" s="5"/>
       <c r="J177" s="5"/>
       <c r="K177" s="5"/>
-      <c r="L177" s="6"/>
-    </row>
-    <row r="178" spans="1:12">
+      <c r="L177" s="5"/>
+      <c r="M177" s="6"/>
+    </row>
+    <row r="178" spans="1:13">
       <c r="A178" s="2"/>
       <c r="B178" s="3"/>
       <c r="F178" s="4"/>
@@ -3249,9 +3467,10 @@
       <c r="I178" s="5"/>
       <c r="J178" s="5"/>
       <c r="K178" s="5"/>
-      <c r="L178" s="6"/>
-    </row>
-    <row r="179" spans="1:12">
+      <c r="L178" s="5"/>
+      <c r="M178" s="6"/>
+    </row>
+    <row r="179" spans="1:13">
       <c r="A179" s="2"/>
       <c r="B179" s="3"/>
       <c r="F179" s="4"/>
@@ -3260,9 +3479,10 @@
       <c r="I179" s="5"/>
       <c r="J179" s="5"/>
       <c r="K179" s="5"/>
-      <c r="L179" s="6"/>
-    </row>
-    <row r="180" spans="1:12">
+      <c r="L179" s="5"/>
+      <c r="M179" s="6"/>
+    </row>
+    <row r="180" spans="1:13">
       <c r="A180" s="2"/>
       <c r="B180" s="3"/>
       <c r="F180" s="4"/>
@@ -3271,9 +3491,10 @@
       <c r="I180" s="5"/>
       <c r="J180" s="5"/>
       <c r="K180" s="5"/>
-      <c r="L180" s="6"/>
-    </row>
-    <row r="181" spans="1:12">
+      <c r="L180" s="5"/>
+      <c r="M180" s="6"/>
+    </row>
+    <row r="181" spans="1:13">
       <c r="A181" s="2"/>
       <c r="B181" s="3"/>
       <c r="F181" s="4"/>
@@ -3282,9 +3503,10 @@
       <c r="I181" s="5"/>
       <c r="J181" s="5"/>
       <c r="K181" s="5"/>
-      <c r="L181" s="6"/>
-    </row>
-    <row r="182" spans="1:12">
+      <c r="L181" s="5"/>
+      <c r="M181" s="6"/>
+    </row>
+    <row r="182" spans="1:13">
       <c r="A182" s="2"/>
       <c r="B182" s="3"/>
       <c r="F182" s="4"/>
@@ -3293,9 +3515,10 @@
       <c r="I182" s="5"/>
       <c r="J182" s="5"/>
       <c r="K182" s="5"/>
-      <c r="L182" s="6"/>
-    </row>
-    <row r="183" spans="1:12">
+      <c r="L182" s="5"/>
+      <c r="M182" s="6"/>
+    </row>
+    <row r="183" spans="1:13">
       <c r="A183" s="2"/>
       <c r="B183" s="3"/>
       <c r="F183" s="4"/>
@@ -3304,9 +3527,10 @@
       <c r="I183" s="5"/>
       <c r="J183" s="5"/>
       <c r="K183" s="5"/>
-      <c r="L183" s="6"/>
-    </row>
-    <row r="184" spans="1:12">
+      <c r="L183" s="5"/>
+      <c r="M183" s="6"/>
+    </row>
+    <row r="184" spans="1:13">
       <c r="A184" s="2"/>
       <c r="B184" s="3"/>
       <c r="F184" s="4"/>
@@ -3315,9 +3539,10 @@
       <c r="I184" s="5"/>
       <c r="J184" s="5"/>
       <c r="K184" s="5"/>
-      <c r="L184" s="6"/>
-    </row>
-    <row r="185" spans="1:12">
+      <c r="L184" s="5"/>
+      <c r="M184" s="6"/>
+    </row>
+    <row r="185" spans="1:13">
       <c r="A185" s="2"/>
       <c r="B185" s="3"/>
       <c r="F185" s="4"/>
@@ -3326,9 +3551,10 @@
       <c r="I185" s="5"/>
       <c r="J185" s="5"/>
       <c r="K185" s="5"/>
-      <c r="L185" s="6"/>
-    </row>
-    <row r="186" spans="1:12">
+      <c r="L185" s="5"/>
+      <c r="M185" s="6"/>
+    </row>
+    <row r="186" spans="1:13">
       <c r="A186" s="2"/>
       <c r="B186" s="3"/>
       <c r="F186" s="4"/>
@@ -3337,9 +3563,10 @@
       <c r="I186" s="5"/>
       <c r="J186" s="5"/>
       <c r="K186" s="5"/>
-      <c r="L186" s="6"/>
-    </row>
-    <row r="187" spans="1:12">
+      <c r="L186" s="5"/>
+      <c r="M186" s="6"/>
+    </row>
+    <row r="187" spans="1:13">
       <c r="A187" s="2"/>
       <c r="B187" s="3"/>
       <c r="F187" s="4"/>
@@ -3348,9 +3575,10 @@
       <c r="I187" s="5"/>
       <c r="J187" s="5"/>
       <c r="K187" s="5"/>
-      <c r="L187" s="6"/>
-    </row>
-    <row r="188" spans="1:12">
+      <c r="L187" s="5"/>
+      <c r="M187" s="6"/>
+    </row>
+    <row r="188" spans="1:13">
       <c r="A188" s="2"/>
       <c r="B188" s="3"/>
       <c r="F188" s="4"/>
@@ -3359,9 +3587,10 @@
       <c r="I188" s="5"/>
       <c r="J188" s="5"/>
       <c r="K188" s="5"/>
-      <c r="L188" s="6"/>
-    </row>
-    <row r="189" spans="1:12">
+      <c r="L188" s="5"/>
+      <c r="M188" s="6"/>
+    </row>
+    <row r="189" spans="1:13">
       <c r="A189" s="2"/>
       <c r="B189" s="3"/>
       <c r="F189" s="4"/>
@@ -3370,9 +3599,10 @@
       <c r="I189" s="5"/>
       <c r="J189" s="5"/>
       <c r="K189" s="5"/>
-      <c r="L189" s="6"/>
-    </row>
-    <row r="190" spans="1:12">
+      <c r="L189" s="5"/>
+      <c r="M189" s="6"/>
+    </row>
+    <row r="190" spans="1:13">
       <c r="A190" s="2"/>
       <c r="B190" s="3"/>
       <c r="F190" s="4"/>
@@ -3381,9 +3611,10 @@
       <c r="I190" s="5"/>
       <c r="J190" s="5"/>
       <c r="K190" s="5"/>
-      <c r="L190" s="6"/>
-    </row>
-    <row r="191" spans="1:12">
+      <c r="L190" s="5"/>
+      <c r="M190" s="6"/>
+    </row>
+    <row r="191" spans="1:13">
       <c r="A191" s="2"/>
       <c r="B191" s="3"/>
       <c r="F191" s="4"/>
@@ -3392,9 +3623,10 @@
       <c r="I191" s="5"/>
       <c r="J191" s="5"/>
       <c r="K191" s="5"/>
-      <c r="L191" s="6"/>
-    </row>
-    <row r="192" spans="1:12">
+      <c r="L191" s="5"/>
+      <c r="M191" s="6"/>
+    </row>
+    <row r="192" spans="1:13">
       <c r="A192" s="2"/>
       <c r="B192" s="3"/>
       <c r="F192" s="4"/>
@@ -3403,9 +3635,10 @@
       <c r="I192" s="5"/>
       <c r="J192" s="5"/>
       <c r="K192" s="5"/>
-      <c r="L192" s="6"/>
-    </row>
-    <row r="193" spans="1:12">
+      <c r="L192" s="5"/>
+      <c r="M192" s="6"/>
+    </row>
+    <row r="193" spans="1:13">
       <c r="A193" s="2"/>
       <c r="B193" s="3"/>
       <c r="F193" s="4"/>
@@ -3414,9 +3647,10 @@
       <c r="I193" s="5"/>
       <c r="J193" s="5"/>
       <c r="K193" s="5"/>
-      <c r="L193" s="6"/>
-    </row>
-    <row r="194" spans="1:12">
+      <c r="L193" s="5"/>
+      <c r="M193" s="6"/>
+    </row>
+    <row r="194" spans="1:13">
       <c r="A194" s="2"/>
       <c r="B194" s="3"/>
       <c r="F194" s="4"/>
@@ -3425,9 +3659,10 @@
       <c r="I194" s="5"/>
       <c r="J194" s="5"/>
       <c r="K194" s="5"/>
-      <c r="L194" s="6"/>
-    </row>
-    <row r="195" spans="1:12">
+      <c r="L194" s="5"/>
+      <c r="M194" s="6"/>
+    </row>
+    <row r="195" spans="1:13">
       <c r="A195" s="2"/>
       <c r="B195" s="3"/>
       <c r="F195" s="4"/>
@@ -3436,9 +3671,10 @@
       <c r="I195" s="5"/>
       <c r="J195" s="5"/>
       <c r="K195" s="5"/>
-      <c r="L195" s="6"/>
-    </row>
-    <row r="196" spans="1:12">
+      <c r="L195" s="5"/>
+      <c r="M195" s="6"/>
+    </row>
+    <row r="196" spans="1:13">
       <c r="A196" s="2"/>
       <c r="B196" s="3"/>
       <c r="F196" s="4"/>
@@ -3447,9 +3683,10 @@
       <c r="I196" s="5"/>
       <c r="J196" s="5"/>
       <c r="K196" s="5"/>
-      <c r="L196" s="6"/>
-    </row>
-    <row r="197" spans="1:12">
+      <c r="L196" s="5"/>
+      <c r="M196" s="6"/>
+    </row>
+    <row r="197" spans="1:13">
       <c r="A197" s="2"/>
       <c r="B197" s="3"/>
       <c r="F197" s="4"/>
@@ -3458,9 +3695,10 @@
       <c r="I197" s="5"/>
       <c r="J197" s="5"/>
       <c r="K197" s="5"/>
-      <c r="L197" s="6"/>
-    </row>
-    <row r="198" spans="1:12">
+      <c r="L197" s="5"/>
+      <c r="M197" s="6"/>
+    </row>
+    <row r="198" spans="1:13">
       <c r="A198" s="2"/>
       <c r="B198" s="3"/>
       <c r="F198" s="4"/>
@@ -3469,9 +3707,10 @@
       <c r="I198" s="5"/>
       <c r="J198" s="5"/>
       <c r="K198" s="5"/>
-      <c r="L198" s="6"/>
-    </row>
-    <row r="199" spans="1:12">
+      <c r="L198" s="5"/>
+      <c r="M198" s="6"/>
+    </row>
+    <row r="199" spans="1:13">
       <c r="A199" s="2"/>
       <c r="B199" s="3"/>
       <c r="F199" s="4"/>
@@ -3480,9 +3719,10 @@
       <c r="I199" s="5"/>
       <c r="J199" s="5"/>
       <c r="K199" s="5"/>
-      <c r="L199" s="6"/>
-    </row>
-    <row r="200" spans="1:12">
+      <c r="L199" s="5"/>
+      <c r="M199" s="6"/>
+    </row>
+    <row r="200" spans="1:13">
       <c r="A200" s="2"/>
       <c r="B200" s="3"/>
       <c r="F200" s="4"/>
@@ -3491,9 +3731,10 @@
       <c r="I200" s="5"/>
       <c r="J200" s="5"/>
       <c r="K200" s="5"/>
-      <c r="L200" s="6"/>
-    </row>
-    <row r="201" spans="1:12">
+      <c r="L200" s="5"/>
+      <c r="M200" s="6"/>
+    </row>
+    <row r="201" spans="1:13">
       <c r="A201" s="2"/>
       <c r="B201" s="3"/>
       <c r="F201" s="4"/>
@@ -3502,9 +3743,10 @@
       <c r="I201" s="5"/>
       <c r="J201" s="5"/>
       <c r="K201" s="5"/>
-      <c r="L201" s="6"/>
-    </row>
-    <row r="202" spans="1:12">
+      <c r="L201" s="5"/>
+      <c r="M201" s="6"/>
+    </row>
+    <row r="202" spans="1:13">
       <c r="A202" s="2"/>
       <c r="B202" s="3"/>
       <c r="F202" s="4"/>
@@ -3513,9 +3755,10 @@
       <c r="I202" s="5"/>
       <c r="J202" s="5"/>
       <c r="K202" s="5"/>
-      <c r="L202" s="6"/>
-    </row>
-    <row r="203" spans="1:12">
+      <c r="L202" s="5"/>
+      <c r="M202" s="6"/>
+    </row>
+    <row r="203" spans="1:13">
       <c r="A203" s="2"/>
       <c r="B203" s="3"/>
       <c r="F203" s="4"/>
@@ -3524,9 +3767,10 @@
       <c r="I203" s="5"/>
       <c r="J203" s="5"/>
       <c r="K203" s="5"/>
-      <c r="L203" s="6"/>
-    </row>
-    <row r="204" spans="1:12">
+      <c r="L203" s="5"/>
+      <c r="M203" s="6"/>
+    </row>
+    <row r="204" spans="1:13">
       <c r="A204" s="2"/>
       <c r="B204" s="3"/>
       <c r="F204" s="4"/>
@@ -3535,9 +3779,10 @@
       <c r="I204" s="5"/>
       <c r="J204" s="5"/>
       <c r="K204" s="5"/>
-      <c r="L204" s="6"/>
-    </row>
-    <row r="205" spans="1:12">
+      <c r="L204" s="5"/>
+      <c r="M204" s="6"/>
+    </row>
+    <row r="205" spans="1:13">
       <c r="A205" s="2"/>
       <c r="B205" s="3"/>
       <c r="F205" s="4"/>
@@ -3546,9 +3791,10 @@
       <c r="I205" s="5"/>
       <c r="J205" s="5"/>
       <c r="K205" s="5"/>
-      <c r="L205" s="6"/>
-    </row>
-    <row r="206" spans="1:12">
+      <c r="L205" s="5"/>
+      <c r="M205" s="6"/>
+    </row>
+    <row r="206" spans="1:13">
       <c r="A206" s="2"/>
       <c r="B206" s="3"/>
       <c r="F206" s="4"/>
@@ -3557,9 +3803,10 @@
       <c r="I206" s="5"/>
       <c r="J206" s="5"/>
       <c r="K206" s="5"/>
-      <c r="L206" s="6"/>
-    </row>
-    <row r="207" spans="1:12">
+      <c r="L206" s="5"/>
+      <c r="M206" s="6"/>
+    </row>
+    <row r="207" spans="1:13">
       <c r="A207" s="2"/>
       <c r="B207" s="3"/>
       <c r="F207" s="4"/>
@@ -3568,9 +3815,10 @@
       <c r="I207" s="5"/>
       <c r="J207" s="5"/>
       <c r="K207" s="5"/>
-      <c r="L207" s="6"/>
-    </row>
-    <row r="208" spans="1:12">
+      <c r="L207" s="5"/>
+      <c r="M207" s="6"/>
+    </row>
+    <row r="208" spans="1:13">
       <c r="A208" s="2"/>
       <c r="B208" s="3"/>
       <c r="F208" s="4"/>
@@ -3579,9 +3827,10 @@
       <c r="I208" s="5"/>
       <c r="J208" s="5"/>
       <c r="K208" s="5"/>
-      <c r="L208" s="6"/>
-    </row>
-    <row r="209" spans="1:12">
+      <c r="L208" s="5"/>
+      <c r="M208" s="6"/>
+    </row>
+    <row r="209" spans="1:13">
       <c r="A209" s="2"/>
       <c r="B209" s="3"/>
       <c r="F209" s="4"/>
@@ -3590,9 +3839,10 @@
       <c r="I209" s="5"/>
       <c r="J209" s="5"/>
       <c r="K209" s="5"/>
-      <c r="L209" s="6"/>
-    </row>
-    <row r="210" spans="1:12">
+      <c r="L209" s="5"/>
+      <c r="M209" s="6"/>
+    </row>
+    <row r="210" spans="1:13">
       <c r="A210" s="2"/>
       <c r="B210" s="3"/>
       <c r="F210" s="4"/>
@@ -3601,9 +3851,10 @@
       <c r="I210" s="5"/>
       <c r="J210" s="5"/>
       <c r="K210" s="5"/>
-      <c r="L210" s="6"/>
-    </row>
-    <row r="211" spans="1:12">
+      <c r="L210" s="5"/>
+      <c r="M210" s="6"/>
+    </row>
+    <row r="211" spans="1:13">
       <c r="A211" s="2"/>
       <c r="B211" s="3"/>
       <c r="F211" s="4"/>
@@ -3612,9 +3863,10 @@
       <c r="I211" s="5"/>
       <c r="J211" s="5"/>
       <c r="K211" s="5"/>
-      <c r="L211" s="6"/>
-    </row>
-    <row r="212" spans="1:12">
+      <c r="L211" s="5"/>
+      <c r="M211" s="6"/>
+    </row>
+    <row r="212" spans="1:13">
       <c r="A212" s="2"/>
       <c r="B212" s="3"/>
       <c r="F212" s="4"/>
@@ -3623,9 +3875,10 @@
       <c r="I212" s="5"/>
       <c r="J212" s="5"/>
       <c r="K212" s="5"/>
-      <c r="L212" s="6"/>
-    </row>
-    <row r="213" spans="1:12">
+      <c r="L212" s="5"/>
+      <c r="M212" s="6"/>
+    </row>
+    <row r="213" spans="1:13">
       <c r="A213" s="2"/>
       <c r="B213" s="3"/>
       <c r="F213" s="4"/>
@@ -3634,9 +3887,10 @@
       <c r="I213" s="5"/>
       <c r="J213" s="5"/>
       <c r="K213" s="5"/>
-      <c r="L213" s="6"/>
-    </row>
-    <row r="214" spans="1:12">
+      <c r="L213" s="5"/>
+      <c r="M213" s="6"/>
+    </row>
+    <row r="214" spans="1:13">
       <c r="A214" s="2"/>
       <c r="B214" s="3"/>
       <c r="F214" s="4"/>
@@ -3645,9 +3899,10 @@
       <c r="I214" s="5"/>
       <c r="J214" s="5"/>
       <c r="K214" s="5"/>
-      <c r="L214" s="6"/>
-    </row>
-    <row r="215" spans="1:12">
+      <c r="L214" s="5"/>
+      <c r="M214" s="6"/>
+    </row>
+    <row r="215" spans="1:13">
       <c r="A215" s="2"/>
       <c r="B215" s="3"/>
       <c r="F215" s="4"/>
@@ -3656,9 +3911,10 @@
       <c r="I215" s="5"/>
       <c r="J215" s="5"/>
       <c r="K215" s="5"/>
-      <c r="L215" s="6"/>
-    </row>
-    <row r="216" spans="1:12">
+      <c r="L215" s="5"/>
+      <c r="M215" s="6"/>
+    </row>
+    <row r="216" spans="1:13">
       <c r="A216" s="2"/>
       <c r="B216" s="3"/>
       <c r="F216" s="4"/>
@@ -3667,9 +3923,10 @@
       <c r="I216" s="5"/>
       <c r="J216" s="5"/>
       <c r="K216" s="5"/>
-      <c r="L216" s="6"/>
-    </row>
-    <row r="217" spans="1:12">
+      <c r="L216" s="5"/>
+      <c r="M216" s="6"/>
+    </row>
+    <row r="217" spans="1:13">
       <c r="A217" s="2"/>
       <c r="B217" s="3"/>
       <c r="F217" s="4"/>
@@ -3678,9 +3935,10 @@
       <c r="I217" s="5"/>
       <c r="J217" s="5"/>
       <c r="K217" s="5"/>
-      <c r="L217" s="6"/>
-    </row>
-    <row r="218" spans="1:12">
+      <c r="L217" s="5"/>
+      <c r="M217" s="6"/>
+    </row>
+    <row r="218" spans="1:13">
       <c r="A218" s="2"/>
       <c r="B218" s="3"/>
       <c r="F218" s="4"/>
@@ -3689,9 +3947,10 @@
       <c r="I218" s="5"/>
       <c r="J218" s="5"/>
       <c r="K218" s="5"/>
-      <c r="L218" s="6"/>
-    </row>
-    <row r="219" spans="1:12">
+      <c r="L218" s="5"/>
+      <c r="M218" s="6"/>
+    </row>
+    <row r="219" spans="1:13">
       <c r="A219" s="2"/>
       <c r="B219" s="3"/>
       <c r="F219" s="4"/>
@@ -3700,9 +3959,10 @@
       <c r="I219" s="5"/>
       <c r="J219" s="5"/>
       <c r="K219" s="5"/>
-      <c r="L219" s="6"/>
-    </row>
-    <row r="220" spans="1:12">
+      <c r="L219" s="5"/>
+      <c r="M219" s="6"/>
+    </row>
+    <row r="220" spans="1:13">
       <c r="A220" s="2"/>
       <c r="B220" s="3"/>
       <c r="F220" s="4"/>
@@ -3711,9 +3971,10 @@
       <c r="I220" s="5"/>
       <c r="J220" s="5"/>
       <c r="K220" s="5"/>
-      <c r="L220" s="6"/>
-    </row>
-    <row r="221" spans="1:12">
+      <c r="L220" s="5"/>
+      <c r="M220" s="6"/>
+    </row>
+    <row r="221" spans="1:13">
       <c r="A221" s="2"/>
       <c r="B221" s="3"/>
       <c r="F221" s="4"/>
@@ -3722,9 +3983,10 @@
       <c r="I221" s="5"/>
       <c r="J221" s="5"/>
       <c r="K221" s="5"/>
-      <c r="L221" s="6"/>
-    </row>
-    <row r="222" spans="1:12">
+      <c r="L221" s="5"/>
+      <c r="M221" s="6"/>
+    </row>
+    <row r="222" spans="1:13">
       <c r="A222" s="2"/>
       <c r="B222" s="3"/>
       <c r="F222" s="4"/>
@@ -3733,9 +3995,10 @@
       <c r="I222" s="5"/>
       <c r="J222" s="5"/>
       <c r="K222" s="5"/>
-      <c r="L222" s="6"/>
-    </row>
-    <row r="223" spans="1:12">
+      <c r="L222" s="5"/>
+      <c r="M222" s="6"/>
+    </row>
+    <row r="223" spans="1:13">
       <c r="A223" s="2"/>
       <c r="B223" s="3"/>
       <c r="F223" s="4"/>
@@ -3744,9 +4007,10 @@
       <c r="I223" s="5"/>
       <c r="J223" s="5"/>
       <c r="K223" s="5"/>
-      <c r="L223" s="6"/>
-    </row>
-    <row r="224" spans="1:12">
+      <c r="L223" s="5"/>
+      <c r="M223" s="6"/>
+    </row>
+    <row r="224" spans="1:13">
       <c r="A224" s="2"/>
       <c r="B224" s="3"/>
       <c r="F224" s="4"/>
@@ -3755,9 +4019,10 @@
       <c r="I224" s="5"/>
       <c r="J224" s="5"/>
       <c r="K224" s="5"/>
-      <c r="L224" s="6"/>
-    </row>
-    <row r="225" spans="1:12">
+      <c r="L224" s="5"/>
+      <c r="M224" s="6"/>
+    </row>
+    <row r="225" spans="1:13">
       <c r="A225" s="2"/>
       <c r="B225" s="3"/>
       <c r="F225" s="4"/>
@@ -3766,9 +4031,10 @@
       <c r="I225" s="5"/>
       <c r="J225" s="5"/>
       <c r="K225" s="5"/>
-      <c r="L225" s="6"/>
-    </row>
-    <row r="226" spans="1:12">
+      <c r="L225" s="5"/>
+      <c r="M225" s="6"/>
+    </row>
+    <row r="226" spans="1:13">
       <c r="A226" s="2"/>
       <c r="B226" s="3"/>
       <c r="F226" s="4"/>
@@ -3777,9 +4043,10 @@
       <c r="I226" s="5"/>
       <c r="J226" s="5"/>
       <c r="K226" s="5"/>
-      <c r="L226" s="6"/>
-    </row>
-    <row r="227" spans="1:12">
+      <c r="L226" s="5"/>
+      <c r="M226" s="6"/>
+    </row>
+    <row r="227" spans="1:13">
       <c r="A227" s="2"/>
       <c r="B227" s="3"/>
       <c r="F227" s="4"/>
@@ -3788,9 +4055,10 @@
       <c r="I227" s="5"/>
       <c r="J227" s="5"/>
       <c r="K227" s="5"/>
-      <c r="L227" s="6"/>
-    </row>
-    <row r="228" spans="1:12">
+      <c r="L227" s="5"/>
+      <c r="M227" s="6"/>
+    </row>
+    <row r="228" spans="1:13">
       <c r="A228" s="2"/>
       <c r="B228" s="3"/>
       <c r="F228" s="4"/>
@@ -3799,9 +4067,10 @@
       <c r="I228" s="5"/>
       <c r="J228" s="5"/>
       <c r="K228" s="5"/>
-      <c r="L228" s="6"/>
-    </row>
-    <row r="229" spans="1:12">
+      <c r="L228" s="5"/>
+      <c r="M228" s="6"/>
+    </row>
+    <row r="229" spans="1:13">
       <c r="A229" s="2"/>
       <c r="B229" s="3"/>
       <c r="F229" s="4"/>
@@ -3810,9 +4079,10 @@
       <c r="I229" s="5"/>
       <c r="J229" s="5"/>
       <c r="K229" s="5"/>
-      <c r="L229" s="6"/>
-    </row>
-    <row r="230" spans="1:12">
+      <c r="L229" s="5"/>
+      <c r="M229" s="6"/>
+    </row>
+    <row r="230" spans="1:13">
       <c r="A230" s="2"/>
       <c r="B230" s="3"/>
       <c r="F230" s="4"/>
@@ -3821,9 +4091,10 @@
       <c r="I230" s="5"/>
       <c r="J230" s="5"/>
       <c r="K230" s="5"/>
-      <c r="L230" s="6"/>
-    </row>
-    <row r="231" spans="1:12">
+      <c r="L230" s="5"/>
+      <c r="M230" s="6"/>
+    </row>
+    <row r="231" spans="1:13">
       <c r="A231" s="2"/>
       <c r="B231" s="3"/>
       <c r="F231" s="4"/>
@@ -3832,9 +4103,10 @@
       <c r="I231" s="5"/>
       <c r="J231" s="5"/>
       <c r="K231" s="5"/>
-      <c r="L231" s="6"/>
-    </row>
-    <row r="232" spans="1:12">
+      <c r="L231" s="5"/>
+      <c r="M231" s="6"/>
+    </row>
+    <row r="232" spans="1:13">
       <c r="A232" s="2"/>
       <c r="B232" s="3"/>
       <c r="F232" s="4"/>
@@ -3843,9 +4115,10 @@
       <c r="I232" s="5"/>
       <c r="J232" s="5"/>
       <c r="K232" s="5"/>
-      <c r="L232" s="6"/>
-    </row>
-    <row r="233" spans="1:12">
+      <c r="L232" s="5"/>
+      <c r="M232" s="6"/>
+    </row>
+    <row r="233" spans="1:13">
       <c r="A233" s="2"/>
       <c r="B233" s="3"/>
       <c r="F233" s="4"/>
@@ -3854,9 +4127,10 @@
       <c r="I233" s="5"/>
       <c r="J233" s="5"/>
       <c r="K233" s="5"/>
-      <c r="L233" s="6"/>
-    </row>
-    <row r="234" spans="1:12">
+      <c r="L233" s="5"/>
+      <c r="M233" s="6"/>
+    </row>
+    <row r="234" spans="1:13">
       <c r="A234" s="2"/>
       <c r="B234" s="3"/>
       <c r="F234" s="4"/>
@@ -3865,9 +4139,10 @@
       <c r="I234" s="5"/>
       <c r="J234" s="5"/>
       <c r="K234" s="5"/>
-      <c r="L234" s="6"/>
-    </row>
-    <row r="235" spans="1:12">
+      <c r="L234" s="5"/>
+      <c r="M234" s="6"/>
+    </row>
+    <row r="235" spans="1:13">
       <c r="A235" s="2"/>
       <c r="B235" s="3"/>
       <c r="F235" s="4"/>
@@ -3876,9 +4151,10 @@
       <c r="I235" s="5"/>
       <c r="J235" s="5"/>
       <c r="K235" s="5"/>
-      <c r="L235" s="6"/>
-    </row>
-    <row r="236" spans="1:12">
+      <c r="L235" s="5"/>
+      <c r="M235" s="6"/>
+    </row>
+    <row r="236" spans="1:13">
       <c r="A236" s="2"/>
       <c r="B236" s="3"/>
       <c r="F236" s="4"/>
@@ -3887,9 +4163,10 @@
       <c r="I236" s="5"/>
       <c r="J236" s="5"/>
       <c r="K236" s="5"/>
-      <c r="L236" s="6"/>
-    </row>
-    <row r="237" spans="1:12">
+      <c r="L236" s="5"/>
+      <c r="M236" s="6"/>
+    </row>
+    <row r="237" spans="1:13">
       <c r="A237" s="2"/>
       <c r="B237" s="3"/>
       <c r="F237" s="4"/>
@@ -3898,9 +4175,10 @@
       <c r="I237" s="5"/>
       <c r="J237" s="5"/>
       <c r="K237" s="5"/>
-      <c r="L237" s="6"/>
-    </row>
-    <row r="238" spans="1:12">
+      <c r="L237" s="5"/>
+      <c r="M237" s="6"/>
+    </row>
+    <row r="238" spans="1:13">
       <c r="A238" s="2"/>
       <c r="B238" s="3"/>
       <c r="F238" s="4"/>
@@ -3909,9 +4187,10 @@
       <c r="I238" s="5"/>
       <c r="J238" s="5"/>
       <c r="K238" s="5"/>
-      <c r="L238" s="6"/>
-    </row>
-    <row r="239" spans="1:12">
+      <c r="L238" s="5"/>
+      <c r="M238" s="6"/>
+    </row>
+    <row r="239" spans="1:13">
       <c r="A239" s="2"/>
       <c r="B239" s="3"/>
       <c r="F239" s="4"/>
@@ -3920,9 +4199,10 @@
       <c r="I239" s="5"/>
       <c r="J239" s="5"/>
       <c r="K239" s="5"/>
-      <c r="L239" s="6"/>
-    </row>
-    <row r="240" spans="1:12">
+      <c r="L239" s="5"/>
+      <c r="M239" s="6"/>
+    </row>
+    <row r="240" spans="1:13">
       <c r="A240" s="2"/>
       <c r="B240" s="3"/>
       <c r="F240" s="4"/>
@@ -3931,9 +4211,10 @@
       <c r="I240" s="5"/>
       <c r="J240" s="5"/>
       <c r="K240" s="5"/>
-      <c r="L240" s="6"/>
-    </row>
-    <row r="241" spans="1:12">
+      <c r="L240" s="5"/>
+      <c r="M240" s="6"/>
+    </row>
+    <row r="241" spans="1:13">
       <c r="A241" s="2"/>
       <c r="B241" s="3"/>
       <c r="F241" s="4"/>
@@ -3942,9 +4223,10 @@
       <c r="I241" s="5"/>
       <c r="J241" s="5"/>
       <c r="K241" s="5"/>
-      <c r="L241" s="6"/>
-    </row>
-    <row r="242" spans="1:12">
+      <c r="L241" s="5"/>
+      <c r="M241" s="6"/>
+    </row>
+    <row r="242" spans="1:13">
       <c r="A242" s="2"/>
       <c r="B242" s="3"/>
       <c r="F242" s="4"/>
@@ -3953,9 +4235,10 @@
       <c r="I242" s="5"/>
       <c r="J242" s="5"/>
       <c r="K242" s="5"/>
-      <c r="L242" s="6"/>
-    </row>
-    <row r="243" spans="1:12">
+      <c r="L242" s="5"/>
+      <c r="M242" s="6"/>
+    </row>
+    <row r="243" spans="1:13">
       <c r="A243" s="2"/>
       <c r="B243" s="3"/>
       <c r="F243" s="4"/>
@@ -3964,9 +4247,10 @@
       <c r="I243" s="5"/>
       <c r="J243" s="5"/>
       <c r="K243" s="5"/>
-      <c r="L243" s="6"/>
-    </row>
-    <row r="244" spans="1:12">
+      <c r="L243" s="5"/>
+      <c r="M243" s="6"/>
+    </row>
+    <row r="244" spans="1:13">
       <c r="A244" s="2"/>
       <c r="B244" s="3"/>
       <c r="F244" s="4"/>
@@ -3975,9 +4259,10 @@
       <c r="I244" s="5"/>
       <c r="J244" s="5"/>
       <c r="K244" s="5"/>
-      <c r="L244" s="6"/>
-    </row>
-    <row r="245" spans="1:12">
+      <c r="L244" s="5"/>
+      <c r="M244" s="6"/>
+    </row>
+    <row r="245" spans="1:13">
       <c r="A245" s="2"/>
       <c r="B245" s="3"/>
       <c r="F245" s="4"/>
@@ -3986,9 +4271,10 @@
       <c r="I245" s="5"/>
       <c r="J245" s="5"/>
       <c r="K245" s="5"/>
-      <c r="L245" s="6"/>
-    </row>
-    <row r="246" spans="1:12">
+      <c r="L245" s="5"/>
+      <c r="M245" s="6"/>
+    </row>
+    <row r="246" spans="1:13">
       <c r="A246" s="2"/>
       <c r="B246" s="3"/>
       <c r="F246" s="4"/>
@@ -3997,9 +4283,10 @@
       <c r="I246" s="5"/>
       <c r="J246" s="5"/>
       <c r="K246" s="5"/>
-      <c r="L246" s="6"/>
-    </row>
-    <row r="247" spans="1:12">
+      <c r="L246" s="5"/>
+      <c r="M246" s="6"/>
+    </row>
+    <row r="247" spans="1:13">
       <c r="A247" s="2"/>
       <c r="B247" s="3"/>
       <c r="F247" s="4"/>
@@ -4008,9 +4295,10 @@
       <c r="I247" s="5"/>
       <c r="J247" s="5"/>
       <c r="K247" s="5"/>
-      <c r="L247" s="6"/>
-    </row>
-    <row r="248" spans="1:12">
+      <c r="L247" s="5"/>
+      <c r="M247" s="6"/>
+    </row>
+    <row r="248" spans="1:13">
       <c r="A248" s="2"/>
       <c r="B248" s="3"/>
       <c r="F248" s="4"/>
@@ -4019,9 +4307,10 @@
       <c r="I248" s="5"/>
       <c r="J248" s="5"/>
       <c r="K248" s="5"/>
-      <c r="L248" s="6"/>
-    </row>
-    <row r="249" spans="1:12">
+      <c r="L248" s="5"/>
+      <c r="M248" s="6"/>
+    </row>
+    <row r="249" spans="1:13">
       <c r="A249" s="2"/>
       <c r="B249" s="3"/>
       <c r="F249" s="4"/>
@@ -4030,9 +4319,10 @@
       <c r="I249" s="5"/>
       <c r="J249" s="5"/>
       <c r="K249" s="5"/>
-      <c r="L249" s="6"/>
-    </row>
-    <row r="250" spans="1:12">
+      <c r="L249" s="5"/>
+      <c r="M249" s="6"/>
+    </row>
+    <row r="250" spans="1:13">
       <c r="A250" s="2"/>
       <c r="B250" s="3"/>
       <c r="F250" s="4"/>
@@ -4041,9 +4331,10 @@
       <c r="I250" s="5"/>
       <c r="J250" s="5"/>
       <c r="K250" s="5"/>
-      <c r="L250" s="6"/>
-    </row>
-    <row r="251" spans="1:12">
+      <c r="L250" s="5"/>
+      <c r="M250" s="6"/>
+    </row>
+    <row r="251" spans="1:13">
       <c r="A251" s="2"/>
       <c r="B251" s="3"/>
       <c r="F251" s="4"/>
@@ -4052,9 +4343,10 @@
       <c r="I251" s="5"/>
       <c r="J251" s="5"/>
       <c r="K251" s="5"/>
-      <c r="L251" s="6"/>
-    </row>
-    <row r="252" spans="1:12">
+      <c r="L251" s="5"/>
+      <c r="M251" s="6"/>
+    </row>
+    <row r="252" spans="1:13">
       <c r="A252" s="2"/>
       <c r="B252" s="3"/>
       <c r="F252" s="4"/>
@@ -4063,9 +4355,10 @@
       <c r="I252" s="5"/>
       <c r="J252" s="5"/>
       <c r="K252" s="5"/>
-      <c r="L252" s="6"/>
-    </row>
-    <row r="253" spans="1:12">
+      <c r="L252" s="5"/>
+      <c r="M252" s="6"/>
+    </row>
+    <row r="253" spans="1:13">
       <c r="A253" s="2"/>
       <c r="B253" s="3"/>
       <c r="F253" s="4"/>
@@ -4074,9 +4367,10 @@
       <c r="I253" s="5"/>
       <c r="J253" s="5"/>
       <c r="K253" s="5"/>
-      <c r="L253" s="6"/>
-    </row>
-    <row r="254" spans="1:12">
+      <c r="L253" s="5"/>
+      <c r="M253" s="6"/>
+    </row>
+    <row r="254" spans="1:13">
       <c r="A254" s="2"/>
       <c r="B254" s="3"/>
       <c r="F254" s="4"/>
@@ -4085,9 +4379,10 @@
       <c r="I254" s="5"/>
       <c r="J254" s="5"/>
       <c r="K254" s="5"/>
-      <c r="L254" s="6"/>
-    </row>
-    <row r="255" spans="1:12">
+      <c r="L254" s="5"/>
+      <c r="M254" s="6"/>
+    </row>
+    <row r="255" spans="1:13">
       <c r="A255" s="2"/>
       <c r="B255" s="3"/>
       <c r="F255" s="4"/>
@@ -4096,9 +4391,10 @@
       <c r="I255" s="5"/>
       <c r="J255" s="5"/>
       <c r="K255" s="5"/>
-      <c r="L255" s="6"/>
-    </row>
-    <row r="256" spans="1:12">
+      <c r="L255" s="5"/>
+      <c r="M255" s="6"/>
+    </row>
+    <row r="256" spans="1:13">
       <c r="A256" s="2"/>
       <c r="B256" s="3"/>
       <c r="F256" s="4"/>
@@ -4107,9 +4403,10 @@
       <c r="I256" s="5"/>
       <c r="J256" s="5"/>
       <c r="K256" s="5"/>
-      <c r="L256" s="6"/>
-    </row>
-    <row r="257" spans="1:12">
+      <c r="L256" s="5"/>
+      <c r="M256" s="6"/>
+    </row>
+    <row r="257" spans="1:13">
       <c r="A257" s="2"/>
       <c r="B257" s="3"/>
       <c r="F257" s="4"/>
@@ -4118,9 +4415,10 @@
       <c r="I257" s="5"/>
       <c r="J257" s="5"/>
       <c r="K257" s="5"/>
-      <c r="L257" s="6"/>
-    </row>
-    <row r="258" spans="1:12">
+      <c r="L257" s="5"/>
+      <c r="M257" s="6"/>
+    </row>
+    <row r="258" spans="1:13">
       <c r="A258" s="2"/>
       <c r="B258" s="3"/>
       <c r="F258" s="4"/>
@@ -4129,9 +4427,10 @@
       <c r="I258" s="5"/>
       <c r="J258" s="5"/>
       <c r="K258" s="5"/>
-      <c r="L258" s="6"/>
-    </row>
-    <row r="259" spans="1:12">
+      <c r="L258" s="5"/>
+      <c r="M258" s="6"/>
+    </row>
+    <row r="259" spans="1:13">
       <c r="A259" s="2"/>
       <c r="B259" s="3"/>
       <c r="F259" s="4"/>
@@ -4140,9 +4439,10 @@
       <c r="I259" s="5"/>
       <c r="J259" s="5"/>
       <c r="K259" s="5"/>
-      <c r="L259" s="6"/>
-    </row>
-    <row r="260" spans="1:12">
+      <c r="L259" s="5"/>
+      <c r="M259" s="6"/>
+    </row>
+    <row r="260" spans="1:13">
       <c r="A260" s="2"/>
       <c r="B260" s="3"/>
       <c r="F260" s="4"/>
@@ -4151,9 +4451,10 @@
       <c r="I260" s="5"/>
       <c r="J260" s="5"/>
       <c r="K260" s="5"/>
-      <c r="L260" s="6"/>
-    </row>
-    <row r="261" spans="1:12">
+      <c r="L260" s="5"/>
+      <c r="M260" s="6"/>
+    </row>
+    <row r="261" spans="1:13">
       <c r="A261" s="2"/>
       <c r="B261" s="3"/>
       <c r="F261" s="4"/>
@@ -4162,9 +4463,10 @@
       <c r="I261" s="5"/>
       <c r="J261" s="5"/>
       <c r="K261" s="5"/>
-      <c r="L261" s="6"/>
-    </row>
-    <row r="262" spans="1:12">
+      <c r="L261" s="5"/>
+      <c r="M261" s="6"/>
+    </row>
+    <row r="262" spans="1:13">
       <c r="A262" s="2"/>
       <c r="B262" s="3"/>
       <c r="F262" s="4"/>
@@ -4173,9 +4475,10 @@
       <c r="I262" s="5"/>
       <c r="J262" s="5"/>
       <c r="K262" s="5"/>
-      <c r="L262" s="6"/>
-    </row>
-    <row r="263" spans="1:12">
+      <c r="L262" s="5"/>
+      <c r="M262" s="6"/>
+    </row>
+    <row r="263" spans="1:13">
       <c r="A263" s="2"/>
       <c r="B263" s="3"/>
       <c r="F263" s="4"/>
@@ -4184,9 +4487,10 @@
       <c r="I263" s="5"/>
       <c r="J263" s="5"/>
       <c r="K263" s="5"/>
-      <c r="L263" s="6"/>
-    </row>
-    <row r="264" spans="1:12">
+      <c r="L263" s="5"/>
+      <c r="M263" s="6"/>
+    </row>
+    <row r="264" spans="1:13">
       <c r="A264" s="2"/>
       <c r="B264" s="3"/>
       <c r="F264" s="4"/>
@@ -4195,9 +4499,10 @@
       <c r="I264" s="5"/>
       <c r="J264" s="5"/>
       <c r="K264" s="5"/>
-      <c r="L264" s="6"/>
-    </row>
-    <row r="265" spans="1:12">
+      <c r="L264" s="5"/>
+      <c r="M264" s="6"/>
+    </row>
+    <row r="265" spans="1:13">
       <c r="A265" s="2"/>
       <c r="B265" s="3"/>
       <c r="F265" s="4"/>
@@ -4206,9 +4511,10 @@
       <c r="I265" s="5"/>
       <c r="J265" s="5"/>
       <c r="K265" s="5"/>
-      <c r="L265" s="6"/>
-    </row>
-    <row r="266" spans="1:12">
+      <c r="L265" s="5"/>
+      <c r="M265" s="6"/>
+    </row>
+    <row r="266" spans="1:13">
       <c r="A266" s="2"/>
       <c r="B266" s="3"/>
       <c r="F266" s="4"/>
@@ -4217,9 +4523,10 @@
       <c r="I266" s="5"/>
       <c r="J266" s="5"/>
       <c r="K266" s="5"/>
-      <c r="L266" s="6"/>
-    </row>
-    <row r="267" spans="1:12">
+      <c r="L266" s="5"/>
+      <c r="M266" s="6"/>
+    </row>
+    <row r="267" spans="1:13">
       <c r="A267" s="2"/>
       <c r="B267" s="3"/>
       <c r="F267" s="4"/>
@@ -4228,9 +4535,10 @@
       <c r="I267" s="5"/>
       <c r="J267" s="5"/>
       <c r="K267" s="5"/>
-      <c r="L267" s="6"/>
-    </row>
-    <row r="268" spans="1:12">
+      <c r="L267" s="5"/>
+      <c r="M267" s="6"/>
+    </row>
+    <row r="268" spans="1:13">
       <c r="A268" s="2"/>
       <c r="B268" s="3"/>
       <c r="F268" s="4"/>
@@ -4239,9 +4547,10 @@
       <c r="I268" s="5"/>
       <c r="J268" s="5"/>
       <c r="K268" s="5"/>
-      <c r="L268" s="6"/>
-    </row>
-    <row r="269" spans="1:12">
+      <c r="L268" s="5"/>
+      <c r="M268" s="6"/>
+    </row>
+    <row r="269" spans="1:13">
       <c r="A269" s="2"/>
       <c r="B269" s="3"/>
       <c r="F269" s="4"/>
@@ -4250,9 +4559,10 @@
       <c r="I269" s="5"/>
       <c r="J269" s="5"/>
       <c r="K269" s="5"/>
-      <c r="L269" s="6"/>
-    </row>
-    <row r="270" spans="1:12">
+      <c r="L269" s="5"/>
+      <c r="M269" s="6"/>
+    </row>
+    <row r="270" spans="1:13">
       <c r="A270" s="2"/>
       <c r="B270" s="3"/>
       <c r="F270" s="4"/>
@@ -4261,9 +4571,10 @@
       <c r="I270" s="5"/>
       <c r="J270" s="5"/>
       <c r="K270" s="5"/>
-      <c r="L270" s="6"/>
-    </row>
-    <row r="271" spans="1:12">
+      <c r="L270" s="5"/>
+      <c r="M270" s="6"/>
+    </row>
+    <row r="271" spans="1:13">
       <c r="A271" s="2"/>
       <c r="B271" s="3"/>
       <c r="F271" s="4"/>
@@ -4272,9 +4583,10 @@
       <c r="I271" s="5"/>
       <c r="J271" s="5"/>
       <c r="K271" s="5"/>
-      <c r="L271" s="6"/>
-    </row>
-    <row r="272" spans="1:12">
+      <c r="L271" s="5"/>
+      <c r="M271" s="6"/>
+    </row>
+    <row r="272" spans="1:13">
       <c r="A272" s="2"/>
       <c r="B272" s="3"/>
       <c r="F272" s="4"/>
@@ -4283,9 +4595,10 @@
       <c r="I272" s="5"/>
       <c r="J272" s="5"/>
       <c r="K272" s="5"/>
-      <c r="L272" s="6"/>
-    </row>
-    <row r="273" spans="1:12">
+      <c r="L272" s="5"/>
+      <c r="M272" s="6"/>
+    </row>
+    <row r="273" spans="1:13">
       <c r="A273" s="2"/>
       <c r="B273" s="3"/>
       <c r="F273" s="4"/>
@@ -4294,9 +4607,10 @@
       <c r="I273" s="5"/>
       <c r="J273" s="5"/>
       <c r="K273" s="5"/>
-      <c r="L273" s="6"/>
-    </row>
-    <row r="274" spans="1:12">
+      <c r="L273" s="5"/>
+      <c r="M273" s="6"/>
+    </row>
+    <row r="274" spans="1:13">
       <c r="A274" s="2"/>
       <c r="B274" s="3"/>
       <c r="F274" s="4"/>
@@ -4305,9 +4619,10 @@
       <c r="I274" s="5"/>
       <c r="J274" s="5"/>
       <c r="K274" s="5"/>
-      <c r="L274" s="6"/>
-    </row>
-    <row r="275" spans="1:12">
+      <c r="L274" s="5"/>
+      <c r="M274" s="6"/>
+    </row>
+    <row r="275" spans="1:13">
       <c r="A275" s="2"/>
       <c r="B275" s="3"/>
       <c r="F275" s="4"/>
@@ -4316,9 +4631,10 @@
       <c r="I275" s="5"/>
       <c r="J275" s="5"/>
       <c r="K275" s="5"/>
-      <c r="L275" s="6"/>
-    </row>
-    <row r="276" spans="1:12">
+      <c r="L275" s="5"/>
+      <c r="M275" s="6"/>
+    </row>
+    <row r="276" spans="1:13">
       <c r="A276" s="2"/>
       <c r="B276" s="3"/>
       <c r="F276" s="4"/>
@@ -4327,9 +4643,10 @@
       <c r="I276" s="5"/>
       <c r="J276" s="5"/>
       <c r="K276" s="5"/>
-      <c r="L276" s="6"/>
-    </row>
-    <row r="277" spans="1:12">
+      <c r="L276" s="5"/>
+      <c r="M276" s="6"/>
+    </row>
+    <row r="277" spans="1:13">
       <c r="A277" s="2"/>
       <c r="B277" s="3"/>
       <c r="F277" s="4"/>
@@ -4338,9 +4655,10 @@
       <c r="I277" s="5"/>
       <c r="J277" s="5"/>
       <c r="K277" s="5"/>
-      <c r="L277" s="6"/>
-    </row>
-    <row r="278" spans="1:12">
+      <c r="L277" s="5"/>
+      <c r="M277" s="6"/>
+    </row>
+    <row r="278" spans="1:13">
       <c r="A278" s="2"/>
       <c r="B278" s="3"/>
       <c r="F278" s="4"/>
@@ -4349,9 +4667,10 @@
       <c r="I278" s="5"/>
       <c r="J278" s="5"/>
       <c r="K278" s="5"/>
-      <c r="L278" s="6"/>
-    </row>
-    <row r="279" spans="1:12">
+      <c r="L278" s="5"/>
+      <c r="M278" s="6"/>
+    </row>
+    <row r="279" spans="1:13">
       <c r="A279" s="2"/>
       <c r="B279" s="3"/>
       <c r="F279" s="4"/>
@@ -4360,9 +4679,10 @@
       <c r="I279" s="5"/>
       <c r="J279" s="5"/>
       <c r="K279" s="5"/>
-      <c r="L279" s="6"/>
-    </row>
-    <row r="280" spans="1:12">
+      <c r="L279" s="5"/>
+      <c r="M279" s="6"/>
+    </row>
+    <row r="280" spans="1:13">
       <c r="A280" s="2"/>
       <c r="B280" s="3"/>
       <c r="F280" s="4"/>
@@ -4371,9 +4691,10 @@
       <c r="I280" s="5"/>
       <c r="J280" s="5"/>
       <c r="K280" s="5"/>
-      <c r="L280" s="6"/>
-    </row>
-    <row r="281" spans="1:12">
+      <c r="L280" s="5"/>
+      <c r="M280" s="6"/>
+    </row>
+    <row r="281" spans="1:13">
       <c r="A281" s="2"/>
       <c r="B281" s="3"/>
       <c r="F281" s="4"/>
@@ -4382,9 +4703,10 @@
       <c r="I281" s="5"/>
       <c r="J281" s="5"/>
       <c r="K281" s="5"/>
-      <c r="L281" s="6"/>
-    </row>
-    <row r="282" spans="1:12">
+      <c r="L281" s="5"/>
+      <c r="M281" s="6"/>
+    </row>
+    <row r="282" spans="1:13">
       <c r="A282" s="2"/>
       <c r="B282" s="3"/>
       <c r="F282" s="4"/>
@@ -4393,9 +4715,10 @@
       <c r="I282" s="5"/>
       <c r="J282" s="5"/>
       <c r="K282" s="5"/>
-      <c r="L282" s="6"/>
-    </row>
-    <row r="283" spans="1:12">
+      <c r="L282" s="5"/>
+      <c r="M282" s="6"/>
+    </row>
+    <row r="283" spans="1:13">
       <c r="A283" s="2"/>
       <c r="B283" s="3"/>
       <c r="F283" s="4"/>
@@ -4404,9 +4727,10 @@
       <c r="I283" s="5"/>
       <c r="J283" s="5"/>
       <c r="K283" s="5"/>
-      <c r="L283" s="6"/>
-    </row>
-    <row r="284" spans="1:12">
+      <c r="L283" s="5"/>
+      <c r="M283" s="6"/>
+    </row>
+    <row r="284" spans="1:13">
       <c r="A284" s="2"/>
       <c r="B284" s="3"/>
       <c r="F284" s="4"/>
@@ -4415,9 +4739,10 @@
       <c r="I284" s="5"/>
       <c r="J284" s="5"/>
       <c r="K284" s="5"/>
-      <c r="L284" s="6"/>
-    </row>
-    <row r="285" spans="1:12">
+      <c r="L284" s="5"/>
+      <c r="M284" s="6"/>
+    </row>
+    <row r="285" spans="1:13">
       <c r="A285" s="2"/>
       <c r="B285" s="3"/>
       <c r="F285" s="4"/>
@@ -4426,9 +4751,10 @@
       <c r="I285" s="5"/>
       <c r="J285" s="5"/>
       <c r="K285" s="5"/>
-      <c r="L285" s="6"/>
-    </row>
-    <row r="286" spans="1:12">
+      <c r="L285" s="5"/>
+      <c r="M285" s="6"/>
+    </row>
+    <row r="286" spans="1:13">
       <c r="A286" s="2"/>
       <c r="B286" s="3"/>
       <c r="F286" s="4"/>
@@ -4437,9 +4763,10 @@
       <c r="I286" s="5"/>
       <c r="J286" s="5"/>
       <c r="K286" s="5"/>
-      <c r="L286" s="6"/>
-    </row>
-    <row r="287" spans="1:12">
+      <c r="L286" s="5"/>
+      <c r="M286" s="6"/>
+    </row>
+    <row r="287" spans="1:13">
       <c r="A287" s="2"/>
       <c r="B287" s="3"/>
       <c r="F287" s="4"/>
@@ -4448,9 +4775,10 @@
       <c r="I287" s="5"/>
       <c r="J287" s="5"/>
       <c r="K287" s="5"/>
-      <c r="L287" s="6"/>
-    </row>
-    <row r="288" spans="1:12">
+      <c r="L287" s="5"/>
+      <c r="M287" s="6"/>
+    </row>
+    <row r="288" spans="1:13">
       <c r="A288" s="2"/>
       <c r="B288" s="3"/>
       <c r="F288" s="4"/>
@@ -4459,9 +4787,10 @@
       <c r="I288" s="5"/>
       <c r="J288" s="5"/>
       <c r="K288" s="5"/>
-      <c r="L288" s="6"/>
-    </row>
-    <row r="289" spans="1:12">
+      <c r="L288" s="5"/>
+      <c r="M288" s="6"/>
+    </row>
+    <row r="289" spans="1:13">
       <c r="A289" s="2"/>
       <c r="B289" s="3"/>
       <c r="F289" s="4"/>
@@ -4470,9 +4799,10 @@
       <c r="I289" s="5"/>
       <c r="J289" s="5"/>
       <c r="K289" s="5"/>
-      <c r="L289" s="6"/>
-    </row>
-    <row r="290" spans="1:12">
+      <c r="L289" s="5"/>
+      <c r="M289" s="6"/>
+    </row>
+    <row r="290" spans="1:13">
       <c r="A290" s="2"/>
       <c r="B290" s="3"/>
       <c r="F290" s="4"/>
@@ -4481,9 +4811,10 @@
       <c r="I290" s="5"/>
       <c r="J290" s="5"/>
       <c r="K290" s="5"/>
-      <c r="L290" s="6"/>
-    </row>
-    <row r="291" spans="1:12">
+      <c r="L290" s="5"/>
+      <c r="M290" s="6"/>
+    </row>
+    <row r="291" spans="1:13">
       <c r="A291" s="2"/>
       <c r="B291" s="3"/>
       <c r="F291" s="4"/>
@@ -4492,9 +4823,10 @@
       <c r="I291" s="5"/>
       <c r="J291" s="5"/>
       <c r="K291" s="5"/>
-      <c r="L291" s="6"/>
-    </row>
-    <row r="292" spans="1:12">
+      <c r="L291" s="5"/>
+      <c r="M291" s="6"/>
+    </row>
+    <row r="292" spans="1:13">
       <c r="A292" s="2"/>
       <c r="B292" s="3"/>
       <c r="F292" s="4"/>
@@ -4503,9 +4835,10 @@
       <c r="I292" s="5"/>
       <c r="J292" s="5"/>
       <c r="K292" s="5"/>
-      <c r="L292" s="6"/>
-    </row>
-    <row r="293" spans="1:12">
+      <c r="L292" s="5"/>
+      <c r="M292" s="6"/>
+    </row>
+    <row r="293" spans="1:13">
       <c r="A293" s="2"/>
       <c r="B293" s="3"/>
       <c r="F293" s="4"/>
@@ -4514,9 +4847,10 @@
       <c r="I293" s="5"/>
       <c r="J293" s="5"/>
       <c r="K293" s="5"/>
-      <c r="L293" s="6"/>
-    </row>
-    <row r="294" spans="1:12">
+      <c r="L293" s="5"/>
+      <c r="M293" s="6"/>
+    </row>
+    <row r="294" spans="1:13">
       <c r="A294" s="2"/>
       <c r="B294" s="3"/>
       <c r="F294" s="4"/>
@@ -4525,9 +4859,10 @@
       <c r="I294" s="5"/>
       <c r="J294" s="5"/>
       <c r="K294" s="5"/>
-      <c r="L294" s="6"/>
-    </row>
-    <row r="295" spans="1:12">
+      <c r="L294" s="5"/>
+      <c r="M294" s="6"/>
+    </row>
+    <row r="295" spans="1:13">
       <c r="A295" s="2"/>
       <c r="B295" s="3"/>
       <c r="F295" s="4"/>
@@ -4536,9 +4871,10 @@
       <c r="I295" s="5"/>
       <c r="J295" s="5"/>
       <c r="K295" s="5"/>
-      <c r="L295" s="6"/>
-    </row>
-    <row r="296" spans="1:12">
+      <c r="L295" s="5"/>
+      <c r="M295" s="6"/>
+    </row>
+    <row r="296" spans="1:13">
       <c r="A296" s="2"/>
       <c r="B296" s="3"/>
       <c r="F296" s="4"/>
@@ -4547,9 +4883,10 @@
       <c r="I296" s="5"/>
       <c r="J296" s="5"/>
       <c r="K296" s="5"/>
-      <c r="L296" s="6"/>
-    </row>
-    <row r="297" spans="1:12">
+      <c r="L296" s="5"/>
+      <c r="M296" s="6"/>
+    </row>
+    <row r="297" spans="1:13">
       <c r="A297" s="2"/>
       <c r="B297" s="3"/>
       <c r="F297" s="4"/>
@@ -4558,9 +4895,10 @@
       <c r="I297" s="5"/>
       <c r="J297" s="5"/>
       <c r="K297" s="5"/>
-      <c r="L297" s="6"/>
-    </row>
-    <row r="298" spans="1:12">
+      <c r="L297" s="5"/>
+      <c r="M297" s="6"/>
+    </row>
+    <row r="298" spans="1:13">
       <c r="A298" s="2"/>
       <c r="B298" s="3"/>
       <c r="F298" s="4"/>
@@ -4569,9 +4907,10 @@
       <c r="I298" s="5"/>
       <c r="J298" s="5"/>
       <c r="K298" s="5"/>
-      <c r="L298" s="6"/>
-    </row>
-    <row r="299" spans="1:12">
+      <c r="L298" s="5"/>
+      <c r="M298" s="6"/>
+    </row>
+    <row r="299" spans="1:13">
       <c r="A299" s="2"/>
       <c r="B299" s="3"/>
       <c r="F299" s="4"/>
@@ -4580,9 +4919,10 @@
       <c r="I299" s="5"/>
       <c r="J299" s="5"/>
       <c r="K299" s="5"/>
-      <c r="L299" s="6"/>
-    </row>
-    <row r="300" spans="1:12">
+      <c r="L299" s="5"/>
+      <c r="M299" s="6"/>
+    </row>
+    <row r="300" spans="1:13">
       <c r="A300" s="2"/>
       <c r="B300" s="3"/>
       <c r="F300" s="4"/>
@@ -4591,9 +4931,10 @@
       <c r="I300" s="5"/>
       <c r="J300" s="5"/>
       <c r="K300" s="5"/>
-      <c r="L300" s="6"/>
-    </row>
-    <row r="301" spans="1:12">
+      <c r="L300" s="5"/>
+      <c r="M300" s="6"/>
+    </row>
+    <row r="301" spans="1:13">
       <c r="A301" s="2"/>
       <c r="B301" s="3"/>
       <c r="F301" s="4"/>
@@ -4602,9 +4943,10 @@
       <c r="I301" s="5"/>
       <c r="J301" s="5"/>
       <c r="K301" s="5"/>
-      <c r="L301" s="6"/>
-    </row>
-    <row r="302" spans="1:12">
+      <c r="L301" s="5"/>
+      <c r="M301" s="6"/>
+    </row>
+    <row r="302" spans="1:13">
       <c r="A302" s="2"/>
       <c r="B302" s="3"/>
       <c r="F302" s="4"/>
@@ -4613,9 +4955,10 @@
       <c r="I302" s="5"/>
       <c r="J302" s="5"/>
       <c r="K302" s="5"/>
-      <c r="L302" s="6"/>
-    </row>
-    <row r="303" spans="1:12">
+      <c r="L302" s="5"/>
+      <c r="M302" s="6"/>
+    </row>
+    <row r="303" spans="1:13">
       <c r="A303" s="2"/>
       <c r="B303" s="3"/>
       <c r="F303" s="4"/>
@@ -4624,9 +4967,10 @@
       <c r="I303" s="5"/>
       <c r="J303" s="5"/>
       <c r="K303" s="5"/>
-      <c r="L303" s="6"/>
-    </row>
-    <row r="304" spans="1:12">
+      <c r="L303" s="5"/>
+      <c r="M303" s="6"/>
+    </row>
+    <row r="304" spans="1:13">
       <c r="A304" s="2"/>
       <c r="B304" s="3"/>
       <c r="F304" s="4"/>
@@ -4635,9 +4979,10 @@
       <c r="I304" s="5"/>
       <c r="J304" s="5"/>
       <c r="K304" s="5"/>
-      <c r="L304" s="6"/>
-    </row>
-    <row r="305" spans="1:12">
+      <c r="L304" s="5"/>
+      <c r="M304" s="6"/>
+    </row>
+    <row r="305" spans="1:13">
       <c r="A305" s="2"/>
       <c r="B305" s="3"/>
       <c r="F305" s="4"/>
@@ -4646,9 +4991,10 @@
       <c r="I305" s="5"/>
       <c r="J305" s="5"/>
       <c r="K305" s="5"/>
-      <c r="L305" s="6"/>
-    </row>
-    <row r="306" spans="1:12">
+      <c r="L305" s="5"/>
+      <c r="M305" s="6"/>
+    </row>
+    <row r="306" spans="1:13">
       <c r="A306" s="2"/>
       <c r="B306" s="3"/>
       <c r="F306" s="4"/>
@@ -4657,9 +5003,10 @@
       <c r="I306" s="5"/>
       <c r="J306" s="5"/>
       <c r="K306" s="5"/>
-      <c r="L306" s="6"/>
-    </row>
-    <row r="307" spans="1:12">
+      <c r="L306" s="5"/>
+      <c r="M306" s="6"/>
+    </row>
+    <row r="307" spans="1:13">
       <c r="A307" s="2"/>
       <c r="B307" s="3"/>
       <c r="F307" s="4"/>
@@ -4668,9 +5015,10 @@
       <c r="I307" s="5"/>
       <c r="J307" s="5"/>
       <c r="K307" s="5"/>
-      <c r="L307" s="6"/>
-    </row>
-    <row r="308" spans="1:12">
+      <c r="L307" s="5"/>
+      <c r="M307" s="6"/>
+    </row>
+    <row r="308" spans="1:13">
       <c r="A308" s="2"/>
       <c r="B308" s="3"/>
       <c r="F308" s="4"/>
@@ -4679,9 +5027,10 @@
       <c r="I308" s="5"/>
       <c r="J308" s="5"/>
       <c r="K308" s="5"/>
-      <c r="L308" s="6"/>
-    </row>
-    <row r="309" spans="1:12">
+      <c r="L308" s="5"/>
+      <c r="M308" s="6"/>
+    </row>
+    <row r="309" spans="1:13">
       <c r="A309" s="2"/>
       <c r="B309" s="3"/>
       <c r="F309" s="4"/>
@@ -4690,9 +5039,10 @@
       <c r="I309" s="5"/>
       <c r="J309" s="5"/>
       <c r="K309" s="5"/>
-      <c r="L309" s="6"/>
-    </row>
-    <row r="310" spans="1:12">
+      <c r="L309" s="5"/>
+      <c r="M309" s="6"/>
+    </row>
+    <row r="310" spans="1:13">
       <c r="A310" s="2"/>
       <c r="B310" s="3"/>
       <c r="F310" s="4"/>
@@ -4701,9 +5051,10 @@
       <c r="I310" s="5"/>
       <c r="J310" s="5"/>
       <c r="K310" s="5"/>
-      <c r="L310" s="6"/>
-    </row>
-    <row r="311" spans="1:12">
+      <c r="L310" s="5"/>
+      <c r="M310" s="6"/>
+    </row>
+    <row r="311" spans="1:13">
       <c r="A311" s="2"/>
       <c r="B311" s="3"/>
       <c r="F311" s="4"/>
@@ -4712,9 +5063,10 @@
       <c r="I311" s="5"/>
       <c r="J311" s="5"/>
       <c r="K311" s="5"/>
-      <c r="L311" s="6"/>
-    </row>
-    <row r="312" spans="1:12">
+      <c r="L311" s="5"/>
+      <c r="M311" s="6"/>
+    </row>
+    <row r="312" spans="1:13">
       <c r="A312" s="2"/>
       <c r="B312" s="3"/>
       <c r="F312" s="4"/>
@@ -4723,9 +5075,10 @@
       <c r="I312" s="5"/>
       <c r="J312" s="5"/>
       <c r="K312" s="5"/>
-      <c r="L312" s="6"/>
-    </row>
-    <row r="313" spans="1:12">
+      <c r="L312" s="5"/>
+      <c r="M312" s="6"/>
+    </row>
+    <row r="313" spans="1:13">
       <c r="A313" s="2"/>
       <c r="B313" s="3"/>
       <c r="F313" s="4"/>
@@ -4734,9 +5087,10 @@
       <c r="I313" s="5"/>
       <c r="J313" s="5"/>
       <c r="K313" s="5"/>
-      <c r="L313" s="6"/>
-    </row>
-    <row r="314" spans="1:12">
+      <c r="L313" s="5"/>
+      <c r="M313" s="6"/>
+    </row>
+    <row r="314" spans="1:13">
       <c r="A314" s="2"/>
       <c r="B314" s="3"/>
       <c r="F314" s="4"/>
@@ -4745,9 +5099,10 @@
       <c r="I314" s="5"/>
       <c r="J314" s="5"/>
       <c r="K314" s="5"/>
-      <c r="L314" s="6"/>
-    </row>
-    <row r="315" spans="1:12">
+      <c r="L314" s="5"/>
+      <c r="M314" s="6"/>
+    </row>
+    <row r="315" spans="1:13">
       <c r="A315" s="2"/>
       <c r="B315" s="3"/>
       <c r="F315" s="4"/>
@@ -4756,9 +5111,10 @@
       <c r="I315" s="5"/>
       <c r="J315" s="5"/>
       <c r="K315" s="5"/>
-      <c r="L315" s="6"/>
-    </row>
-    <row r="316" spans="1:12">
+      <c r="L315" s="5"/>
+      <c r="M315" s="6"/>
+    </row>
+    <row r="316" spans="1:13">
       <c r="A316" s="2"/>
       <c r="B316" s="3"/>
       <c r="F316" s="4"/>
@@ -4767,9 +5123,10 @@
       <c r="I316" s="5"/>
       <c r="J316" s="5"/>
       <c r="K316" s="5"/>
-      <c r="L316" s="6"/>
-    </row>
-    <row r="317" spans="1:12">
+      <c r="L316" s="5"/>
+      <c r="M316" s="6"/>
+    </row>
+    <row r="317" spans="1:13">
       <c r="A317" s="2"/>
       <c r="B317" s="3"/>
       <c r="F317" s="4"/>
@@ -4778,9 +5135,10 @@
       <c r="I317" s="5"/>
       <c r="J317" s="5"/>
       <c r="K317" s="5"/>
-      <c r="L317" s="6"/>
-    </row>
-    <row r="318" spans="1:12">
+      <c r="L317" s="5"/>
+      <c r="M317" s="6"/>
+    </row>
+    <row r="318" spans="1:13">
       <c r="A318" s="2"/>
       <c r="B318" s="3"/>
       <c r="F318" s="4"/>
@@ -4789,9 +5147,10 @@
       <c r="I318" s="5"/>
       <c r="J318" s="5"/>
       <c r="K318" s="5"/>
-      <c r="L318" s="6"/>
-    </row>
-    <row r="319" spans="1:12">
+      <c r="L318" s="5"/>
+      <c r="M318" s="6"/>
+    </row>
+    <row r="319" spans="1:13">
       <c r="A319" s="2"/>
       <c r="B319" s="3"/>
       <c r="F319" s="4"/>
@@ -4800,9 +5159,10 @@
       <c r="I319" s="5"/>
       <c r="J319" s="5"/>
       <c r="K319" s="5"/>
-      <c r="L319" s="6"/>
-    </row>
-    <row r="320" spans="1:12">
+      <c r="L319" s="5"/>
+      <c r="M319" s="6"/>
+    </row>
+    <row r="320" spans="1:13">
       <c r="A320" s="2"/>
       <c r="B320" s="3"/>
       <c r="F320" s="4"/>
@@ -4811,9 +5171,10 @@
       <c r="I320" s="5"/>
       <c r="J320" s="5"/>
       <c r="K320" s="5"/>
-      <c r="L320" s="6"/>
-    </row>
-    <row r="321" spans="1:12">
+      <c r="L320" s="5"/>
+      <c r="M320" s="6"/>
+    </row>
+    <row r="321" spans="1:13">
       <c r="A321" s="2"/>
       <c r="B321" s="3"/>
       <c r="F321" s="4"/>
@@ -4822,9 +5183,10 @@
       <c r="I321" s="5"/>
       <c r="J321" s="5"/>
       <c r="K321" s="5"/>
-      <c r="L321" s="6"/>
-    </row>
-    <row r="322" spans="1:12">
+      <c r="L321" s="5"/>
+      <c r="M321" s="6"/>
+    </row>
+    <row r="322" spans="1:13">
       <c r="A322" s="2"/>
       <c r="B322" s="3"/>
       <c r="F322" s="4"/>
@@ -4833,9 +5195,10 @@
       <c r="I322" s="5"/>
       <c r="J322" s="5"/>
       <c r="K322" s="5"/>
-      <c r="L322" s="6"/>
-    </row>
-    <row r="323" spans="1:12">
+      <c r="L322" s="5"/>
+      <c r="M322" s="6"/>
+    </row>
+    <row r="323" spans="1:13">
       <c r="A323" s="2"/>
       <c r="B323" s="3"/>
       <c r="F323" s="4"/>
@@ -4844,9 +5207,10 @@
       <c r="I323" s="5"/>
       <c r="J323" s="5"/>
       <c r="K323" s="5"/>
-      <c r="L323" s="6"/>
-    </row>
-    <row r="324" spans="1:12">
+      <c r="L323" s="5"/>
+      <c r="M323" s="6"/>
+    </row>
+    <row r="324" spans="1:13">
       <c r="A324" s="2"/>
       <c r="B324" s="3"/>
       <c r="F324" s="4"/>
@@ -4855,9 +5219,10 @@
       <c r="I324" s="5"/>
       <c r="J324" s="5"/>
       <c r="K324" s="5"/>
-      <c r="L324" s="6"/>
-    </row>
-    <row r="325" spans="1:12">
+      <c r="L324" s="5"/>
+      <c r="M324" s="6"/>
+    </row>
+    <row r="325" spans="1:13">
       <c r="A325" s="2"/>
       <c r="B325" s="3"/>
       <c r="F325" s="4"/>
@@ -4866,9 +5231,10 @@
       <c r="I325" s="5"/>
       <c r="J325" s="5"/>
       <c r="K325" s="5"/>
-      <c r="L325" s="6"/>
-    </row>
-    <row r="326" spans="1:12">
+      <c r="L325" s="5"/>
+      <c r="M325" s="6"/>
+    </row>
+    <row r="326" spans="1:13">
       <c r="A326" s="2"/>
       <c r="B326" s="3"/>
       <c r="F326" s="4"/>
@@ -4877,9 +5243,10 @@
       <c r="I326" s="5"/>
       <c r="J326" s="5"/>
       <c r="K326" s="5"/>
-      <c r="L326" s="6"/>
-    </row>
-    <row r="327" spans="1:12">
+      <c r="L326" s="5"/>
+      <c r="M326" s="6"/>
+    </row>
+    <row r="327" spans="1:13">
       <c r="A327" s="2"/>
       <c r="B327" s="3"/>
       <c r="F327" s="4"/>
@@ -4888,9 +5255,10 @@
       <c r="I327" s="5"/>
       <c r="J327" s="5"/>
       <c r="K327" s="5"/>
-      <c r="L327" s="6"/>
-    </row>
-    <row r="328" spans="1:12">
+      <c r="L327" s="5"/>
+      <c r="M327" s="6"/>
+    </row>
+    <row r="328" spans="1:13">
       <c r="A328" s="2"/>
       <c r="B328" s="3"/>
       <c r="F328" s="4"/>
@@ -4899,9 +5267,10 @@
       <c r="I328" s="5"/>
       <c r="J328" s="5"/>
       <c r="K328" s="5"/>
-      <c r="L328" s="6"/>
-    </row>
-    <row r="329" spans="1:12">
+      <c r="L328" s="5"/>
+      <c r="M328" s="6"/>
+    </row>
+    <row r="329" spans="1:13">
       <c r="A329" s="2"/>
       <c r="B329" s="3"/>
       <c r="F329" s="4"/>
@@ -4910,9 +5279,10 @@
       <c r="I329" s="5"/>
       <c r="J329" s="5"/>
       <c r="K329" s="5"/>
-      <c r="L329" s="6"/>
-    </row>
-    <row r="330" spans="1:12">
+      <c r="L329" s="5"/>
+      <c r="M329" s="6"/>
+    </row>
+    <row r="330" spans="1:13">
       <c r="A330" s="2"/>
       <c r="B330" s="3"/>
       <c r="F330" s="4"/>
@@ -4921,9 +5291,10 @@
       <c r="I330" s="5"/>
       <c r="J330" s="5"/>
       <c r="K330" s="5"/>
-      <c r="L330" s="6"/>
-    </row>
-    <row r="331" spans="1:12">
+      <c r="L330" s="5"/>
+      <c r="M330" s="6"/>
+    </row>
+    <row r="331" spans="1:13">
       <c r="A331" s="2"/>
       <c r="B331" s="3"/>
       <c r="F331" s="4"/>
@@ -4932,9 +5303,10 @@
       <c r="I331" s="5"/>
       <c r="J331" s="5"/>
       <c r="K331" s="5"/>
-      <c r="L331" s="6"/>
-    </row>
-    <row r="332" spans="1:12">
+      <c r="L331" s="5"/>
+      <c r="M331" s="6"/>
+    </row>
+    <row r="332" spans="1:13">
       <c r="A332" s="2"/>
       <c r="B332" s="3"/>
       <c r="F332" s="4"/>
@@ -4943,9 +5315,10 @@
       <c r="I332" s="5"/>
       <c r="J332" s="5"/>
       <c r="K332" s="5"/>
-      <c r="L332" s="6"/>
-    </row>
-    <row r="333" spans="1:12">
+      <c r="L332" s="5"/>
+      <c r="M332" s="6"/>
+    </row>
+    <row r="333" spans="1:13">
       <c r="A333" s="2"/>
       <c r="B333" s="3"/>
       <c r="F333" s="4"/>
@@ -4954,9 +5327,10 @@
       <c r="I333" s="5"/>
       <c r="J333" s="5"/>
       <c r="K333" s="5"/>
-      <c r="L333" s="6"/>
-    </row>
-    <row r="334" spans="1:12">
+      <c r="L333" s="5"/>
+      <c r="M333" s="6"/>
+    </row>
+    <row r="334" spans="1:13">
       <c r="A334" s="2"/>
       <c r="B334" s="3"/>
       <c r="F334" s="4"/>
@@ -4965,9 +5339,10 @@
       <c r="I334" s="5"/>
       <c r="J334" s="5"/>
       <c r="K334" s="5"/>
-      <c r="L334" s="6"/>
-    </row>
-    <row r="335" spans="1:12">
+      <c r="L334" s="5"/>
+      <c r="M334" s="6"/>
+    </row>
+    <row r="335" spans="1:13">
       <c r="A335" s="2"/>
       <c r="B335" s="3"/>
       <c r="F335" s="4"/>
@@ -4976,9 +5351,10 @@
       <c r="I335" s="5"/>
       <c r="J335" s="5"/>
       <c r="K335" s="5"/>
-      <c r="L335" s="6"/>
-    </row>
-    <row r="336" spans="1:12">
+      <c r="L335" s="5"/>
+      <c r="M335" s="6"/>
+    </row>
+    <row r="336" spans="1:13">
       <c r="A336" s="2"/>
       <c r="B336" s="3"/>
       <c r="F336" s="4"/>
@@ -4987,9 +5363,10 @@
       <c r="I336" s="5"/>
       <c r="J336" s="5"/>
       <c r="K336" s="5"/>
-      <c r="L336" s="6"/>
-    </row>
-    <row r="337" spans="1:12">
+      <c r="L336" s="5"/>
+      <c r="M336" s="6"/>
+    </row>
+    <row r="337" spans="1:13">
       <c r="A337" s="2"/>
       <c r="B337" s="3"/>
       <c r="F337" s="4"/>
@@ -4998,9 +5375,10 @@
       <c r="I337" s="5"/>
       <c r="J337" s="5"/>
       <c r="K337" s="5"/>
-      <c r="L337" s="6"/>
-    </row>
-    <row r="338" spans="1:12">
+      <c r="L337" s="5"/>
+      <c r="M337" s="6"/>
+    </row>
+    <row r="338" spans="1:13">
       <c r="A338" s="2"/>
       <c r="B338" s="3"/>
       <c r="F338" s="4"/>
@@ -5009,9 +5387,10 @@
       <c r="I338" s="5"/>
       <c r="J338" s="5"/>
       <c r="K338" s="5"/>
-      <c r="L338" s="6"/>
-    </row>
-    <row r="339" spans="1:12">
+      <c r="L338" s="5"/>
+      <c r="M338" s="6"/>
+    </row>
+    <row r="339" spans="1:13">
       <c r="A339" s="2"/>
       <c r="B339" s="3"/>
       <c r="F339" s="4"/>
@@ -5020,9 +5399,10 @@
       <c r="I339" s="5"/>
       <c r="J339" s="5"/>
       <c r="K339" s="5"/>
-      <c r="L339" s="6"/>
-    </row>
-    <row r="340" spans="1:12">
+      <c r="L339" s="5"/>
+      <c r="M339" s="6"/>
+    </row>
+    <row r="340" spans="1:13">
       <c r="A340" s="2"/>
       <c r="B340" s="3"/>
       <c r="F340" s="4"/>
@@ -5031,9 +5411,10 @@
       <c r="I340" s="5"/>
       <c r="J340" s="5"/>
       <c r="K340" s="5"/>
-      <c r="L340" s="6"/>
-    </row>
-    <row r="341" spans="1:12">
+      <c r="L340" s="5"/>
+      <c r="M340" s="6"/>
+    </row>
+    <row r="341" spans="1:13">
       <c r="A341" s="2"/>
       <c r="B341" s="3"/>
       <c r="F341" s="4"/>
@@ -5042,9 +5423,10 @@
       <c r="I341" s="5"/>
       <c r="J341" s="5"/>
       <c r="K341" s="5"/>
-      <c r="L341" s="6"/>
-    </row>
-    <row r="342" spans="1:12">
+      <c r="L341" s="5"/>
+      <c r="M341" s="6"/>
+    </row>
+    <row r="342" spans="1:13">
       <c r="A342" s="2"/>
       <c r="B342" s="3"/>
       <c r="F342" s="4"/>
@@ -5053,9 +5435,10 @@
       <c r="I342" s="5"/>
       <c r="J342" s="5"/>
       <c r="K342" s="5"/>
-      <c r="L342" s="6"/>
-    </row>
-    <row r="343" spans="1:12">
+      <c r="L342" s="5"/>
+      <c r="M342" s="6"/>
+    </row>
+    <row r="343" spans="1:13">
       <c r="A343" s="2"/>
       <c r="B343" s="3"/>
       <c r="F343" s="4"/>
@@ -5064,9 +5447,10 @@
       <c r="I343" s="5"/>
       <c r="J343" s="5"/>
       <c r="K343" s="5"/>
-      <c r="L343" s="6"/>
-    </row>
-    <row r="344" spans="1:12">
+      <c r="L343" s="5"/>
+      <c r="M343" s="6"/>
+    </row>
+    <row r="344" spans="1:13">
       <c r="A344" s="2"/>
       <c r="B344" s="3"/>
       <c r="F344" s="4"/>
@@ -5075,9 +5459,10 @@
       <c r="I344" s="5"/>
       <c r="J344" s="5"/>
       <c r="K344" s="5"/>
-      <c r="L344" s="6"/>
-    </row>
-    <row r="345" spans="1:12">
+      <c r="L344" s="5"/>
+      <c r="M344" s="6"/>
+    </row>
+    <row r="345" spans="1:13">
       <c r="A345" s="2"/>
       <c r="B345" s="3"/>
       <c r="F345" s="4"/>
@@ -5086,9 +5471,10 @@
       <c r="I345" s="5"/>
       <c r="J345" s="5"/>
       <c r="K345" s="5"/>
-      <c r="L345" s="6"/>
-    </row>
-    <row r="346" spans="1:12">
+      <c r="L345" s="5"/>
+      <c r="M345" s="6"/>
+    </row>
+    <row r="346" spans="1:13">
       <c r="A346" s="2"/>
       <c r="B346" s="3"/>
       <c r="F346" s="4"/>
@@ -5097,9 +5483,10 @@
       <c r="I346" s="5"/>
       <c r="J346" s="5"/>
       <c r="K346" s="5"/>
-      <c r="L346" s="6"/>
-    </row>
-    <row r="347" spans="1:12">
+      <c r="L346" s="5"/>
+      <c r="M346" s="6"/>
+    </row>
+    <row r="347" spans="1:13">
       <c r="A347" s="2"/>
       <c r="B347" s="3"/>
       <c r="F347" s="4"/>
@@ -5108,9 +5495,10 @@
       <c r="I347" s="5"/>
       <c r="J347" s="5"/>
       <c r="K347" s="5"/>
-      <c r="L347" s="6"/>
-    </row>
-    <row r="348" spans="1:12">
+      <c r="L347" s="5"/>
+      <c r="M347" s="6"/>
+    </row>
+    <row r="348" spans="1:13">
       <c r="A348" s="2"/>
       <c r="B348" s="3"/>
       <c r="F348" s="4"/>
@@ -5119,9 +5507,10 @@
       <c r="I348" s="5"/>
       <c r="J348" s="5"/>
       <c r="K348" s="5"/>
-      <c r="L348" s="6"/>
-    </row>
-    <row r="349" spans="1:12">
+      <c r="L348" s="5"/>
+      <c r="M348" s="6"/>
+    </row>
+    <row r="349" spans="1:13">
       <c r="A349" s="2"/>
       <c r="B349" s="3"/>
       <c r="F349" s="4"/>
@@ -5130,9 +5519,10 @@
       <c r="I349" s="5"/>
       <c r="J349" s="5"/>
       <c r="K349" s="5"/>
-      <c r="L349" s="6"/>
-    </row>
-    <row r="350" spans="1:12">
+      <c r="L349" s="5"/>
+      <c r="M349" s="6"/>
+    </row>
+    <row r="350" spans="1:13">
       <c r="A350" s="2"/>
       <c r="B350" s="3"/>
       <c r="F350" s="4"/>
@@ -5141,9 +5531,10 @@
       <c r="I350" s="5"/>
       <c r="J350" s="5"/>
       <c r="K350" s="5"/>
-      <c r="L350" s="6"/>
-    </row>
-    <row r="351" spans="1:12">
+      <c r="L350" s="5"/>
+      <c r="M350" s="6"/>
+    </row>
+    <row r="351" spans="1:13">
       <c r="A351" s="2"/>
       <c r="B351" s="3"/>
       <c r="F351" s="4"/>
@@ -5152,9 +5543,10 @@
       <c r="I351" s="5"/>
       <c r="J351" s="5"/>
       <c r="K351" s="5"/>
-      <c r="L351" s="6"/>
-    </row>
-    <row r="352" spans="1:12">
+      <c r="L351" s="5"/>
+      <c r="M351" s="6"/>
+    </row>
+    <row r="352" spans="1:13">
       <c r="A352" s="2"/>
       <c r="B352" s="3"/>
       <c r="F352" s="4"/>
@@ -5163,9 +5555,10 @@
       <c r="I352" s="5"/>
       <c r="J352" s="5"/>
       <c r="K352" s="5"/>
-      <c r="L352" s="6"/>
-    </row>
-    <row r="353" spans="1:12">
+      <c r="L352" s="5"/>
+      <c r="M352" s="6"/>
+    </row>
+    <row r="353" spans="1:13">
       <c r="A353" s="2"/>
       <c r="B353" s="3"/>
       <c r="F353" s="4"/>
@@ -5174,9 +5567,10 @@
       <c r="I353" s="5"/>
       <c r="J353" s="5"/>
       <c r="K353" s="5"/>
-      <c r="L353" s="6"/>
-    </row>
-    <row r="354" spans="1:12">
+      <c r="L353" s="5"/>
+      <c r="M353" s="6"/>
+    </row>
+    <row r="354" spans="1:13">
       <c r="A354" s="2"/>
       <c r="B354" s="3"/>
       <c r="F354" s="4"/>
@@ -5185,9 +5579,10 @@
       <c r="I354" s="5"/>
       <c r="J354" s="5"/>
       <c r="K354" s="5"/>
-      <c r="L354" s="6"/>
-    </row>
-    <row r="355" spans="1:12">
+      <c r="L354" s="5"/>
+      <c r="M354" s="6"/>
+    </row>
+    <row r="355" spans="1:13">
       <c r="A355" s="2"/>
       <c r="B355" s="3"/>
       <c r="F355" s="4"/>
@@ -5196,9 +5591,10 @@
       <c r="I355" s="5"/>
       <c r="J355" s="5"/>
       <c r="K355" s="5"/>
-      <c r="L355" s="6"/>
-    </row>
-    <row r="356" spans="1:12">
+      <c r="L355" s="5"/>
+      <c r="M355" s="6"/>
+    </row>
+    <row r="356" spans="1:13">
       <c r="A356" s="2"/>
       <c r="B356" s="3"/>
       <c r="F356" s="4"/>
@@ -5207,9 +5603,10 @@
       <c r="I356" s="5"/>
       <c r="J356" s="5"/>
       <c r="K356" s="5"/>
-      <c r="L356" s="6"/>
-    </row>
-    <row r="357" spans="1:12">
+      <c r="L356" s="5"/>
+      <c r="M356" s="6"/>
+    </row>
+    <row r="357" spans="1:13">
       <c r="A357" s="2"/>
       <c r="B357" s="3"/>
       <c r="F357" s="4"/>
@@ -5218,9 +5615,10 @@
       <c r="I357" s="5"/>
       <c r="J357" s="5"/>
       <c r="K357" s="5"/>
-      <c r="L357" s="6"/>
-    </row>
-    <row r="358" spans="1:12">
+      <c r="L357" s="5"/>
+      <c r="M357" s="6"/>
+    </row>
+    <row r="358" spans="1:13">
       <c r="A358" s="2"/>
       <c r="B358" s="3"/>
       <c r="F358" s="4"/>
@@ -5229,9 +5627,10 @@
       <c r="I358" s="5"/>
       <c r="J358" s="5"/>
       <c r="K358" s="5"/>
-      <c r="L358" s="6"/>
-    </row>
-    <row r="359" spans="1:12">
+      <c r="L358" s="5"/>
+      <c r="M358" s="6"/>
+    </row>
+    <row r="359" spans="1:13">
       <c r="A359" s="2"/>
       <c r="B359" s="3"/>
       <c r="F359" s="4"/>
@@ -5240,9 +5639,10 @@
       <c r="I359" s="5"/>
       <c r="J359" s="5"/>
       <c r="K359" s="5"/>
-      <c r="L359" s="6"/>
-    </row>
-    <row r="360" spans="1:12">
+      <c r="L359" s="5"/>
+      <c r="M359" s="6"/>
+    </row>
+    <row r="360" spans="1:13">
       <c r="A360" s="2"/>
       <c r="B360" s="3"/>
       <c r="F360" s="4"/>
@@ -5251,9 +5651,10 @@
       <c r="I360" s="5"/>
       <c r="J360" s="5"/>
       <c r="K360" s="5"/>
-      <c r="L360" s="6"/>
-    </row>
-    <row r="361" spans="1:12">
+      <c r="L360" s="5"/>
+      <c r="M360" s="6"/>
+    </row>
+    <row r="361" spans="1:13">
       <c r="A361" s="2"/>
       <c r="B361" s="3"/>
       <c r="F361" s="4"/>
@@ -5262,9 +5663,10 @@
       <c r="I361" s="5"/>
       <c r="J361" s="5"/>
       <c r="K361" s="5"/>
-      <c r="L361" s="6"/>
-    </row>
-    <row r="362" spans="1:12">
+      <c r="L361" s="5"/>
+      <c r="M361" s="6"/>
+    </row>
+    <row r="362" spans="1:13">
       <c r="A362" s="2"/>
       <c r="B362" s="3"/>
       <c r="F362" s="4"/>
@@ -5273,9 +5675,10 @@
       <c r="I362" s="5"/>
       <c r="J362" s="5"/>
       <c r="K362" s="5"/>
-      <c r="L362" s="6"/>
-    </row>
-    <row r="363" spans="1:12">
+      <c r="L362" s="5"/>
+      <c r="M362" s="6"/>
+    </row>
+    <row r="363" spans="1:13">
       <c r="A363" s="2"/>
       <c r="B363" s="3"/>
       <c r="F363" s="4"/>
@@ -5284,9 +5687,10 @@
       <c r="I363" s="5"/>
       <c r="J363" s="5"/>
       <c r="K363" s="5"/>
-      <c r="L363" s="6"/>
-    </row>
-    <row r="364" spans="1:12">
+      <c r="L363" s="5"/>
+      <c r="M363" s="6"/>
+    </row>
+    <row r="364" spans="1:13">
       <c r="A364" s="2"/>
       <c r="B364" s="3"/>
       <c r="F364" s="4"/>
@@ -5295,9 +5699,10 @@
       <c r="I364" s="5"/>
       <c r="J364" s="5"/>
       <c r="K364" s="5"/>
-      <c r="L364" s="6"/>
-    </row>
-    <row r="365" spans="1:12">
+      <c r="L364" s="5"/>
+      <c r="M364" s="6"/>
+    </row>
+    <row r="365" spans="1:13">
       <c r="A365" s="2"/>
       <c r="B365" s="3"/>
       <c r="F365" s="4"/>
@@ -5306,9 +5711,10 @@
       <c r="I365" s="5"/>
       <c r="J365" s="5"/>
       <c r="K365" s="5"/>
-      <c r="L365" s="6"/>
-    </row>
-    <row r="366" spans="1:12">
+      <c r="L365" s="5"/>
+      <c r="M365" s="6"/>
+    </row>
+    <row r="366" spans="1:13">
       <c r="A366" s="2"/>
       <c r="B366" s="3"/>
       <c r="F366" s="4"/>
@@ -5317,9 +5723,10 @@
       <c r="I366" s="5"/>
       <c r="J366" s="5"/>
       <c r="K366" s="5"/>
-      <c r="L366" s="6"/>
-    </row>
-    <row r="367" spans="1:12">
+      <c r="L366" s="5"/>
+      <c r="M366" s="6"/>
+    </row>
+    <row r="367" spans="1:13">
       <c r="A367" s="2"/>
       <c r="B367" s="3"/>
       <c r="F367" s="4"/>
@@ -5328,9 +5735,10 @@
       <c r="I367" s="5"/>
       <c r="J367" s="5"/>
       <c r="K367" s="5"/>
-      <c r="L367" s="6"/>
-    </row>
-    <row r="368" spans="1:12">
+      <c r="L367" s="5"/>
+      <c r="M367" s="6"/>
+    </row>
+    <row r="368" spans="1:13">
       <c r="A368" s="2"/>
       <c r="B368" s="3"/>
       <c r="F368" s="4"/>
@@ -5339,9 +5747,10 @@
       <c r="I368" s="5"/>
       <c r="J368" s="5"/>
       <c r="K368" s="5"/>
-      <c r="L368" s="6"/>
-    </row>
-    <row r="369" spans="1:12">
+      <c r="L368" s="5"/>
+      <c r="M368" s="6"/>
+    </row>
+    <row r="369" spans="1:13">
       <c r="A369" s="2"/>
       <c r="B369" s="3"/>
       <c r="F369" s="4"/>
@@ -5350,9 +5759,10 @@
       <c r="I369" s="5"/>
       <c r="J369" s="5"/>
       <c r="K369" s="5"/>
-      <c r="L369" s="6"/>
-    </row>
-    <row r="370" spans="1:12">
+      <c r="L369" s="5"/>
+      <c r="M369" s="6"/>
+    </row>
+    <row r="370" spans="1:13">
       <c r="A370" s="2"/>
       <c r="B370" s="3"/>
       <c r="F370" s="4"/>
@@ -5361,9 +5771,10 @@
       <c r="I370" s="5"/>
       <c r="J370" s="5"/>
       <c r="K370" s="5"/>
-      <c r="L370" s="6"/>
-    </row>
-    <row r="371" spans="1:12">
+      <c r="L370" s="5"/>
+      <c r="M370" s="6"/>
+    </row>
+    <row r="371" spans="1:13">
       <c r="A371" s="2"/>
       <c r="B371" s="3"/>
       <c r="F371" s="4"/>
@@ -5372,9 +5783,10 @@
       <c r="I371" s="5"/>
       <c r="J371" s="5"/>
       <c r="K371" s="5"/>
-      <c r="L371" s="6"/>
-    </row>
-    <row r="372" spans="1:12">
+      <c r="L371" s="5"/>
+      <c r="M371" s="6"/>
+    </row>
+    <row r="372" spans="1:13">
       <c r="A372" s="2"/>
       <c r="B372" s="3"/>
       <c r="F372" s="4"/>
@@ -5383,9 +5795,10 @@
       <c r="I372" s="5"/>
       <c r="J372" s="5"/>
       <c r="K372" s="5"/>
-      <c r="L372" s="6"/>
-    </row>
-    <row r="373" spans="1:12">
+      <c r="L372" s="5"/>
+      <c r="M372" s="6"/>
+    </row>
+    <row r="373" spans="1:13">
       <c r="A373" s="2"/>
       <c r="B373" s="3"/>
       <c r="F373" s="4"/>
@@ -5394,9 +5807,10 @@
       <c r="I373" s="5"/>
       <c r="J373" s="5"/>
       <c r="K373" s="5"/>
-      <c r="L373" s="6"/>
-    </row>
-    <row r="374" spans="1:12">
+      <c r="L373" s="5"/>
+      <c r="M373" s="6"/>
+    </row>
+    <row r="374" spans="1:13">
       <c r="A374" s="2"/>
       <c r="B374" s="3"/>
       <c r="F374" s="4"/>
@@ -5405,9 +5819,10 @@
       <c r="I374" s="5"/>
       <c r="J374" s="5"/>
       <c r="K374" s="5"/>
-      <c r="L374" s="6"/>
-    </row>
-    <row r="375" spans="1:12">
+      <c r="L374" s="5"/>
+      <c r="M374" s="6"/>
+    </row>
+    <row r="375" spans="1:13">
       <c r="A375" s="2"/>
       <c r="B375" s="3"/>
       <c r="F375" s="4"/>
@@ -5416,9 +5831,10 @@
       <c r="I375" s="5"/>
       <c r="J375" s="5"/>
       <c r="K375" s="5"/>
-      <c r="L375" s="6"/>
-    </row>
-    <row r="376" spans="1:12">
+      <c r="L375" s="5"/>
+      <c r="M375" s="6"/>
+    </row>
+    <row r="376" spans="1:13">
       <c r="A376" s="2"/>
       <c r="B376" s="3"/>
       <c r="F376" s="4"/>
@@ -5427,9 +5843,10 @@
       <c r="I376" s="5"/>
       <c r="J376" s="5"/>
       <c r="K376" s="5"/>
-      <c r="L376" s="6"/>
-    </row>
-    <row r="377" spans="1:12">
+      <c r="L376" s="5"/>
+      <c r="M376" s="6"/>
+    </row>
+    <row r="377" spans="1:13">
       <c r="A377" s="2"/>
       <c r="B377" s="3"/>
       <c r="F377" s="4"/>
@@ -5438,9 +5855,10 @@
       <c r="I377" s="5"/>
       <c r="J377" s="5"/>
       <c r="K377" s="5"/>
-      <c r="L377" s="6"/>
-    </row>
-    <row r="378" spans="1:12">
+      <c r="L377" s="5"/>
+      <c r="M377" s="6"/>
+    </row>
+    <row r="378" spans="1:13">
       <c r="A378" s="2"/>
       <c r="B378" s="3"/>
       <c r="F378" s="4"/>
@@ -5449,9 +5867,10 @@
       <c r="I378" s="5"/>
       <c r="J378" s="5"/>
       <c r="K378" s="5"/>
-      <c r="L378" s="6"/>
-    </row>
-    <row r="379" spans="1:12">
+      <c r="L378" s="5"/>
+      <c r="M378" s="6"/>
+    </row>
+    <row r="379" spans="1:13">
       <c r="A379" s="2"/>
       <c r="B379" s="3"/>
       <c r="F379" s="4"/>
@@ -5460,9 +5879,10 @@
       <c r="I379" s="5"/>
       <c r="J379" s="5"/>
       <c r="K379" s="5"/>
-      <c r="L379" s="6"/>
-    </row>
-    <row r="380" spans="1:12">
+      <c r="L379" s="5"/>
+      <c r="M379" s="6"/>
+    </row>
+    <row r="380" spans="1:13">
       <c r="A380" s="2"/>
       <c r="B380" s="3"/>
       <c r="F380" s="4"/>
@@ -5471,9 +5891,10 @@
       <c r="I380" s="5"/>
       <c r="J380" s="5"/>
       <c r="K380" s="5"/>
-      <c r="L380" s="6"/>
-    </row>
-    <row r="381" spans="1:12">
+      <c r="L380" s="5"/>
+      <c r="M380" s="6"/>
+    </row>
+    <row r="381" spans="1:13">
       <c r="A381" s="2"/>
       <c r="B381" s="3"/>
       <c r="F381" s="4"/>
@@ -5482,9 +5903,10 @@
       <c r="I381" s="5"/>
       <c r="J381" s="5"/>
       <c r="K381" s="5"/>
-      <c r="L381" s="6"/>
-    </row>
-    <row r="382" spans="1:12">
+      <c r="L381" s="5"/>
+      <c r="M381" s="6"/>
+    </row>
+    <row r="382" spans="1:13">
       <c r="A382" s="2"/>
       <c r="B382" s="3"/>
       <c r="F382" s="4"/>
@@ -5493,9 +5915,10 @@
       <c r="I382" s="5"/>
       <c r="J382" s="5"/>
       <c r="K382" s="5"/>
-      <c r="L382" s="6"/>
-    </row>
-    <row r="383" spans="1:12">
+      <c r="L382" s="5"/>
+      <c r="M382" s="6"/>
+    </row>
+    <row r="383" spans="1:13">
       <c r="A383" s="2"/>
       <c r="B383" s="3"/>
       <c r="F383" s="4"/>
@@ -5504,9 +5927,10 @@
       <c r="I383" s="5"/>
       <c r="J383" s="5"/>
       <c r="K383" s="5"/>
-      <c r="L383" s="6"/>
-    </row>
-    <row r="384" spans="1:12">
+      <c r="L383" s="5"/>
+      <c r="M383" s="6"/>
+    </row>
+    <row r="384" spans="1:13">
       <c r="A384" s="2"/>
       <c r="B384" s="3"/>
       <c r="F384" s="4"/>
@@ -5515,9 +5939,10 @@
       <c r="I384" s="5"/>
       <c r="J384" s="5"/>
       <c r="K384" s="5"/>
-      <c r="L384" s="6"/>
-    </row>
-    <row r="385" spans="1:12">
+      <c r="L384" s="5"/>
+      <c r="M384" s="6"/>
+    </row>
+    <row r="385" spans="1:13">
       <c r="A385" s="2"/>
       <c r="B385" s="3"/>
       <c r="F385" s="4"/>
@@ -5526,9 +5951,10 @@
       <c r="I385" s="5"/>
       <c r="J385" s="5"/>
       <c r="K385" s="5"/>
-      <c r="L385" s="6"/>
-    </row>
-    <row r="386" spans="1:12">
+      <c r="L385" s="5"/>
+      <c r="M385" s="6"/>
+    </row>
+    <row r="386" spans="1:13">
       <c r="A386" s="2"/>
       <c r="B386" s="3"/>
       <c r="F386" s="4"/>
@@ -5537,9 +5963,10 @@
       <c r="I386" s="5"/>
       <c r="J386" s="5"/>
       <c r="K386" s="5"/>
-      <c r="L386" s="6"/>
-    </row>
-    <row r="387" spans="1:12">
+      <c r="L386" s="5"/>
+      <c r="M386" s="6"/>
+    </row>
+    <row r="387" spans="1:13">
       <c r="A387" s="2"/>
       <c r="B387" s="3"/>
       <c r="F387" s="4"/>
@@ -5548,9 +5975,10 @@
       <c r="I387" s="5"/>
       <c r="J387" s="5"/>
       <c r="K387" s="5"/>
-      <c r="L387" s="6"/>
-    </row>
-    <row r="388" spans="1:12">
+      <c r="L387" s="5"/>
+      <c r="M387" s="6"/>
+    </row>
+    <row r="388" spans="1:13">
       <c r="A388" s="2"/>
       <c r="B388" s="3"/>
       <c r="F388" s="4"/>
@@ -5559,9 +5987,10 @@
       <c r="I388" s="5"/>
       <c r="J388" s="5"/>
       <c r="K388" s="5"/>
-      <c r="L388" s="6"/>
-    </row>
-    <row r="389" spans="1:12">
+      <c r="L388" s="5"/>
+      <c r="M388" s="6"/>
+    </row>
+    <row r="389" spans="1:13">
       <c r="A389" s="2"/>
       <c r="B389" s="3"/>
       <c r="F389" s="4"/>
@@ -5570,9 +5999,10 @@
       <c r="I389" s="5"/>
       <c r="J389" s="5"/>
       <c r="K389" s="5"/>
-      <c r="L389" s="6"/>
-    </row>
-    <row r="390" spans="1:12">
+      <c r="L389" s="5"/>
+      <c r="M389" s="6"/>
+    </row>
+    <row r="390" spans="1:13">
       <c r="A390" s="2"/>
       <c r="B390" s="3"/>
       <c r="F390" s="4"/>
@@ -5581,9 +6011,10 @@
       <c r="I390" s="5"/>
       <c r="J390" s="5"/>
       <c r="K390" s="5"/>
-      <c r="L390" s="6"/>
-    </row>
-    <row r="391" spans="1:12">
+      <c r="L390" s="5"/>
+      <c r="M390" s="6"/>
+    </row>
+    <row r="391" spans="1:13">
       <c r="A391" s="2"/>
       <c r="B391" s="3"/>
       <c r="F391" s="4"/>
@@ -5592,9 +6023,10 @@
       <c r="I391" s="5"/>
       <c r="J391" s="5"/>
       <c r="K391" s="5"/>
-      <c r="L391" s="6"/>
-    </row>
-    <row r="392" spans="1:12">
+      <c r="L391" s="5"/>
+      <c r="M391" s="6"/>
+    </row>
+    <row r="392" spans="1:13">
       <c r="A392" s="2"/>
       <c r="B392" s="3"/>
       <c r="F392" s="4"/>
@@ -5603,9 +6035,10 @@
       <c r="I392" s="5"/>
       <c r="J392" s="5"/>
       <c r="K392" s="5"/>
-      <c r="L392" s="6"/>
-    </row>
-    <row r="393" spans="1:12">
+      <c r="L392" s="5"/>
+      <c r="M392" s="6"/>
+    </row>
+    <row r="393" spans="1:13">
       <c r="A393" s="2"/>
       <c r="B393" s="3"/>
       <c r="F393" s="4"/>
@@ -5614,9 +6047,10 @@
       <c r="I393" s="5"/>
       <c r="J393" s="5"/>
       <c r="K393" s="5"/>
-      <c r="L393" s="6"/>
-    </row>
-    <row r="394" spans="1:12">
+      <c r="L393" s="5"/>
+      <c r="M393" s="6"/>
+    </row>
+    <row r="394" spans="1:13">
       <c r="A394" s="2"/>
       <c r="B394" s="3"/>
       <c r="F394" s="4"/>
@@ -5625,9 +6059,10 @@
       <c r="I394" s="5"/>
       <c r="J394" s="5"/>
       <c r="K394" s="5"/>
-      <c r="L394" s="6"/>
-    </row>
-    <row r="395" spans="1:12">
+      <c r="L394" s="5"/>
+      <c r="M394" s="6"/>
+    </row>
+    <row r="395" spans="1:13">
       <c r="A395" s="2"/>
       <c r="B395" s="3"/>
       <c r="F395" s="4"/>
@@ -5636,9 +6071,10 @@
       <c r="I395" s="5"/>
       <c r="J395" s="5"/>
       <c r="K395" s="5"/>
-      <c r="L395" s="6"/>
-    </row>
-    <row r="396" spans="1:12">
+      <c r="L395" s="5"/>
+      <c r="M395" s="6"/>
+    </row>
+    <row r="396" spans="1:13">
       <c r="A396" s="2"/>
       <c r="B396" s="3"/>
       <c r="F396" s="4"/>
@@ -5647,9 +6083,10 @@
       <c r="I396" s="5"/>
       <c r="J396" s="5"/>
       <c r="K396" s="5"/>
-      <c r="L396" s="6"/>
-    </row>
-    <row r="397" spans="1:12">
+      <c r="L396" s="5"/>
+      <c r="M396" s="6"/>
+    </row>
+    <row r="397" spans="1:13">
       <c r="A397" s="2"/>
       <c r="B397" s="3"/>
       <c r="F397" s="4"/>
@@ -5658,9 +6095,10 @@
       <c r="I397" s="5"/>
       <c r="J397" s="5"/>
       <c r="K397" s="5"/>
-      <c r="L397" s="6"/>
-    </row>
-    <row r="398" spans="1:12">
+      <c r="L397" s="5"/>
+      <c r="M397" s="6"/>
+    </row>
+    <row r="398" spans="1:13">
       <c r="A398" s="2"/>
       <c r="B398" s="3"/>
       <c r="F398" s="4"/>
@@ -5669,9 +6107,10 @@
       <c r="I398" s="5"/>
       <c r="J398" s="5"/>
       <c r="K398" s="5"/>
-      <c r="L398" s="6"/>
-    </row>
-    <row r="399" spans="1:12">
+      <c r="L398" s="5"/>
+      <c r="M398" s="6"/>
+    </row>
+    <row r="399" spans="1:13">
       <c r="A399" s="2"/>
       <c r="B399" s="3"/>
       <c r="F399" s="4"/>
@@ -5680,9 +6119,10 @@
       <c r="I399" s="5"/>
       <c r="J399" s="5"/>
       <c r="K399" s="5"/>
-      <c r="L399" s="6"/>
-    </row>
-    <row r="400" spans="1:12">
+      <c r="L399" s="5"/>
+      <c r="M399" s="6"/>
+    </row>
+    <row r="400" spans="1:13">
       <c r="A400" s="2"/>
       <c r="B400" s="3"/>
       <c r="F400" s="4"/>
@@ -5691,9 +6131,10 @@
       <c r="I400" s="5"/>
       <c r="J400" s="5"/>
       <c r="K400" s="5"/>
-      <c r="L400" s="6"/>
-    </row>
-    <row r="401" spans="1:12">
+      <c r="L400" s="5"/>
+      <c r="M400" s="6"/>
+    </row>
+    <row r="401" spans="1:13">
       <c r="A401" s="2"/>
       <c r="B401" s="3"/>
       <c r="F401" s="4"/>
@@ -5702,9 +6143,10 @@
       <c r="I401" s="5"/>
       <c r="J401" s="5"/>
       <c r="K401" s="5"/>
-      <c r="L401" s="6"/>
-    </row>
-    <row r="402" spans="1:12">
+      <c r="L401" s="5"/>
+      <c r="M401" s="6"/>
+    </row>
+    <row r="402" spans="1:13">
       <c r="A402" s="2"/>
       <c r="B402" s="3"/>
       <c r="F402" s="4"/>
@@ -5713,9 +6155,10 @@
       <c r="I402" s="5"/>
       <c r="J402" s="5"/>
       <c r="K402" s="5"/>
-      <c r="L402" s="6"/>
-    </row>
-    <row r="403" spans="1:12">
+      <c r="L402" s="5"/>
+      <c r="M402" s="6"/>
+    </row>
+    <row r="403" spans="1:13">
       <c r="A403" s="2"/>
       <c r="B403" s="3"/>
       <c r="F403" s="4"/>
@@ -5724,9 +6167,10 @@
       <c r="I403" s="5"/>
       <c r="J403" s="5"/>
       <c r="K403" s="5"/>
-      <c r="L403" s="6"/>
-    </row>
-    <row r="404" spans="1:12">
+      <c r="L403" s="5"/>
+      <c r="M403" s="6"/>
+    </row>
+    <row r="404" spans="1:13">
       <c r="A404" s="2"/>
       <c r="B404" s="3"/>
       <c r="F404" s="4"/>
@@ -5735,9 +6179,10 @@
       <c r="I404" s="5"/>
       <c r="J404" s="5"/>
       <c r="K404" s="5"/>
-      <c r="L404" s="6"/>
-    </row>
-    <row r="405" spans="1:12">
+      <c r="L404" s="5"/>
+      <c r="M404" s="6"/>
+    </row>
+    <row r="405" spans="1:13">
       <c r="A405" s="2"/>
       <c r="B405" s="3"/>
       <c r="F405" s="4"/>
@@ -5746,9 +6191,10 @@
       <c r="I405" s="5"/>
       <c r="J405" s="5"/>
       <c r="K405" s="5"/>
-      <c r="L405" s="6"/>
-    </row>
-    <row r="406" spans="1:12">
+      <c r="L405" s="5"/>
+      <c r="M405" s="6"/>
+    </row>
+    <row r="406" spans="1:13">
       <c r="A406" s="2"/>
       <c r="B406" s="3"/>
       <c r="F406" s="4"/>
@@ -5757,9 +6203,10 @@
       <c r="I406" s="5"/>
       <c r="J406" s="5"/>
       <c r="K406" s="5"/>
-      <c r="L406" s="6"/>
-    </row>
-    <row r="407" spans="1:12">
+      <c r="L406" s="5"/>
+      <c r="M406" s="6"/>
+    </row>
+    <row r="407" spans="1:13">
       <c r="A407" s="2"/>
       <c r="B407" s="3"/>
       <c r="F407" s="4"/>
@@ -5768,9 +6215,10 @@
       <c r="I407" s="5"/>
       <c r="J407" s="5"/>
       <c r="K407" s="5"/>
-      <c r="L407" s="6"/>
-    </row>
-    <row r="408" spans="1:12">
+      <c r="L407" s="5"/>
+      <c r="M407" s="6"/>
+    </row>
+    <row r="408" spans="1:13">
       <c r="A408" s="2"/>
       <c r="B408" s="3"/>
       <c r="F408" s="4"/>
@@ -5779,9 +6227,10 @@
       <c r="I408" s="5"/>
       <c r="J408" s="5"/>
       <c r="K408" s="5"/>
-      <c r="L408" s="6"/>
-    </row>
-    <row r="409" spans="1:12">
+      <c r="L408" s="5"/>
+      <c r="M408" s="6"/>
+    </row>
+    <row r="409" spans="1:13">
       <c r="A409" s="2"/>
       <c r="B409" s="3"/>
       <c r="F409" s="4"/>
@@ -5790,9 +6239,10 @@
       <c r="I409" s="5"/>
       <c r="J409" s="5"/>
       <c r="K409" s="5"/>
-      <c r="L409" s="6"/>
-    </row>
-    <row r="410" spans="1:12">
+      <c r="L409" s="5"/>
+      <c r="M409" s="6"/>
+    </row>
+    <row r="410" spans="1:13">
       <c r="A410" s="2"/>
       <c r="B410" s="3"/>
       <c r="F410" s="4"/>
@@ -5801,9 +6251,10 @@
       <c r="I410" s="5"/>
       <c r="J410" s="5"/>
       <c r="K410" s="5"/>
-      <c r="L410" s="6"/>
-    </row>
-    <row r="411" spans="1:12">
+      <c r="L410" s="5"/>
+      <c r="M410" s="6"/>
+    </row>
+    <row r="411" spans="1:13">
       <c r="A411" s="2"/>
       <c r="B411" s="3"/>
       <c r="F411" s="4"/>
@@ -5812,9 +6263,10 @@
       <c r="I411" s="5"/>
       <c r="J411" s="5"/>
       <c r="K411" s="5"/>
-      <c r="L411" s="6"/>
-    </row>
-    <row r="412" spans="1:12">
+      <c r="L411" s="5"/>
+      <c r="M411" s="6"/>
+    </row>
+    <row r="412" spans="1:13">
       <c r="A412" s="2"/>
       <c r="B412" s="3"/>
       <c r="F412" s="4"/>
@@ -5823,9 +6275,10 @@
       <c r="I412" s="5"/>
       <c r="J412" s="5"/>
       <c r="K412" s="5"/>
-      <c r="L412" s="6"/>
-    </row>
-    <row r="413" spans="1:12">
+      <c r="L412" s="5"/>
+      <c r="M412" s="6"/>
+    </row>
+    <row r="413" spans="1:13">
       <c r="A413" s="2"/>
       <c r="B413" s="3"/>
       <c r="F413" s="4"/>
@@ -5834,9 +6287,10 @@
       <c r="I413" s="5"/>
       <c r="J413" s="5"/>
       <c r="K413" s="5"/>
-      <c r="L413" s="6"/>
-    </row>
-    <row r="414" spans="1:12">
+      <c r="L413" s="5"/>
+      <c r="M413" s="6"/>
+    </row>
+    <row r="414" spans="1:13">
       <c r="A414" s="2"/>
       <c r="B414" s="3"/>
       <c r="F414" s="4"/>
@@ -5845,9 +6299,10 @@
       <c r="I414" s="5"/>
       <c r="J414" s="5"/>
       <c r="K414" s="5"/>
-      <c r="L414" s="6"/>
-    </row>
-    <row r="415" spans="1:12">
+      <c r="L414" s="5"/>
+      <c r="M414" s="6"/>
+    </row>
+    <row r="415" spans="1:13">
       <c r="A415" s="2"/>
       <c r="B415" s="3"/>
       <c r="F415" s="4"/>
@@ -5856,9 +6311,10 @@
       <c r="I415" s="5"/>
       <c r="J415" s="5"/>
       <c r="K415" s="5"/>
-      <c r="L415" s="6"/>
-    </row>
-    <row r="416" spans="1:12">
+      <c r="L415" s="5"/>
+      <c r="M415" s="6"/>
+    </row>
+    <row r="416" spans="1:13">
       <c r="A416" s="2"/>
       <c r="B416" s="3"/>
       <c r="F416" s="4"/>
@@ -5867,9 +6323,10 @@
       <c r="I416" s="5"/>
       <c r="J416" s="5"/>
       <c r="K416" s="5"/>
-      <c r="L416" s="6"/>
-    </row>
-    <row r="417" spans="1:12">
+      <c r="L416" s="5"/>
+      <c r="M416" s="6"/>
+    </row>
+    <row r="417" spans="1:13">
       <c r="A417" s="2"/>
       <c r="B417" s="3"/>
       <c r="F417" s="4"/>
@@ -5878,9 +6335,10 @@
       <c r="I417" s="5"/>
       <c r="J417" s="5"/>
       <c r="K417" s="5"/>
-      <c r="L417" s="6"/>
-    </row>
-    <row r="418" spans="1:12">
+      <c r="L417" s="5"/>
+      <c r="M417" s="6"/>
+    </row>
+    <row r="418" spans="1:13">
       <c r="A418" s="2"/>
       <c r="B418" s="3"/>
       <c r="F418" s="4"/>
@@ -5889,9 +6347,10 @@
       <c r="I418" s="5"/>
       <c r="J418" s="5"/>
       <c r="K418" s="5"/>
-      <c r="L418" s="6"/>
-    </row>
-    <row r="419" spans="1:12">
+      <c r="L418" s="5"/>
+      <c r="M418" s="6"/>
+    </row>
+    <row r="419" spans="1:13">
       <c r="A419" s="2"/>
       <c r="B419" s="3"/>
       <c r="F419" s="4"/>
@@ -5900,9 +6359,10 @@
       <c r="I419" s="5"/>
       <c r="J419" s="5"/>
       <c r="K419" s="5"/>
-      <c r="L419" s="6"/>
-    </row>
-    <row r="420" spans="1:12">
+      <c r="L419" s="5"/>
+      <c r="M419" s="6"/>
+    </row>
+    <row r="420" spans="1:13">
       <c r="A420" s="2"/>
       <c r="B420" s="3"/>
       <c r="F420" s="4"/>
@@ -5911,9 +6371,10 @@
       <c r="I420" s="5"/>
       <c r="J420" s="5"/>
       <c r="K420" s="5"/>
-      <c r="L420" s="6"/>
-    </row>
-    <row r="421" spans="1:12">
+      <c r="L420" s="5"/>
+      <c r="M420" s="6"/>
+    </row>
+    <row r="421" spans="1:13">
       <c r="A421" s="2"/>
       <c r="B421" s="3"/>
       <c r="F421" s="4"/>
@@ -5922,9 +6383,10 @@
       <c r="I421" s="5"/>
       <c r="J421" s="5"/>
       <c r="K421" s="5"/>
-      <c r="L421" s="6"/>
-    </row>
-    <row r="422" spans="1:12">
+      <c r="L421" s="5"/>
+      <c r="M421" s="6"/>
+    </row>
+    <row r="422" spans="1:13">
       <c r="A422" s="2"/>
       <c r="B422" s="3"/>
       <c r="F422" s="4"/>
@@ -5933,9 +6395,10 @@
       <c r="I422" s="5"/>
       <c r="J422" s="5"/>
       <c r="K422" s="5"/>
-      <c r="L422" s="6"/>
-    </row>
-    <row r="423" spans="1:12">
+      <c r="L422" s="5"/>
+      <c r="M422" s="6"/>
+    </row>
+    <row r="423" spans="1:13">
       <c r="A423" s="2"/>
       <c r="B423" s="3"/>
       <c r="F423" s="4"/>
@@ -5944,9 +6407,10 @@
       <c r="I423" s="5"/>
       <c r="J423" s="5"/>
       <c r="K423" s="5"/>
-      <c r="L423" s="6"/>
-    </row>
-    <row r="424" spans="1:12">
+      <c r="L423" s="5"/>
+      <c r="M423" s="6"/>
+    </row>
+    <row r="424" spans="1:13">
       <c r="A424" s="2"/>
       <c r="B424" s="3"/>
       <c r="F424" s="4"/>
@@ -5955,9 +6419,10 @@
       <c r="I424" s="5"/>
       <c r="J424" s="5"/>
       <c r="K424" s="5"/>
-      <c r="L424" s="6"/>
-    </row>
-    <row r="425" spans="1:12">
+      <c r="L424" s="5"/>
+      <c r="M424" s="6"/>
+    </row>
+    <row r="425" spans="1:13">
       <c r="A425" s="2"/>
       <c r="B425" s="3"/>
       <c r="F425" s="4"/>
@@ -5966,9 +6431,10 @@
       <c r="I425" s="5"/>
       <c r="J425" s="5"/>
       <c r="K425" s="5"/>
-      <c r="L425" s="6"/>
-    </row>
-    <row r="426" spans="1:12">
+      <c r="L425" s="5"/>
+      <c r="M425" s="6"/>
+    </row>
+    <row r="426" spans="1:13">
       <c r="A426" s="2"/>
       <c r="B426" s="3"/>
       <c r="F426" s="4"/>
@@ -5977,9 +6443,10 @@
       <c r="I426" s="5"/>
       <c r="J426" s="5"/>
       <c r="K426" s="5"/>
-      <c r="L426" s="6"/>
-    </row>
-    <row r="427" spans="1:12">
+      <c r="L426" s="5"/>
+      <c r="M426" s="6"/>
+    </row>
+    <row r="427" spans="1:13">
       <c r="A427" s="2"/>
       <c r="B427" s="3"/>
       <c r="F427" s="4"/>
@@ -5988,9 +6455,10 @@
       <c r="I427" s="5"/>
       <c r="J427" s="5"/>
       <c r="K427" s="5"/>
-      <c r="L427" s="6"/>
-    </row>
-    <row r="428" spans="1:12">
+      <c r="L427" s="5"/>
+      <c r="M427" s="6"/>
+    </row>
+    <row r="428" spans="1:13">
       <c r="A428" s="2"/>
       <c r="B428" s="3"/>
       <c r="F428" s="4"/>
@@ -5999,9 +6467,10 @@
       <c r="I428" s="5"/>
       <c r="J428" s="5"/>
       <c r="K428" s="5"/>
-      <c r="L428" s="6"/>
-    </row>
-    <row r="429" spans="1:12">
+      <c r="L428" s="5"/>
+      <c r="M428" s="6"/>
+    </row>
+    <row r="429" spans="1:13">
       <c r="A429" s="2"/>
       <c r="B429" s="3"/>
       <c r="F429" s="4"/>
@@ -6010,9 +6479,10 @@
       <c r="I429" s="5"/>
       <c r="J429" s="5"/>
       <c r="K429" s="5"/>
-      <c r="L429" s="6"/>
-    </row>
-    <row r="430" spans="1:12">
+      <c r="L429" s="5"/>
+      <c r="M429" s="6"/>
+    </row>
+    <row r="430" spans="1:13">
       <c r="A430" s="2"/>
       <c r="B430" s="3"/>
       <c r="F430" s="4"/>
@@ -6021,9 +6491,10 @@
       <c r="I430" s="5"/>
       <c r="J430" s="5"/>
       <c r="K430" s="5"/>
-      <c r="L430" s="6"/>
-    </row>
-    <row r="431" spans="1:12">
+      <c r="L430" s="5"/>
+      <c r="M430" s="6"/>
+    </row>
+    <row r="431" spans="1:13">
       <c r="A431" s="2"/>
       <c r="B431" s="3"/>
       <c r="F431" s="4"/>
@@ -6032,9 +6503,10 @@
       <c r="I431" s="5"/>
       <c r="J431" s="5"/>
       <c r="K431" s="5"/>
-      <c r="L431" s="6"/>
-    </row>
-    <row r="432" spans="1:12">
+      <c r="L431" s="5"/>
+      <c r="M431" s="6"/>
+    </row>
+    <row r="432" spans="1:13">
       <c r="A432" s="2"/>
       <c r="B432" s="3"/>
       <c r="F432" s="4"/>
@@ -6043,9 +6515,10 @@
       <c r="I432" s="5"/>
       <c r="J432" s="5"/>
       <c r="K432" s="5"/>
-      <c r="L432" s="6"/>
-    </row>
-    <row r="433" spans="1:12">
+      <c r="L432" s="5"/>
+      <c r="M432" s="6"/>
+    </row>
+    <row r="433" spans="1:13">
       <c r="A433" s="2"/>
       <c r="B433" s="3"/>
       <c r="F433" s="4"/>
@@ -6054,9 +6527,10 @@
       <c r="I433" s="5"/>
       <c r="J433" s="5"/>
       <c r="K433" s="5"/>
-      <c r="L433" s="6"/>
-    </row>
-    <row r="434" spans="1:12">
+      <c r="L433" s="5"/>
+      <c r="M433" s="6"/>
+    </row>
+    <row r="434" spans="1:13">
       <c r="A434" s="2"/>
       <c r="B434" s="3"/>
       <c r="F434" s="4"/>
@@ -6065,9 +6539,10 @@
       <c r="I434" s="5"/>
       <c r="J434" s="5"/>
       <c r="K434" s="5"/>
-      <c r="L434" s="6"/>
-    </row>
-    <row r="435" spans="1:12">
+      <c r="L434" s="5"/>
+      <c r="M434" s="6"/>
+    </row>
+    <row r="435" spans="1:13">
       <c r="A435" s="2"/>
       <c r="B435" s="3"/>
       <c r="F435" s="4"/>
@@ -6076,9 +6551,10 @@
       <c r="I435" s="5"/>
       <c r="J435" s="5"/>
       <c r="K435" s="5"/>
-      <c r="L435" s="6"/>
-    </row>
-    <row r="436" spans="1:12">
+      <c r="L435" s="5"/>
+      <c r="M435" s="6"/>
+    </row>
+    <row r="436" spans="1:13">
       <c r="A436" s="2"/>
       <c r="B436" s="3"/>
       <c r="F436" s="4"/>
@@ -6087,9 +6563,10 @@
       <c r="I436" s="5"/>
       <c r="J436" s="5"/>
       <c r="K436" s="5"/>
-      <c r="L436" s="6"/>
-    </row>
-    <row r="437" spans="1:12">
+      <c r="L436" s="5"/>
+      <c r="M436" s="6"/>
+    </row>
+    <row r="437" spans="1:13">
       <c r="A437" s="2"/>
       <c r="B437" s="3"/>
       <c r="F437" s="4"/>
@@ -6098,9 +6575,10 @@
       <c r="I437" s="5"/>
       <c r="J437" s="5"/>
       <c r="K437" s="5"/>
-      <c r="L437" s="6"/>
-    </row>
-    <row r="438" spans="1:12">
+      <c r="L437" s="5"/>
+      <c r="M437" s="6"/>
+    </row>
+    <row r="438" spans="1:13">
       <c r="A438" s="2"/>
       <c r="B438" s="3"/>
       <c r="F438" s="4"/>
@@ -6109,9 +6587,10 @@
       <c r="I438" s="5"/>
       <c r="J438" s="5"/>
       <c r="K438" s="5"/>
-      <c r="L438" s="6"/>
-    </row>
-    <row r="439" spans="1:12">
+      <c r="L438" s="5"/>
+      <c r="M438" s="6"/>
+    </row>
+    <row r="439" spans="1:13">
       <c r="A439" s="2"/>
       <c r="B439" s="3"/>
       <c r="F439" s="4"/>
@@ -6120,9 +6599,10 @@
       <c r="I439" s="5"/>
       <c r="J439" s="5"/>
       <c r="K439" s="5"/>
-      <c r="L439" s="6"/>
-    </row>
-    <row r="440" spans="1:12">
+      <c r="L439" s="5"/>
+      <c r="M439" s="6"/>
+    </row>
+    <row r="440" spans="1:13">
       <c r="A440" s="2"/>
       <c r="B440" s="3"/>
       <c r="F440" s="4"/>
@@ -6131,9 +6611,10 @@
       <c r="I440" s="5"/>
       <c r="J440" s="5"/>
       <c r="K440" s="5"/>
-      <c r="L440" s="6"/>
-    </row>
-    <row r="441" spans="1:12">
+      <c r="L440" s="5"/>
+      <c r="M440" s="6"/>
+    </row>
+    <row r="441" spans="1:13">
       <c r="A441" s="2"/>
       <c r="B441" s="3"/>
       <c r="F441" s="4"/>
@@ -6142,9 +6623,10 @@
       <c r="I441" s="5"/>
       <c r="J441" s="5"/>
       <c r="K441" s="5"/>
-      <c r="L441" s="6"/>
-    </row>
-    <row r="442" spans="1:12">
+      <c r="L441" s="5"/>
+      <c r="M441" s="6"/>
+    </row>
+    <row r="442" spans="1:13">
       <c r="A442" s="2"/>
       <c r="B442" s="3"/>
       <c r="F442" s="4"/>
@@ -6153,9 +6635,10 @@
       <c r="I442" s="5"/>
       <c r="J442" s="5"/>
       <c r="K442" s="5"/>
-      <c r="L442" s="6"/>
-    </row>
-    <row r="443" spans="1:12">
+      <c r="L442" s="5"/>
+      <c r="M442" s="6"/>
+    </row>
+    <row r="443" spans="1:13">
       <c r="A443" s="2"/>
       <c r="B443" s="3"/>
       <c r="F443" s="4"/>
@@ -6164,9 +6647,10 @@
       <c r="I443" s="5"/>
       <c r="J443" s="5"/>
       <c r="K443" s="5"/>
-      <c r="L443" s="6"/>
-    </row>
-    <row r="444" spans="1:12">
+      <c r="L443" s="5"/>
+      <c r="M443" s="6"/>
+    </row>
+    <row r="444" spans="1:13">
       <c r="A444" s="2"/>
       <c r="B444" s="3"/>
       <c r="F444" s="4"/>
@@ -6175,9 +6659,10 @@
       <c r="I444" s="5"/>
       <c r="J444" s="5"/>
       <c r="K444" s="5"/>
-      <c r="L444" s="6"/>
-    </row>
-    <row r="445" spans="1:12">
+      <c r="L444" s="5"/>
+      <c r="M444" s="6"/>
+    </row>
+    <row r="445" spans="1:13">
       <c r="A445" s="2"/>
       <c r="B445" s="3"/>
       <c r="F445" s="4"/>
@@ -6186,9 +6671,10 @@
       <c r="I445" s="5"/>
       <c r="J445" s="5"/>
       <c r="K445" s="5"/>
-      <c r="L445" s="6"/>
-    </row>
-    <row r="446" spans="1:12">
+      <c r="L445" s="5"/>
+      <c r="M445" s="6"/>
+    </row>
+    <row r="446" spans="1:13">
       <c r="A446" s="2"/>
       <c r="B446" s="3"/>
       <c r="F446" s="4"/>
@@ -6197,9 +6683,10 @@
       <c r="I446" s="5"/>
       <c r="J446" s="5"/>
       <c r="K446" s="5"/>
-      <c r="L446" s="6"/>
-    </row>
-    <row r="447" spans="1:12">
+      <c r="L446" s="5"/>
+      <c r="M446" s="6"/>
+    </row>
+    <row r="447" spans="1:13">
       <c r="A447" s="2"/>
       <c r="B447" s="3"/>
       <c r="F447" s="4"/>
@@ -6208,9 +6695,10 @@
       <c r="I447" s="5"/>
       <c r="J447" s="5"/>
       <c r="K447" s="5"/>
-      <c r="L447" s="6"/>
-    </row>
-    <row r="448" spans="1:12">
+      <c r="L447" s="5"/>
+      <c r="M447" s="6"/>
+    </row>
+    <row r="448" spans="1:13">
       <c r="A448" s="2"/>
       <c r="B448" s="3"/>
       <c r="F448" s="4"/>
@@ -6219,9 +6707,10 @@
       <c r="I448" s="5"/>
       <c r="J448" s="5"/>
       <c r="K448" s="5"/>
-      <c r="L448" s="6"/>
-    </row>
-    <row r="449" spans="1:12">
+      <c r="L448" s="5"/>
+      <c r="M448" s="6"/>
+    </row>
+    <row r="449" spans="1:13">
       <c r="A449" s="2"/>
       <c r="B449" s="3"/>
       <c r="F449" s="4"/>
@@ -6230,9 +6719,10 @@
       <c r="I449" s="5"/>
       <c r="J449" s="5"/>
       <c r="K449" s="5"/>
-      <c r="L449" s="6"/>
-    </row>
-    <row r="450" spans="1:12">
+      <c r="L449" s="5"/>
+      <c r="M449" s="6"/>
+    </row>
+    <row r="450" spans="1:13">
       <c r="A450" s="2"/>
       <c r="B450" s="3"/>
       <c r="F450" s="4"/>
@@ -6241,9 +6731,10 @@
       <c r="I450" s="5"/>
       <c r="J450" s="5"/>
       <c r="K450" s="5"/>
-      <c r="L450" s="6"/>
-    </row>
-    <row r="451" spans="1:12">
+      <c r="L450" s="5"/>
+      <c r="M450" s="6"/>
+    </row>
+    <row r="451" spans="1:13">
       <c r="A451" s="2"/>
       <c r="B451" s="3"/>
       <c r="F451" s="4"/>
@@ -6252,9 +6743,10 @@
       <c r="I451" s="5"/>
       <c r="J451" s="5"/>
       <c r="K451" s="5"/>
-      <c r="L451" s="6"/>
-    </row>
-    <row r="452" spans="1:12">
+      <c r="L451" s="5"/>
+      <c r="M451" s="6"/>
+    </row>
+    <row r="452" spans="1:13">
       <c r="A452" s="2"/>
       <c r="B452" s="3"/>
       <c r="F452" s="4"/>
@@ -6263,9 +6755,10 @@
       <c r="I452" s="5"/>
       <c r="J452" s="5"/>
       <c r="K452" s="5"/>
-      <c r="L452" s="6"/>
-    </row>
-    <row r="453" spans="1:12">
+      <c r="L452" s="5"/>
+      <c r="M452" s="6"/>
+    </row>
+    <row r="453" spans="1:13">
       <c r="A453" s="2"/>
       <c r="B453" s="3"/>
       <c r="F453" s="4"/>
@@ -6274,9 +6767,10 @@
       <c r="I453" s="5"/>
       <c r="J453" s="5"/>
       <c r="K453" s="5"/>
-      <c r="L453" s="6"/>
-    </row>
-    <row r="454" spans="1:12">
+      <c r="L453" s="5"/>
+      <c r="M453" s="6"/>
+    </row>
+    <row r="454" spans="1:13">
       <c r="A454" s="2"/>
       <c r="B454" s="3"/>
       <c r="F454" s="4"/>
@@ -6285,9 +6779,10 @@
       <c r="I454" s="5"/>
       <c r="J454" s="5"/>
       <c r="K454" s="5"/>
-      <c r="L454" s="6"/>
-    </row>
-    <row r="455" spans="1:12">
+      <c r="L454" s="5"/>
+      <c r="M454" s="6"/>
+    </row>
+    <row r="455" spans="1:13">
       <c r="A455" s="2"/>
       <c r="B455" s="3"/>
       <c r="F455" s="4"/>
@@ -6296,9 +6791,10 @@
       <c r="I455" s="5"/>
       <c r="J455" s="5"/>
       <c r="K455" s="5"/>
-      <c r="L455" s="6"/>
-    </row>
-    <row r="456" spans="1:12">
+      <c r="L455" s="5"/>
+      <c r="M455" s="6"/>
+    </row>
+    <row r="456" spans="1:13">
       <c r="A456" s="2"/>
       <c r="B456" s="3"/>
       <c r="F456" s="4"/>
@@ -6307,9 +6803,10 @@
       <c r="I456" s="5"/>
       <c r="J456" s="5"/>
       <c r="K456" s="5"/>
-      <c r="L456" s="6"/>
-    </row>
-    <row r="457" spans="1:12">
+      <c r="L456" s="5"/>
+      <c r="M456" s="6"/>
+    </row>
+    <row r="457" spans="1:13">
       <c r="A457" s="2"/>
       <c r="B457" s="3"/>
       <c r="F457" s="4"/>
@@ -6318,9 +6815,10 @@
       <c r="I457" s="5"/>
       <c r="J457" s="5"/>
       <c r="K457" s="5"/>
-      <c r="L457" s="6"/>
-    </row>
-    <row r="458" spans="1:12">
+      <c r="L457" s="5"/>
+      <c r="M457" s="6"/>
+    </row>
+    <row r="458" spans="1:13">
       <c r="A458" s="2"/>
       <c r="B458" s="3"/>
       <c r="F458" s="4"/>
@@ -6329,9 +6827,10 @@
       <c r="I458" s="5"/>
       <c r="J458" s="5"/>
       <c r="K458" s="5"/>
-      <c r="L458" s="6"/>
-    </row>
-    <row r="459" spans="1:12">
+      <c r="L458" s="5"/>
+      <c r="M458" s="6"/>
+    </row>
+    <row r="459" spans="1:13">
       <c r="A459" s="2"/>
       <c r="B459" s="3"/>
       <c r="F459" s="4"/>
@@ -6340,9 +6839,10 @@
       <c r="I459" s="5"/>
       <c r="J459" s="5"/>
       <c r="K459" s="5"/>
-      <c r="L459" s="6"/>
-    </row>
-    <row r="460" spans="1:12">
+      <c r="L459" s="5"/>
+      <c r="M459" s="6"/>
+    </row>
+    <row r="460" spans="1:13">
       <c r="A460" s="2"/>
       <c r="B460" s="3"/>
       <c r="F460" s="4"/>
@@ -6351,9 +6851,10 @@
       <c r="I460" s="5"/>
       <c r="J460" s="5"/>
       <c r="K460" s="5"/>
-      <c r="L460" s="6"/>
-    </row>
-    <row r="461" spans="1:12">
+      <c r="L460" s="5"/>
+      <c r="M460" s="6"/>
+    </row>
+    <row r="461" spans="1:13">
       <c r="A461" s="2"/>
       <c r="B461" s="3"/>
       <c r="F461" s="4"/>
@@ -6362,9 +6863,10 @@
       <c r="I461" s="5"/>
       <c r="J461" s="5"/>
       <c r="K461" s="5"/>
-      <c r="L461" s="6"/>
-    </row>
-    <row r="462" spans="1:12">
+      <c r="L461" s="5"/>
+      <c r="M461" s="6"/>
+    </row>
+    <row r="462" spans="1:13">
       <c r="A462" s="2"/>
       <c r="B462" s="3"/>
       <c r="F462" s="4"/>
@@ -6373,9 +6875,10 @@
       <c r="I462" s="5"/>
       <c r="J462" s="5"/>
       <c r="K462" s="5"/>
-      <c r="L462" s="6"/>
-    </row>
-    <row r="463" spans="1:12">
+      <c r="L462" s="5"/>
+      <c r="M462" s="6"/>
+    </row>
+    <row r="463" spans="1:13">
       <c r="A463" s="2"/>
       <c r="B463" s="3"/>
       <c r="F463" s="4"/>
@@ -6384,9 +6887,10 @@
       <c r="I463" s="5"/>
       <c r="J463" s="5"/>
       <c r="K463" s="5"/>
-      <c r="L463" s="6"/>
-    </row>
-    <row r="464" spans="1:12">
+      <c r="L463" s="5"/>
+      <c r="M463" s="6"/>
+    </row>
+    <row r="464" spans="1:13">
       <c r="A464" s="2"/>
       <c r="B464" s="3"/>
       <c r="F464" s="4"/>
@@ -6395,9 +6899,10 @@
       <c r="I464" s="5"/>
       <c r="J464" s="5"/>
       <c r="K464" s="5"/>
-      <c r="L464" s="6"/>
-    </row>
-    <row r="465" spans="1:12">
+      <c r="L464" s="5"/>
+      <c r="M464" s="6"/>
+    </row>
+    <row r="465" spans="1:13">
       <c r="A465" s="2"/>
       <c r="B465" s="3"/>
       <c r="F465" s="4"/>
@@ -6406,9 +6911,10 @@
       <c r="I465" s="5"/>
       <c r="J465" s="5"/>
       <c r="K465" s="5"/>
-      <c r="L465" s="6"/>
-    </row>
-    <row r="466" spans="1:12">
+      <c r="L465" s="5"/>
+      <c r="M465" s="6"/>
+    </row>
+    <row r="466" spans="1:13">
       <c r="A466" s="2"/>
       <c r="B466" s="3"/>
       <c r="F466" s="4"/>
@@ -6417,9 +6923,10 @@
       <c r="I466" s="5"/>
       <c r="J466" s="5"/>
       <c r="K466" s="5"/>
-      <c r="L466" s="6"/>
-    </row>
-    <row r="467" spans="1:12">
+      <c r="L466" s="5"/>
+      <c r="M466" s="6"/>
+    </row>
+    <row r="467" spans="1:13">
       <c r="A467" s="2"/>
       <c r="B467" s="3"/>
       <c r="F467" s="4"/>
@@ -6428,9 +6935,10 @@
       <c r="I467" s="5"/>
       <c r="J467" s="5"/>
       <c r="K467" s="5"/>
-      <c r="L467" s="6"/>
-    </row>
-    <row r="468" spans="1:12">
+      <c r="L467" s="5"/>
+      <c r="M467" s="6"/>
+    </row>
+    <row r="468" spans="1:13">
       <c r="A468" s="2"/>
       <c r="B468" s="3"/>
       <c r="F468" s="4"/>
@@ -6439,9 +6947,10 @@
       <c r="I468" s="5"/>
       <c r="J468" s="5"/>
       <c r="K468" s="5"/>
-      <c r="L468" s="6"/>
-    </row>
-    <row r="469" spans="1:12">
+      <c r="L468" s="5"/>
+      <c r="M468" s="6"/>
+    </row>
+    <row r="469" spans="1:13">
       <c r="A469" s="2"/>
       <c r="B469" s="3"/>
       <c r="F469" s="4"/>
@@ -6450,9 +6959,10 @@
       <c r="I469" s="5"/>
       <c r="J469" s="5"/>
       <c r="K469" s="5"/>
-      <c r="L469" s="6"/>
-    </row>
-    <row r="470" spans="1:12">
+      <c r="L469" s="5"/>
+      <c r="M469" s="6"/>
+    </row>
+    <row r="470" spans="1:13">
       <c r="A470" s="2"/>
       <c r="B470" s="3"/>
       <c r="F470" s="4"/>
@@ -6461,9 +6971,10 @@
       <c r="I470" s="5"/>
       <c r="J470" s="5"/>
       <c r="K470" s="5"/>
-      <c r="L470" s="6"/>
-    </row>
-    <row r="471" spans="1:12">
+      <c r="L470" s="5"/>
+      <c r="M470" s="6"/>
+    </row>
+    <row r="471" spans="1:13">
       <c r="A471" s="2"/>
       <c r="B471" s="3"/>
       <c r="F471" s="4"/>
@@ -6472,9 +6983,10 @@
       <c r="I471" s="5"/>
       <c r="J471" s="5"/>
       <c r="K471" s="5"/>
-      <c r="L471" s="6"/>
-    </row>
-    <row r="472" spans="1:12">
+      <c r="L471" s="5"/>
+      <c r="M471" s="6"/>
+    </row>
+    <row r="472" spans="1:13">
       <c r="A472" s="2"/>
       <c r="B472" s="3"/>
       <c r="F472" s="4"/>
@@ -6483,9 +6995,10 @@
       <c r="I472" s="5"/>
       <c r="J472" s="5"/>
       <c r="K472" s="5"/>
-      <c r="L472" s="6"/>
-    </row>
-    <row r="473" spans="1:12">
+      <c r="L472" s="5"/>
+      <c r="M472" s="6"/>
+    </row>
+    <row r="473" spans="1:13">
       <c r="A473" s="2"/>
       <c r="B473" s="3"/>
       <c r="F473" s="4"/>
@@ -6494,9 +7007,10 @@
       <c r="I473" s="5"/>
       <c r="J473" s="5"/>
       <c r="K473" s="5"/>
-      <c r="L473" s="6"/>
-    </row>
-    <row r="474" spans="1:12">
+      <c r="L473" s="5"/>
+      <c r="M473" s="6"/>
+    </row>
+    <row r="474" spans="1:13">
       <c r="A474" s="2"/>
       <c r="B474" s="3"/>
       <c r="F474" s="4"/>
@@ -6505,9 +7019,10 @@
       <c r="I474" s="5"/>
       <c r="J474" s="5"/>
       <c r="K474" s="5"/>
-      <c r="L474" s="6"/>
-    </row>
-    <row r="475" spans="1:12">
+      <c r="L474" s="5"/>
+      <c r="M474" s="6"/>
+    </row>
+    <row r="475" spans="1:13">
       <c r="A475" s="2"/>
       <c r="B475" s="3"/>
       <c r="F475" s="4"/>
@@ -6516,9 +7031,10 @@
       <c r="I475" s="5"/>
       <c r="J475" s="5"/>
       <c r="K475" s="5"/>
-      <c r="L475" s="6"/>
-    </row>
-    <row r="476" spans="1:12">
+      <c r="L475" s="5"/>
+      <c r="M475" s="6"/>
+    </row>
+    <row r="476" spans="1:13">
       <c r="A476" s="2"/>
       <c r="B476" s="3"/>
       <c r="F476" s="4"/>
@@ -6527,9 +7043,10 @@
       <c r="I476" s="5"/>
       <c r="J476" s="5"/>
       <c r="K476" s="5"/>
-      <c r="L476" s="6"/>
-    </row>
-    <row r="477" spans="1:12">
+      <c r="L476" s="5"/>
+      <c r="M476" s="6"/>
+    </row>
+    <row r="477" spans="1:13">
       <c r="A477" s="2"/>
       <c r="B477" s="3"/>
       <c r="F477" s="4"/>
@@ -6538,9 +7055,10 @@
       <c r="I477" s="5"/>
       <c r="J477" s="5"/>
       <c r="K477" s="5"/>
-      <c r="L477" s="6"/>
-    </row>
-    <row r="478" spans="1:12">
+      <c r="L477" s="5"/>
+      <c r="M477" s="6"/>
+    </row>
+    <row r="478" spans="1:13">
       <c r="A478" s="2"/>
       <c r="B478" s="3"/>
       <c r="F478" s="4"/>
@@ -6549,9 +7067,10 @@
       <c r="I478" s="5"/>
       <c r="J478" s="5"/>
       <c r="K478" s="5"/>
-      <c r="L478" s="6"/>
-    </row>
-    <row r="479" spans="1:12">
+      <c r="L478" s="5"/>
+      <c r="M478" s="6"/>
+    </row>
+    <row r="479" spans="1:13">
       <c r="A479" s="2"/>
       <c r="B479" s="3"/>
       <c r="F479" s="4"/>
@@ -6560,9 +7079,10 @@
       <c r="I479" s="5"/>
       <c r="J479" s="5"/>
       <c r="K479" s="5"/>
-      <c r="L479" s="6"/>
-    </row>
-    <row r="480" spans="1:12">
+      <c r="L479" s="5"/>
+      <c r="M479" s="6"/>
+    </row>
+    <row r="480" spans="1:13">
       <c r="A480" s="2"/>
       <c r="B480" s="3"/>
       <c r="F480" s="4"/>
@@ -6571,9 +7091,10 @@
       <c r="I480" s="5"/>
       <c r="J480" s="5"/>
       <c r="K480" s="5"/>
-      <c r="L480" s="6"/>
-    </row>
-    <row r="481" spans="1:12">
+      <c r="L480" s="5"/>
+      <c r="M480" s="6"/>
+    </row>
+    <row r="481" spans="1:13">
       <c r="A481" s="2"/>
       <c r="B481" s="3"/>
       <c r="F481" s="4"/>
@@ -6582,9 +7103,10 @@
       <c r="I481" s="5"/>
       <c r="J481" s="5"/>
       <c r="K481" s="5"/>
-      <c r="L481" s="6"/>
-    </row>
-    <row r="482" spans="1:12">
+      <c r="L481" s="5"/>
+      <c r="M481" s="6"/>
+    </row>
+    <row r="482" spans="1:13">
       <c r="A482" s="2"/>
       <c r="B482" s="3"/>
       <c r="F482" s="4"/>
@@ -6593,9 +7115,10 @@
       <c r="I482" s="5"/>
       <c r="J482" s="5"/>
       <c r="K482" s="5"/>
-      <c r="L482" s="6"/>
-    </row>
-    <row r="483" spans="1:12">
+      <c r="L482" s="5"/>
+      <c r="M482" s="6"/>
+    </row>
+    <row r="483" spans="1:13">
       <c r="A483" s="2"/>
       <c r="B483" s="3"/>
       <c r="F483" s="4"/>
@@ -6604,9 +7127,10 @@
       <c r="I483" s="5"/>
       <c r="J483" s="5"/>
       <c r="K483" s="5"/>
-      <c r="L483" s="6"/>
-    </row>
-    <row r="484" spans="1:12">
+      <c r="L483" s="5"/>
+      <c r="M483" s="6"/>
+    </row>
+    <row r="484" spans="1:13">
       <c r="A484" s="2"/>
       <c r="B484" s="3"/>
       <c r="F484" s="4"/>
@@ -6615,9 +7139,10 @@
       <c r="I484" s="5"/>
       <c r="J484" s="5"/>
       <c r="K484" s="5"/>
-      <c r="L484" s="6"/>
-    </row>
-    <row r="485" spans="1:12">
+      <c r="L484" s="5"/>
+      <c r="M484" s="6"/>
+    </row>
+    <row r="485" spans="1:13">
       <c r="A485" s="2"/>
       <c r="B485" s="3"/>
       <c r="F485" s="4"/>
@@ -6626,9 +7151,10 @@
       <c r="I485" s="5"/>
       <c r="J485" s="5"/>
       <c r="K485" s="5"/>
-      <c r="L485" s="6"/>
-    </row>
-    <row r="486" spans="1:12">
+      <c r="L485" s="5"/>
+      <c r="M485" s="6"/>
+    </row>
+    <row r="486" spans="1:13">
       <c r="A486" s="2"/>
       <c r="B486" s="3"/>
       <c r="F486" s="4"/>
@@ -6637,9 +7163,10 @@
       <c r="I486" s="5"/>
       <c r="J486" s="5"/>
       <c r="K486" s="5"/>
-      <c r="L486" s="6"/>
-    </row>
-    <row r="487" spans="1:12">
+      <c r="L486" s="5"/>
+      <c r="M486" s="6"/>
+    </row>
+    <row r="487" spans="1:13">
       <c r="A487" s="2"/>
       <c r="B487" s="3"/>
       <c r="F487" s="4"/>
@@ -6648,9 +7175,10 @@
       <c r="I487" s="5"/>
       <c r="J487" s="5"/>
       <c r="K487" s="5"/>
-      <c r="L487" s="6"/>
-    </row>
-    <row r="488" spans="1:12">
+      <c r="L487" s="5"/>
+      <c r="M487" s="6"/>
+    </row>
+    <row r="488" spans="1:13">
       <c r="A488" s="2"/>
       <c r="B488" s="3"/>
       <c r="F488" s="4"/>
@@ -6659,9 +7187,10 @@
       <c r="I488" s="5"/>
       <c r="J488" s="5"/>
       <c r="K488" s="5"/>
-      <c r="L488" s="6"/>
-    </row>
-    <row r="489" spans="1:12">
+      <c r="L488" s="5"/>
+      <c r="M488" s="6"/>
+    </row>
+    <row r="489" spans="1:13">
       <c r="A489" s="2"/>
       <c r="B489" s="3"/>
       <c r="F489" s="4"/>
@@ -6670,9 +7199,10 @@
       <c r="I489" s="5"/>
       <c r="J489" s="5"/>
       <c r="K489" s="5"/>
-      <c r="L489" s="6"/>
-    </row>
-    <row r="490" spans="1:12">
+      <c r="L489" s="5"/>
+      <c r="M489" s="6"/>
+    </row>
+    <row r="490" spans="1:13">
       <c r="A490" s="2"/>
       <c r="B490" s="3"/>
       <c r="F490" s="4"/>
@@ -6681,9 +7211,10 @@
       <c r="I490" s="5"/>
       <c r="J490" s="5"/>
       <c r="K490" s="5"/>
-      <c r="L490" s="6"/>
-    </row>
-    <row r="491" spans="1:12">
+      <c r="L490" s="5"/>
+      <c r="M490" s="6"/>
+    </row>
+    <row r="491" spans="1:13">
       <c r="A491" s="2"/>
       <c r="B491" s="3"/>
       <c r="F491" s="4"/>
@@ -6692,9 +7223,10 @@
       <c r="I491" s="5"/>
       <c r="J491" s="5"/>
       <c r="K491" s="5"/>
-      <c r="L491" s="6"/>
-    </row>
-    <row r="492" spans="1:12">
+      <c r="L491" s="5"/>
+      <c r="M491" s="6"/>
+    </row>
+    <row r="492" spans="1:13">
       <c r="A492" s="2"/>
       <c r="B492" s="3"/>
       <c r="F492" s="4"/>
@@ -6703,9 +7235,10 @@
       <c r="I492" s="5"/>
       <c r="J492" s="5"/>
       <c r="K492" s="5"/>
-      <c r="L492" s="6"/>
-    </row>
-    <row r="493" spans="1:12">
+      <c r="L492" s="5"/>
+      <c r="M492" s="6"/>
+    </row>
+    <row r="493" spans="1:13">
       <c r="A493" s="2"/>
       <c r="B493" s="3"/>
       <c r="F493" s="4"/>
@@ -6714,9 +7247,10 @@
       <c r="I493" s="5"/>
       <c r="J493" s="5"/>
       <c r="K493" s="5"/>
-      <c r="L493" s="6"/>
-    </row>
-    <row r="494" spans="1:12">
+      <c r="L493" s="5"/>
+      <c r="M493" s="6"/>
+    </row>
+    <row r="494" spans="1:13">
       <c r="A494" s="2"/>
       <c r="B494" s="3"/>
       <c r="F494" s="4"/>
@@ -6725,9 +7259,10 @@
       <c r="I494" s="5"/>
       <c r="J494" s="5"/>
       <c r="K494" s="5"/>
-      <c r="L494" s="6"/>
-    </row>
-    <row r="495" spans="1:12">
+      <c r="L494" s="5"/>
+      <c r="M494" s="6"/>
+    </row>
+    <row r="495" spans="1:13">
       <c r="A495" s="2"/>
       <c r="B495" s="3"/>
       <c r="F495" s="4"/>
@@ -6736,9 +7271,10 @@
       <c r="I495" s="5"/>
       <c r="J495" s="5"/>
       <c r="K495" s="5"/>
-      <c r="L495" s="6"/>
-    </row>
-    <row r="496" spans="1:12">
+      <c r="L495" s="5"/>
+      <c r="M495" s="6"/>
+    </row>
+    <row r="496" spans="1:13">
       <c r="A496" s="2"/>
       <c r="B496" s="3"/>
       <c r="F496" s="4"/>
@@ -6747,9 +7283,10 @@
       <c r="I496" s="5"/>
       <c r="J496" s="5"/>
       <c r="K496" s="5"/>
-      <c r="L496" s="6"/>
-    </row>
-    <row r="497" spans="1:12">
+      <c r="L496" s="5"/>
+      <c r="M496" s="6"/>
+    </row>
+    <row r="497" spans="1:13">
       <c r="A497" s="2"/>
       <c r="B497" s="3"/>
       <c r="F497" s="4"/>
@@ -6758,9 +7295,10 @@
       <c r="I497" s="5"/>
       <c r="J497" s="5"/>
       <c r="K497" s="5"/>
-      <c r="L497" s="6"/>
-    </row>
-    <row r="498" spans="1:12">
+      <c r="L497" s="5"/>
+      <c r="M497" s="6"/>
+    </row>
+    <row r="498" spans="1:13">
       <c r="A498" s="2"/>
       <c r="B498" s="3"/>
       <c r="F498" s="4"/>
@@ -6769,9 +7307,10 @@
       <c r="I498" s="5"/>
       <c r="J498" s="5"/>
       <c r="K498" s="5"/>
-      <c r="L498" s="6"/>
-    </row>
-    <row r="499" spans="1:12">
+      <c r="L498" s="5"/>
+      <c r="M498" s="6"/>
+    </row>
+    <row r="499" spans="1:13">
       <c r="A499" s="2"/>
       <c r="B499" s="3"/>
       <c r="F499" s="4"/>
@@ -6780,9 +7319,10 @@
       <c r="I499" s="5"/>
       <c r="J499" s="5"/>
       <c r="K499" s="5"/>
-      <c r="L499" s="6"/>
-    </row>
-    <row r="500" spans="1:12">
+      <c r="L499" s="5"/>
+      <c r="M499" s="6"/>
+    </row>
+    <row r="500" spans="1:13">
       <c r="A500" s="2"/>
       <c r="B500" s="3"/>
       <c r="F500" s="4"/>
@@ -6791,7 +7331,8 @@
       <c r="I500" s="5"/>
       <c r="J500" s="5"/>
       <c r="K500" s="5"/>
-      <c r="L500" s="6"/>
+      <c r="L500" s="5"/>
+      <c r="M500" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="1">
